--- a/database/event/2099/event_2099_evp_summary.xlsx
+++ b/database/event/2099/event_2099_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.1661</v>
+        <v>7.6156</v>
       </c>
       <c r="C2" t="n">
-        <v>4.1865</v>
+        <v>4.4491</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4736</v>
+        <v>2.5901</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1661</v>
+        <v>7.6156</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7141</v>
+        <v>4.1636</v>
       </c>
       <c r="G2" t="n">
         <v>3.452</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7141</v>
+        <v>4.1906</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0104</v>
+        <v>3.3966</v>
       </c>
       <c r="J2" t="n">
         <v>3.452</v>
@@ -529,7 +529,7 @@
         <v>101</v>
       </c>
       <c r="M2" t="n">
-        <v>6.462400000000001</v>
+        <v>6.848599999999999</v>
       </c>
       <c r="N2" t="n">
         <v>209</v>
@@ -548,7 +548,7 @@
         <v>3.5815</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0552</v>
+        <v>1.9985</v>
       </c>
       <c r="E3" t="n">
         <v>6.1305</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8188</v>
+        <v>5.8906</v>
       </c>
       <c r="C4" t="n">
-        <v>3.3994</v>
+        <v>3.4413</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9293</v>
+        <v>1.9029</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8188</v>
+        <v>5.8906</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5853</v>
+        <v>4.2411</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2335</v>
+        <v>1.6495</v>
       </c>
       <c r="H4" t="n">
-        <v>5.8874</v>
+        <v>4.5025</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7719</v>
+        <v>3.6494</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2335</v>
+        <v>1.6495</v>
       </c>
       <c r="K4" t="n">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="L4" t="n">
-        <v>91</v>
+        <v>151</v>
       </c>
       <c r="M4" t="n">
-        <v>6.0054</v>
+        <v>5.2989</v>
       </c>
       <c r="N4" t="n">
-        <v>279</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7645</v>
+        <v>5.8734</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3676</v>
+        <v>3.4313</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9074</v>
+        <v>1.8961</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7645</v>
+        <v>5.8734</v>
       </c>
       <c r="F5" t="n">
-        <v>4.115</v>
+        <v>4.6399</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6495</v>
+        <v>1.2335</v>
       </c>
       <c r="H5" t="n">
-        <v>4.115</v>
+        <v>6.1069</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3353</v>
+        <v>4.9498</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6495</v>
+        <v>1.2335</v>
       </c>
       <c r="K5" t="n">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="L5" t="n">
-        <v>151</v>
+        <v>91</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9848</v>
+        <v>6.1833</v>
       </c>
       <c r="N5" t="n">
-        <v>323</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6">
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5597</v>
+        <v>4.749</v>
       </c>
       <c r="C6" t="n">
-        <v>2.6638</v>
+        <v>2.7744</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4207</v>
+        <v>1.4481</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5597</v>
+        <v>4.749</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5816</v>
+        <v>2.7708</v>
       </c>
       <c r="G6" t="n">
         <v>1.9782</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5816</v>
+        <v>2.7708</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0924</v>
+        <v>2.2458</v>
       </c>
       <c r="J6" t="n">
         <v>1.9782</v>
@@ -713,7 +713,7 @@
         <v>101</v>
       </c>
       <c r="M6" t="n">
-        <v>4.0706</v>
+        <v>4.224</v>
       </c>
       <c r="N6" t="n">
         <v>209</v>
@@ -732,7 +732,7 @@
         <v>2.5385</v>
       </c>
       <c r="D7" t="n">
-        <v>1.334</v>
+        <v>1.2872</v>
       </c>
       <c r="E7" t="n">
         <v>4.3452</v>
@@ -778,7 +778,7 @@
         <v>2.4151</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2487</v>
+        <v>1.2031</v>
       </c>
       <c r="E8" t="n">
         <v>4.134</v>
@@ -814,127 +814,127 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2177</v>
+        <v>3.7149</v>
       </c>
       <c r="C9" t="n">
-        <v>1.8798</v>
+        <v>2.1703</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8784999999999999</v>
+        <v>1.0361</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2177</v>
+        <v>3.7149</v>
       </c>
       <c r="F9" t="n">
-        <v>4.2177</v>
+        <v>3.7149</v>
       </c>
       <c r="G9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4083</v>
+        <v>3.7149</v>
       </c>
       <c r="I9" t="n">
-        <v>3.573</v>
+        <v>3.7149</v>
       </c>
       <c r="J9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="L9" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.573</v>
+        <v>3.7149</v>
       </c>
       <c r="N9" t="n">
-        <v>206</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0945</v>
+        <v>3.3418</v>
       </c>
       <c r="C10" t="n">
-        <v>1.8078</v>
+        <v>1.9523</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8287</v>
+        <v>0.8875</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0945</v>
+        <v>3.3418</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3876</v>
+        <v>2.5691</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2931</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3876</v>
+        <v>2.5691</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7457</v>
+        <v>2.0824</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2931</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4526</v>
+        <v>2.8551</v>
       </c>
       <c r="N10" t="n">
-        <v>206</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0771</v>
+        <v>3.2636</v>
       </c>
       <c r="C11" t="n">
-        <v>1.7977</v>
+        <v>1.9066</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8217</v>
+        <v>0.8563</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0771</v>
+        <v>3.2636</v>
       </c>
       <c r="F11" t="n">
-        <v>3.9037</v>
+        <v>4.2636</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8266</v>
+        <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9037</v>
+        <v>4.5928</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1641</v>
+        <v>3.7226</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8266</v>
+        <v>-1</v>
       </c>
       <c r="K11" t="n">
         <v>165</v>
@@ -943,7 +943,7 @@
         <v>41</v>
       </c>
       <c r="M11" t="n">
-        <v>2.3375</v>
+        <v>2.7226</v>
       </c>
       <c r="N11" t="n">
         <v>206</v>
@@ -952,967 +952,967 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0198</v>
+        <v>3.1664</v>
       </c>
       <c r="C12" t="n">
-        <v>1.7642</v>
+        <v>1.8498</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7986</v>
+        <v>0.8176</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0198</v>
+        <v>3.1664</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2471</v>
+        <v>3.4595</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7727000000000001</v>
+        <v>-0.2931</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2471</v>
+        <v>3.4595</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8213</v>
+        <v>2.804</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7727000000000001</v>
+        <v>-0.2931</v>
       </c>
       <c r="K12" t="n">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="L12" t="n">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="M12" t="n">
-        <v>2.594</v>
+        <v>2.5109</v>
       </c>
       <c r="N12" t="n">
-        <v>279</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6801</v>
+        <v>3.1567</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5657</v>
+        <v>1.8442</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6613</v>
+        <v>0.8137</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6801</v>
+        <v>3.1567</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4142</v>
+        <v>3.1567</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2659</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4142</v>
+        <v>3.1567</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1463</v>
+        <v>3.1832</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2659</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="L13" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4122</v>
+        <v>3.1832</v>
       </c>
       <c r="N13" t="n">
-        <v>209</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.619</v>
+        <v>3.0771</v>
       </c>
       <c r="C14" t="n">
-        <v>1.53</v>
+        <v>1.7977</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6367</v>
+        <v>0.782</v>
       </c>
       <c r="E14" t="n">
-        <v>2.619</v>
+        <v>3.0771</v>
       </c>
       <c r="F14" t="n">
-        <v>2.619</v>
+        <v>3.9037</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.8266</v>
       </c>
       <c r="H14" t="n">
-        <v>2.619</v>
+        <v>3.9037</v>
       </c>
       <c r="I14" t="n">
-        <v>2.619</v>
+        <v>3.1641</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.8266</v>
       </c>
       <c r="K14" t="n">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M14" t="n">
-        <v>2.619</v>
+        <v>2.3375</v>
       </c>
       <c r="N14" t="n">
-        <v>105</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3966</v>
+        <v>2.9525</v>
       </c>
       <c r="C15" t="n">
-        <v>1.4001</v>
+        <v>1.7249</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5468</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3966</v>
+        <v>2.9525</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3966</v>
+        <v>2.9525</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3966</v>
+        <v>2.9525</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4078</v>
+        <v>2.9525</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4078</v>
+        <v>2.9525</v>
       </c>
       <c r="N15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2392</v>
+        <v>2.6801</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3081</v>
+        <v>1.5657</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4832</v>
+        <v>0.6238</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2392</v>
+        <v>2.6801</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2392</v>
+        <v>1.4142</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.2659</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2392</v>
+        <v>1.4142</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2392</v>
+        <v>1.1463</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.2659</v>
       </c>
       <c r="K16" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2392</v>
+        <v>2.4122</v>
       </c>
       <c r="N16" t="n">
-        <v>127</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1915</v>
+        <v>2.6438</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2803</v>
+        <v>1.5445</v>
       </c>
       <c r="D17" t="n">
-        <v>0.464</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1915</v>
+        <v>2.6438</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8499</v>
+        <v>2.6438</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3416</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8499</v>
+        <v>2.6438</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6889</v>
+        <v>2.6438</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3416</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="L17" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0305</v>
+        <v>2.6438</v>
       </c>
       <c r="N17" t="n">
-        <v>209</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8518</v>
+        <v>2.2221</v>
       </c>
       <c r="C18" t="n">
-        <v>1.0818</v>
+        <v>1.2982</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3267</v>
+        <v>0.4414</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8518</v>
+        <v>2.2221</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8518</v>
+        <v>2.2221</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8518</v>
+        <v>2.2221</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8518</v>
+        <v>2.2221</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8518</v>
+        <v>2.2221</v>
       </c>
       <c r="N18" t="n">
-        <v>127</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8482</v>
+        <v>2.1915</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0797</v>
+        <v>1.2803</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3253</v>
+        <v>0.4292</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8482</v>
+        <v>2.1915</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8482</v>
+        <v>0.8499</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1.3416</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8482</v>
+        <v>0.8499</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8482</v>
+        <v>0.6889</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.3416</v>
       </c>
       <c r="K19" t="n">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8482</v>
+        <v>2.0305</v>
       </c>
       <c r="N19" t="n">
-        <v>124</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5243</v>
+        <v>2.0187</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8905</v>
+        <v>1.1793</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1944</v>
+        <v>0.3603</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5243</v>
+        <v>2.0187</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5243</v>
+        <v>2.0187</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5243</v>
+        <v>2.0187</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5243</v>
+        <v>2.0187</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5243</v>
+        <v>2.0187</v>
       </c>
       <c r="N20" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.5237</v>
+        <v>1.8813</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8902</v>
+        <v>1.0991</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1942</v>
+        <v>0.3056</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5237</v>
+        <v>1.8813</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2301</v>
+        <v>1.8813</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2936</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2301</v>
+        <v>1.8813</v>
       </c>
       <c r="I21" t="n">
-        <v>0.997</v>
+        <v>1.8971</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2936</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>47</v>
+        <v>130</v>
       </c>
       <c r="L21" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2906</v>
+        <v>1.8971</v>
       </c>
       <c r="N21" t="n">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4728</v>
+        <v>1.7612</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8604000000000001</v>
+        <v>1.0289</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1736</v>
+        <v>0.2578</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4728</v>
+        <v>1.7612</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4728</v>
+        <v>1.8256</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.0644</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4728</v>
+        <v>1.8256</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4728</v>
+        <v>1.4797</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.0644</v>
       </c>
       <c r="K22" t="n">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4728</v>
+        <v>1.4153</v>
       </c>
       <c r="N22" t="n">
-        <v>111</v>
+        <v>323</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.4502</v>
+        <v>1.6139</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8472</v>
+        <v>0.9428</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1645</v>
+        <v>0.1991</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4502</v>
+        <v>1.6139</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5146</v>
+        <v>1.6139</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0644</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5146</v>
+        <v>1.6139</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2276</v>
+        <v>1.6139</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0644</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>172</v>
+        <v>105</v>
       </c>
       <c r="L23" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1632</v>
+        <v>1.6139</v>
       </c>
       <c r="N23" t="n">
-        <v>323</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3021</v>
+        <v>1.5419</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7607</v>
+        <v>0.9008</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1047</v>
+        <v>0.1704</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3021</v>
+        <v>1.5419</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3021</v>
+        <v>1.5419</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3021</v>
+        <v>1.5419</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3081</v>
+        <v>1.5419</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3081</v>
+        <v>1.5419</v>
       </c>
       <c r="N24" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.2881</v>
+        <v>1.5294</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.8935</v>
       </c>
       <c r="D25" t="n">
-        <v>0.099</v>
+        <v>0.1654</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2881</v>
+        <v>1.5294</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5785</v>
+        <v>1.5294</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2904</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5785</v>
+        <v>1.5294</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2794</v>
+        <v>1.5294</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2904</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>165</v>
+        <v>110</v>
       </c>
       <c r="L25" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9890000000000001</v>
+        <v>1.5294</v>
       </c>
       <c r="N25" t="n">
-        <v>206</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.198</v>
+        <v>1.5237</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6999</v>
+        <v>0.8902</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0626</v>
+        <v>0.1631</v>
       </c>
       <c r="E26" t="n">
-        <v>1.198</v>
+        <v>1.5237</v>
       </c>
       <c r="F26" t="n">
-        <v>1.198</v>
+        <v>1.2301</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.2936</v>
       </c>
       <c r="H26" t="n">
-        <v>1.198</v>
+        <v>1.2301</v>
       </c>
       <c r="I26" t="n">
-        <v>1.198</v>
+        <v>0.997</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.2936</v>
       </c>
       <c r="K26" t="n">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M26" t="n">
-        <v>1.198</v>
+        <v>1.2906</v>
       </c>
       <c r="N26" t="n">
-        <v>95</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.0651</v>
+        <v>1.4281</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6222</v>
+        <v>0.8343</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0089</v>
+        <v>0.125</v>
       </c>
       <c r="E27" t="n">
-        <v>1.0651</v>
+        <v>1.4281</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0651</v>
+        <v>1.4281</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.0651</v>
+        <v>1.4281</v>
       </c>
       <c r="I27" t="n">
-        <v>1.0651</v>
+        <v>1.4281</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.0651</v>
+        <v>1.4281</v>
       </c>
       <c r="N27" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9476</v>
+        <v>1.2965</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5536</v>
+        <v>0.7574</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0386</v>
+        <v>0.0726</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9476</v>
+        <v>1.2965</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9476</v>
+        <v>1.2965</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9476</v>
+        <v>1.2965</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9476</v>
+        <v>1.2965</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9476</v>
+        <v>1.2965</v>
       </c>
       <c r="N28" t="n">
-        <v>124</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TENZKI</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8957000000000001</v>
+        <v>1.2881</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5233</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0595</v>
+        <v>0.0693</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8957000000000001</v>
+        <v>1.2881</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8957000000000001</v>
+        <v>1.5785</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.2904</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8957000000000001</v>
+        <v>1.5785</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8957000000000001</v>
+        <v>1.2794</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.2904</v>
       </c>
       <c r="K29" t="n">
-        <v>95</v>
+        <v>165</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8957000000000001</v>
+        <v>0.9890000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>95</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>starix</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8687</v>
+        <v>1.1471</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5075</v>
+        <v>0.6701</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0704</v>
+        <v>0.0131</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8687</v>
+        <v>1.1471</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8687</v>
+        <v>1.1471</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8687</v>
+        <v>1.1471</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8687</v>
+        <v>1.1471</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8687</v>
+        <v>1.1471</v>
       </c>
       <c r="N30" t="n">
-        <v>61</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>starix</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8552999999999999</v>
+        <v>1.1123</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4997</v>
+        <v>0.6498</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.0008</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8552999999999999</v>
+        <v>1.1123</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2614</v>
+        <v>1.1123</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5939</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2614</v>
+        <v>1.1123</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2119</v>
+        <v>1.1123</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5939</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>172</v>
+        <v>61</v>
       </c>
       <c r="L31" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8058</v>
+        <v>1.1123</v>
       </c>
       <c r="N31" t="n">
-        <v>323</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>TENZKI</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7842</v>
+        <v>1.038</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4581</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1046</v>
+        <v>-0.0304</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7842</v>
+        <v>1.038</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7842</v>
+        <v>1.038</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7842</v>
+        <v>1.038</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7842</v>
+        <v>1.038</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7842</v>
+        <v>1.038</v>
       </c>
       <c r="N32" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7665999999999999</v>
+        <v>1.0315</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4479</v>
+        <v>0.6026</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1117</v>
+        <v>-0.033</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7665999999999999</v>
+        <v>1.0315</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7665999999999999</v>
+        <v>1.0315</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7665999999999999</v>
+        <v>1.0315</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7702</v>
+        <v>1.0402</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7702</v>
+        <v>1.0402</v>
       </c>
       <c r="N33" t="n">
         <v>192</v>
@@ -1964,32 +1964,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7319</v>
+        <v>0.863</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4276</v>
+        <v>0.5042</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1257</v>
+        <v>-0.1001</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7319</v>
+        <v>0.863</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7319</v>
+        <v>0.863</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7319</v>
+        <v>0.863</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7319</v>
+        <v>0.863</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7319</v>
+        <v>0.863</v>
       </c>
       <c r="N34" t="n">
         <v>70</v>
@@ -2010,47 +2010,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7252</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4237</v>
+        <v>0.4997</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1284</v>
+        <v>-0.1032</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7252</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7252</v>
+        <v>0.2614</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.5939</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7252</v>
+        <v>0.2614</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7252</v>
+        <v>0.2119</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.5939</v>
       </c>
       <c r="K35" t="n">
-        <v>95</v>
+        <v>172</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7252</v>
+        <v>0.8058</v>
       </c>
       <c r="N35" t="n">
-        <v>95</v>
+        <v>323</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6016</v>
+        <v>0.7548</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3515</v>
+        <v>0.441</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1783</v>
+        <v>-0.1432</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6016</v>
+        <v>0.7548</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6016</v>
+        <v>0.7548</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6016</v>
+        <v>0.7548</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6016</v>
+        <v>0.7548</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6016</v>
+        <v>0.7548</v>
       </c>
       <c r="N36" t="n">
         <v>52</v>
@@ -2102,170 +2102,170 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.55</v>
+        <v>0.7319</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3213</v>
+        <v>0.4276</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1992</v>
+        <v>-0.1523</v>
       </c>
       <c r="E37" t="n">
-        <v>0.55</v>
+        <v>0.7319</v>
       </c>
       <c r="F37" t="n">
-        <v>0.55</v>
+        <v>0.7319</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.55</v>
+        <v>0.7319</v>
       </c>
       <c r="I37" t="n">
-        <v>0.55</v>
+        <v>0.7319</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.55</v>
+        <v>0.7319</v>
       </c>
       <c r="N37" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4993</v>
+        <v>0.7252</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2917</v>
+        <v>0.4237</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2197</v>
+        <v>-0.155</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4993</v>
+        <v>0.7252</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4993</v>
+        <v>0.7252</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4993</v>
+        <v>0.7252</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4993</v>
+        <v>0.7252</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4993</v>
+        <v>0.7252</v>
       </c>
       <c r="N38" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.484</v>
+        <v>0.6083</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2828</v>
+        <v>0.3554</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2258</v>
+        <v>-0.2016</v>
       </c>
       <c r="E39" t="n">
-        <v>0.484</v>
+        <v>0.6083</v>
       </c>
       <c r="F39" t="n">
-        <v>0.484</v>
+        <v>0.6083</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.484</v>
+        <v>0.6083</v>
       </c>
       <c r="I39" t="n">
-        <v>0.484</v>
+        <v>0.6083</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.484</v>
+        <v>0.6083</v>
       </c>
       <c r="N39" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4638</v>
+        <v>0.5507</v>
       </c>
       <c r="C40" t="n">
-        <v>0.271</v>
+        <v>0.3217</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.234</v>
+        <v>-0.2245</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4638</v>
+        <v>0.5507</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4638</v>
+        <v>0.5507</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4638</v>
+        <v>0.5507</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4638</v>
+        <v>0.5507</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4638</v>
+        <v>0.5507</v>
       </c>
       <c r="N40" t="n">
         <v>95</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4119</v>
+        <v>0.4149</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2406</v>
+        <v>0.2424</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.255</v>
+        <v>-0.2786</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4119</v>
+        <v>0.4149</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4119</v>
+        <v>0.4149</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4119</v>
+        <v>0.4149</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4138</v>
+        <v>0.4184</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4138</v>
+        <v>0.4184</v>
       </c>
       <c r="N41" t="n">
         <v>130</v>
@@ -2342,7 +2342,7 @@
         <v>0.1718</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3026</v>
+        <v>-0.3268</v>
       </c>
       <c r="E42" t="n">
         <v>0.294</v>
@@ -2378,93 +2378,93 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.257</v>
+        <v>0.284</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1501</v>
+        <v>0.1659</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3175</v>
+        <v>-0.3308</v>
       </c>
       <c r="E43" t="n">
-        <v>0.257</v>
+        <v>0.284</v>
       </c>
       <c r="F43" t="n">
-        <v>0.257</v>
+        <v>0.284</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.257</v>
+        <v>0.284</v>
       </c>
       <c r="I43" t="n">
-        <v>0.257</v>
+        <v>0.284</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.257</v>
+        <v>0.284</v>
       </c>
       <c r="N43" t="n">
-        <v>49</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2421</v>
+        <v>0.257</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1414</v>
+        <v>0.1501</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3236</v>
+        <v>-0.3415</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2421</v>
+        <v>0.257</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2421</v>
+        <v>0.257</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2421</v>
+        <v>0.257</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2421</v>
+        <v>0.257</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2421</v>
+        <v>0.257</v>
       </c>
       <c r="N44" t="n">
-        <v>111</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45">
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.1891</v>
+        <v>0.1884</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1105</v>
+        <v>0.1101</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.345</v>
+        <v>-0.3689</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1891</v>
+        <v>0.1884</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1891</v>
+        <v>0.1884</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1891</v>
+        <v>0.1884</v>
       </c>
       <c r="I45" t="n">
         <v>0.19</v>
@@ -2526,7 +2526,7 @@
         <v>0.0658</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3759</v>
+        <v>-0.3991</v>
       </c>
       <c r="E46" t="n">
         <v>0.1126</v>
@@ -2572,7 +2572,7 @@
         <v>0.0558</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3828</v>
+        <v>-0.4059</v>
       </c>
       <c r="E47" t="n">
         <v>0.0955</v>
@@ -2608,32 +2608,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0081</v>
+        <v>0.0532</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0047</v>
+        <v>0.0311</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4181</v>
+        <v>-0.4227</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0081</v>
+        <v>0.0532</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0081</v>
+        <v>0.0532</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0081</v>
+        <v>0.0532</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0081</v>
+        <v>0.0532</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.0081</v>
+        <v>0.0532</v>
       </c>
       <c r="N48" t="n">
         <v>127</v>
@@ -2654,78 +2654,78 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0024</v>
+        <v>0.0081</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0014</v>
+        <v>0.0047</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4204</v>
+        <v>-0.4407</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0024</v>
+        <v>0.0081</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0024</v>
+        <v>0.0081</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0024</v>
+        <v>0.0081</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0024</v>
+        <v>0.0081</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.0024</v>
+        <v>0.0081</v>
       </c>
       <c r="N49" t="n">
-        <v>52</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1243</v>
+        <v>0.0024</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0726</v>
+        <v>0.0014</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4716</v>
+        <v>-0.443</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1243</v>
+        <v>0.0024</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1243</v>
+        <v>0.0024</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1243</v>
+        <v>0.0024</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1243</v>
+        <v>0.0024</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1243</v>
+        <v>0.0024</v>
       </c>
       <c r="N50" t="n">
         <v>52</v>
@@ -2746,170 +2746,170 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1249</v>
+        <v>-0.0309</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.073</v>
+        <v>-0.0181</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4718</v>
+        <v>-0.4562</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1249</v>
+        <v>-0.0309</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1249</v>
+        <v>-0.0309</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1249</v>
+        <v>-0.0309</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1255</v>
+        <v>-0.0309</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>192</v>
+        <v>110</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1255</v>
+        <v>-0.0309</v>
       </c>
       <c r="N51" t="n">
-        <v>192</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.155</v>
+        <v>-0.04</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0906</v>
+        <v>-0.0234</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.484</v>
+        <v>-0.4598</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.155</v>
+        <v>-0.04</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.155</v>
+        <v>-0.04</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.155</v>
+        <v>-0.04</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.155</v>
+        <v>-0.04</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.155</v>
+        <v>-0.04</v>
       </c>
       <c r="N52" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.164</v>
+        <v>-0.1243</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0958</v>
+        <v>-0.0726</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4876</v>
+        <v>-0.4934</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.164</v>
+        <v>-0.1243</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.164</v>
+        <v>-0.1243</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.164</v>
+        <v>-0.1243</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.164</v>
+        <v>-0.1243</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>111</v>
+        <v>52</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.164</v>
+        <v>-0.1243</v>
       </c>
       <c r="N53" t="n">
-        <v>111</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2151</v>
+        <v>-0.1245</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1257</v>
+        <v>-0.0727</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5083</v>
+        <v>-0.4935</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2151</v>
+        <v>-0.1245</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2151</v>
+        <v>-0.1245</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2151</v>
+        <v>-0.1245</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2161</v>
+        <v>-0.1255</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.2161</v>
+        <v>-0.1255</v>
       </c>
       <c r="N54" t="n">
         <v>192</v>
@@ -2930,170 +2930,170 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2533</v>
+        <v>-0.2143</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.148</v>
+        <v>-0.1252</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.5293</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2533</v>
+        <v>-0.2143</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2533</v>
+        <v>-0.2143</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.2533</v>
+        <v>-0.2143</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2545</v>
+        <v>-0.2161</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.2545</v>
+        <v>-0.2161</v>
       </c>
       <c r="N55" t="n">
-        <v>130</v>
+        <v>192</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MINISE</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2888</v>
+        <v>-0.2234</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1687</v>
+        <v>-0.1305</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.538</v>
+        <v>-0.5329</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2888</v>
+        <v>-0.2234</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2888</v>
+        <v>-0.2234</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2888</v>
+        <v>-0.2234</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2888</v>
+        <v>-0.2253</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.2888</v>
+        <v>-0.2253</v>
       </c>
       <c r="N56" t="n">
-        <v>49</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>MINISE</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.2988</v>
+        <v>-0.2888</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1746</v>
+        <v>-0.1687</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5421</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.2988</v>
+        <v>-0.2888</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2988</v>
+        <v>-0.2888</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2988</v>
+        <v>-0.2888</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2988</v>
+        <v>-0.2888</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.2988</v>
+        <v>-0.2888</v>
       </c>
       <c r="N57" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.3208</v>
+        <v>-0.2988</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1874</v>
+        <v>-0.1746</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.551</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.3208</v>
+        <v>-0.2988</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.3208</v>
+        <v>-0.2988</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.3208</v>
+        <v>-0.2988</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.3208</v>
+        <v>-0.2988</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.3208</v>
+        <v>-0.2988</v>
       </c>
       <c r="N58" t="n">
         <v>70</v>
@@ -3114,461 +3114,461 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.3224</v>
+        <v>-0.3123</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1883</v>
+        <v>-0.1824</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5516</v>
+        <v>-0.5683</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.3224</v>
+        <v>-0.3123</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.3224</v>
+        <v>-0.3123</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.3224</v>
+        <v>-0.3123</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3224</v>
+        <v>-0.3123</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.3224</v>
+        <v>-0.3123</v>
       </c>
       <c r="N59" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.382</v>
+        <v>-0.3208</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2232</v>
+        <v>-0.1874</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5757</v>
+        <v>-0.5717</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.382</v>
+        <v>-0.3208</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.382</v>
+        <v>-0.3208</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.382</v>
+        <v>-0.3208</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.382</v>
+        <v>-0.3208</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.382</v>
+        <v>-0.3208</v>
       </c>
       <c r="N60" t="n">
-        <v>124</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.3978</v>
+        <v>-0.3224</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2324</v>
+        <v>-0.1883</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5821</v>
+        <v>-0.5724</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3978</v>
+        <v>-0.3224</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.3978</v>
+        <v>-0.3224</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.3978</v>
+        <v>-0.3224</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3978</v>
+        <v>-0.3224</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.3978</v>
+        <v>-0.3224</v>
       </c>
       <c r="N61" t="n">
-        <v>127</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.4395</v>
+        <v>-0.382</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2568</v>
+        <v>-0.2232</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5989</v>
+        <v>-0.5961</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.4395</v>
+        <v>-0.382</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.4395</v>
+        <v>-0.382</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.4395</v>
+        <v>-0.382</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.4395</v>
+        <v>-0.382</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.4395</v>
+        <v>-0.382</v>
       </c>
       <c r="N62" t="n">
-        <v>42</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.4417</v>
+        <v>-0.4395</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.258</v>
+        <v>-0.2568</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.5998</v>
+        <v>-0.619</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4417</v>
+        <v>-0.4395</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.4417</v>
+        <v>-0.4395</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.4417</v>
+        <v>-0.4395</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.4417</v>
+        <v>-0.4395</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.4417</v>
+        <v>-0.4395</v>
       </c>
       <c r="N63" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.4821</v>
+        <v>-0.4417</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2816</v>
+        <v>-0.258</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6161</v>
+        <v>-0.6199</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.4821</v>
+        <v>-0.4417</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.4821</v>
+        <v>-0.4417</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.4821</v>
+        <v>-0.4417</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4821</v>
+        <v>-0.4417</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.4821</v>
+        <v>-0.4417</v>
       </c>
       <c r="N64" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SZPERO</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.5038</v>
+        <v>-0.4821</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2943</v>
+        <v>-0.2816</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6249</v>
+        <v>-0.636</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.5038</v>
+        <v>-0.4821</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.5038</v>
+        <v>-0.4821</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.5038</v>
+        <v>-0.4821</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5038</v>
+        <v>-0.4821</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.5038</v>
+        <v>-0.4821</v>
       </c>
       <c r="N65" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>SZPERO</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.5748</v>
+        <v>-0.5038</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3358</v>
+        <v>-0.2943</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6536</v>
+        <v>-0.6446</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.5748</v>
+        <v>-0.5038</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.5748</v>
+        <v>-0.5038</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.5748</v>
+        <v>-0.5038</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5748</v>
+        <v>-0.5038</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.5748</v>
+        <v>-0.5038</v>
       </c>
       <c r="N66" t="n">
-        <v>105</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>innocent</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.6256</v>
+        <v>-0.5748</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.3655</v>
+        <v>-0.3358</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.6741</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.6256</v>
+        <v>-0.5748</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.6256</v>
+        <v>-0.5748</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.6256</v>
+        <v>-0.5748</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.6256</v>
+        <v>-0.5748</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.6256</v>
+        <v>-0.5748</v>
       </c>
       <c r="N67" t="n">
-        <v>49</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>innocent</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.6368</v>
+        <v>-0.6256</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.372</v>
+        <v>-0.3655</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.6786</v>
+        <v>-0.6931</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.6368</v>
+        <v>-0.6256</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.6368</v>
+        <v>-0.6256</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.6368</v>
+        <v>-0.6256</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.6368</v>
+        <v>-0.6256</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.6368</v>
+        <v>-0.6256</v>
       </c>
       <c r="N68" t="n">
-        <v>111</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69">
@@ -3584,7 +3584,7 @@
         <v>-0.3856</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.7069</v>
       </c>
       <c r="E69" t="n">
         <v>-0.66</v>
@@ -3630,7 +3630,7 @@
         <v>-0.3919</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.6924</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="E70" t="n">
         <v>-0.6708</v>
@@ -3666,323 +3666,323 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.7003</v>
+        <v>-0.6842</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.4091</v>
+        <v>-0.3997</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.7043</v>
+        <v>-0.7165</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.7003</v>
+        <v>-0.6842</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.7003</v>
+        <v>-0.6842</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.7003</v>
+        <v>-0.6842</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7003</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.7003</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="N71" t="n">
-        <v>124</v>
+        <v>192</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.7178</v>
+        <v>-0.7003</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4193</v>
+        <v>-0.4091</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.7113</v>
+        <v>-0.7229</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.7178</v>
+        <v>-0.7003</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.7178</v>
+        <v>-0.7003</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.7178</v>
+        <v>-0.7003</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.7178</v>
+        <v>-0.7003</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.7178</v>
+        <v>-0.7003</v>
       </c>
       <c r="N72" t="n">
-        <v>42</v>
+        <v>124</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.8333</v>
+        <v>-0.7178</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.4868</v>
+        <v>-0.4193</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.758</v>
+        <v>-0.7299</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.8333</v>
+        <v>-0.7178</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.8333</v>
+        <v>-0.7178</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.8333</v>
+        <v>-0.7178</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.8333</v>
+        <v>-0.7178</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.8333</v>
+        <v>-0.7178</v>
       </c>
       <c r="N73" t="n">
-        <v>124</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.8333</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.4926</v>
+        <v>-0.4868</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.762</v>
+        <v>-0.7759</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.8333</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.8333</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.8333</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.8333</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.8333</v>
       </c>
       <c r="N74" t="n">
-        <v>105</v>
+        <v>124</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.8739</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.5105</v>
+        <v>-0.4926</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.7744</v>
+        <v>-0.7798</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.8739</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.8739</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.8739</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.8739</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.8739</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="N75" t="n">
-        <v>42</v>
+        <v>105</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.0486</v>
+        <v>-0.8739</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.6126</v>
+        <v>-0.5105</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.845</v>
+        <v>-0.7921</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.0486</v>
+        <v>-0.8739</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.0486</v>
+        <v>-0.8739</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.0486</v>
+        <v>-0.8739</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.0486</v>
+        <v>-0.8739</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.0486</v>
+        <v>-0.8739</v>
       </c>
       <c r="N76" t="n">
-        <v>110</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.1095</v>
+        <v>-1.0486</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.6482</v>
+        <v>-0.6126</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.8696</v>
+        <v>-0.8617</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.1095</v>
+        <v>-1.0486</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.1095</v>
+        <v>-1.0486</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.1095</v>
+        <v>-1.0486</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.1147</v>
+        <v>-1.0486</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>192</v>
+        <v>110</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.1147</v>
+        <v>-1.0486</v>
       </c>
       <c r="N77" t="n">
-        <v>192</v>
+        <v>110</v>
       </c>
     </row>
     <row r="78">
@@ -3998,7 +3998,7 @@
         <v>-0.6748</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.888</v>
+        <v>-0.9041</v>
       </c>
       <c r="E78" t="n">
         <v>-1.155</v>
@@ -4044,7 +4044,7 @@
         <v>-0.6939</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.9012</v>
+        <v>-0.9171</v>
       </c>
       <c r="E79" t="n">
         <v>-1.1877</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.3516</v>
+        <v>-1.3466</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.7896</v>
+        <v>-0.7867</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.9674</v>
+        <v>-0.9804</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.3516</v>
+        <v>-1.3466</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.3516</v>
+        <v>-1.3466</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.3516</v>
+        <v>-1.3466</v>
       </c>
       <c r="I80" t="n">
         <v>-1.3579</v>
@@ -4136,7 +4136,7 @@
         <v>-0.9552</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.0819</v>
+        <v>-1.0953</v>
       </c>
       <c r="E81" t="n">
         <v>-1.6351</v>
@@ -4182,7 +4182,7 @@
         <v>-2.3846</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.0703</v>
+        <v>-2.0701</v>
       </c>
       <c r="E82" t="n">
         <v>-4.0818</v>

--- a/database/event/2099/event_2099_evp_summary.xlsx
+++ b/database/event/2099/event_2099_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.4249</v>
+        <v>6.5731</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7534</v>
+        <v>3.84</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2625</v>
+        <v>2.368</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4249</v>
+        <v>6.5731</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3701</v>
+        <v>3.2948</v>
       </c>
       <c r="G2" t="n">
-        <v>3.0547</v>
+        <v>3.2783</v>
       </c>
       <c r="H2" t="n">
-        <v>6.3879</v>
+        <v>5.9766</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3214</v>
+        <v>3.2273</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0547</v>
+        <v>3.2783</v>
       </c>
       <c r="K2" t="n">
         <v>108</v>
@@ -529,7 +529,7 @@
         <v>101</v>
       </c>
       <c r="M2" t="n">
-        <v>6.3761</v>
+        <v>6.5056</v>
       </c>
       <c r="N2" t="n">
         <v>209</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4706</v>
+        <v>5.5303</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1959</v>
+        <v>3.2308</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8317</v>
+        <v>1.8933</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4706</v>
+        <v>5.5303</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4483</v>
+        <v>4.3784</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0223</v>
+        <v>1.1519</v>
       </c>
       <c r="H3" t="n">
-        <v>10.1867</v>
+        <v>9.5518</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2966</v>
+        <v>5.1579</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0223</v>
+        <v>1.1519</v>
       </c>
       <c r="K3" t="n">
         <v>188</v>
@@ -575,7 +575,7 @@
         <v>91</v>
       </c>
       <c r="M3" t="n">
-        <v>6.318899999999999</v>
+        <v>6.309799999999999</v>
       </c>
       <c r="N3" t="n">
         <v>279</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3566</v>
+        <v>5.3397</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1293</v>
+        <v>3.1195</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7802</v>
+        <v>1.8065</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3566</v>
+        <v>5.3397</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6662</v>
+        <v>3.5909</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6904</v>
+        <v>1.7488</v>
       </c>
       <c r="H4" t="n">
-        <v>7.431</v>
+        <v>6.9534</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8638</v>
+        <v>3.7548</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6904</v>
+        <v>1.7488</v>
       </c>
       <c r="K4" t="n">
         <v>172</v>
@@ -621,7 +621,7 @@
         <v>151</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5542</v>
+        <v>5.5036</v>
       </c>
       <c r="N4" t="n">
         <v>323</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.9486</v>
+        <v>4.9642</v>
       </c>
       <c r="C5" t="n">
-        <v>2.891</v>
+        <v>2.9001</v>
       </c>
       <c r="D5" t="n">
-        <v>1.596</v>
+        <v>1.6356</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9486</v>
+        <v>4.9642</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6446</v>
+        <v>3.5477</v>
       </c>
       <c r="G5" t="n">
-        <v>1.304</v>
+        <v>1.4165</v>
       </c>
       <c r="H5" t="n">
-        <v>7.3551</v>
+        <v>6.8108</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8243</v>
+        <v>3.6778</v>
       </c>
       <c r="J5" t="n">
-        <v>1.304</v>
+        <v>1.4165</v>
       </c>
       <c r="K5" t="n">
         <v>172</v>
@@ -667,7 +667,7 @@
         <v>151</v>
       </c>
       <c r="M5" t="n">
-        <v>5.1283</v>
+        <v>5.0943</v>
       </c>
       <c r="N5" t="n">
         <v>323</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3983</v>
+        <v>4.4975</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5695</v>
+        <v>2.6275</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3476</v>
+        <v>1.4232</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3983</v>
+        <v>4.4975</v>
       </c>
       <c r="F6" t="n">
-        <v>2.832</v>
+        <v>2.7574</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5663</v>
+        <v>1.7401</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4917</v>
+        <v>4.2036</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3355</v>
+        <v>2.2699</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5663</v>
+        <v>1.7401</v>
       </c>
       <c r="K6" t="n">
         <v>108</v>
@@ -713,7 +713,7 @@
         <v>101</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9018</v>
+        <v>4.01</v>
       </c>
       <c r="N6" t="n">
         <v>209</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9313</v>
+        <v>3.9984</v>
       </c>
       <c r="C7" t="n">
-        <v>2.2967</v>
+        <v>2.3359</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1368</v>
+        <v>1.196</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9313</v>
+        <v>3.9984</v>
       </c>
       <c r="F7" t="n">
-        <v>3.197</v>
+        <v>3.0967</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7343</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>5.7778</v>
+        <v>5.3229</v>
       </c>
       <c r="I7" t="n">
-        <v>3.0042</v>
+        <v>2.8743</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7343</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>172</v>
@@ -759,7 +759,7 @@
         <v>151</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7385</v>
+        <v>3.776</v>
       </c>
       <c r="N7" t="n">
         <v>323</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9049</v>
+        <v>3.8934</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2813</v>
+        <v>2.2745</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1249</v>
+        <v>1.1482</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9049</v>
+        <v>3.8934</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3361</v>
+        <v>3.2938</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5688</v>
+        <v>0.5996</v>
       </c>
       <c r="H8" t="n">
-        <v>6.2679</v>
+        <v>5.9732</v>
       </c>
       <c r="I8" t="n">
-        <v>3.259</v>
+        <v>3.2255</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5688</v>
+        <v>0.5996</v>
       </c>
       <c r="K8" t="n">
         <v>188</v>
@@ -805,7 +805,7 @@
         <v>91</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8278</v>
+        <v>3.8251</v>
       </c>
       <c r="N8" t="n">
         <v>279</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6272</v>
+        <v>3.614</v>
       </c>
       <c r="C9" t="n">
-        <v>2.119</v>
+        <v>2.1113</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9995000000000001</v>
+        <v>1.021</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6272</v>
+        <v>3.614</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8311</v>
+        <v>2.7476</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7961</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4889</v>
+        <v>4.1712</v>
       </c>
       <c r="I9" t="n">
-        <v>2.334</v>
+        <v>2.2524</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7961</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>188</v>
@@ -851,7 +851,7 @@
         <v>91</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1301</v>
+        <v>3.1188</v>
       </c>
       <c r="N9" t="n">
         <v>279</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4747</v>
+        <v>3.5265</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0299</v>
+        <v>2.0602</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9306</v>
+        <v>0.9811</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4747</v>
+        <v>3.5265</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3629</v>
+        <v>2.3</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1118</v>
+        <v>1.2265</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8391</v>
+        <v>2.6945</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4762</v>
+        <v>1.455</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1118</v>
+        <v>1.2265</v>
       </c>
       <c r="K10" t="n">
         <v>108</v>
@@ -897,7 +897,7 @@
         <v>101</v>
       </c>
       <c r="M10" t="n">
-        <v>2.588</v>
+        <v>2.6815</v>
       </c>
       <c r="N10" t="n">
         <v>209</v>
@@ -906,139 +906,139 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1959</v>
+        <v>2.9744</v>
       </c>
       <c r="C11" t="n">
-        <v>1.8671</v>
+        <v>1.7377</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8048</v>
+        <v>0.7298</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1959</v>
+        <v>2.9744</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1959</v>
+        <v>3.5976</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0.6232</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6579</v>
+        <v>6.9757</v>
       </c>
       <c r="I11" t="n">
-        <v>3.6579</v>
+        <v>3.7668</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.6232</v>
       </c>
       <c r="K11" t="n">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6579</v>
+        <v>3.1436</v>
       </c>
       <c r="N11" t="n">
-        <v>105</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9791</v>
+        <v>2.942</v>
       </c>
       <c r="C12" t="n">
-        <v>1.7404</v>
+        <v>1.7187</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7069</v>
+        <v>0.7151</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9791</v>
+        <v>2.942</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5755</v>
+        <v>1.6371</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5964</v>
+        <v>1.3049</v>
       </c>
       <c r="H12" t="n">
-        <v>7.1114</v>
+        <v>1.6371</v>
       </c>
       <c r="I12" t="n">
-        <v>3.6976</v>
+        <v>0.884</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5964</v>
+        <v>1.3049</v>
       </c>
       <c r="K12" t="n">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="L12" t="n">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1012</v>
+        <v>2.1889</v>
       </c>
       <c r="N12" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9388</v>
+        <v>2.8632</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7169</v>
+        <v>1.6727</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6887</v>
+        <v>0.6792</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9388</v>
+        <v>2.8632</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9388</v>
+        <v>2.8632</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0933</v>
+        <v>3.5418</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0933</v>
+        <v>3.5418</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0933</v>
+        <v>3.5418</v>
       </c>
       <c r="N13" t="n">
-        <v>127</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8796</v>
+        <v>2.737</v>
       </c>
       <c r="C14" t="n">
-        <v>1.6823</v>
+        <v>1.599</v>
       </c>
       <c r="D14" t="n">
-        <v>0.662</v>
+        <v>0.6217</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8796</v>
+        <v>2.737</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1528</v>
+        <v>3.0582</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2732</v>
+        <v>-0.3212</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6222</v>
+        <v>5.1958</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9233</v>
+        <v>2.8057</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2732</v>
+        <v>-0.3212</v>
       </c>
       <c r="K14" t="n">
         <v>165</v>
@@ -1081,7 +1081,7 @@
         <v>41</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6501</v>
+        <v>2.4845</v>
       </c>
       <c r="N14" t="n">
         <v>206</v>
@@ -1090,231 +1090,231 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8494</v>
+        <v>2.6288</v>
       </c>
       <c r="C15" t="n">
-        <v>1.6646</v>
+        <v>1.5358</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6483</v>
+        <v>0.5725</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8494</v>
+        <v>2.6288</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8494</v>
+        <v>2.6288</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.897</v>
+        <v>3.0287</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0162</v>
+        <v>3.0287</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0162</v>
+        <v>3.0287</v>
       </c>
       <c r="N15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8206</v>
+        <v>2.6197</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6478</v>
+        <v>1.5304</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6353</v>
+        <v>0.5683</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8206</v>
+        <v>2.6197</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6621</v>
+        <v>2.4861</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1585</v>
+        <v>0.1336</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6621</v>
+        <v>3.3084</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8642</v>
+        <v>1.7865</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1585</v>
+        <v>0.1336</v>
       </c>
       <c r="K16" t="n">
-        <v>108</v>
+        <v>172</v>
       </c>
       <c r="L16" t="n">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0227</v>
+        <v>1.9201</v>
       </c>
       <c r="N16" t="n">
-        <v>209</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.7195</v>
+        <v>2.5663</v>
       </c>
       <c r="C17" t="n">
-        <v>1.5887</v>
+        <v>1.4992</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5897</v>
+        <v>0.544</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7195</v>
+        <v>2.5663</v>
       </c>
       <c r="F17" t="n">
-        <v>2.564</v>
+        <v>3.5663</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1555</v>
+        <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5476</v>
+        <v>6.8725</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8446</v>
+        <v>3.7111</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1555</v>
+        <v>-1</v>
       </c>
       <c r="K17" t="n">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="L17" t="n">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0001</v>
+        <v>2.7111</v>
       </c>
       <c r="N17" t="n">
-        <v>323</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6726</v>
+        <v>2.5642</v>
       </c>
       <c r="C18" t="n">
-        <v>1.5613</v>
+        <v>1.498</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5685</v>
+        <v>0.5431</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6726</v>
+        <v>2.5642</v>
       </c>
       <c r="F18" t="n">
-        <v>3.6726</v>
+        <v>2.0274</v>
       </c>
       <c r="G18" t="n">
-        <v>-1</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>7.4535</v>
+        <v>2.0274</v>
       </c>
       <c r="I18" t="n">
-        <v>3.8755</v>
+        <v>1.0948</v>
       </c>
       <c r="J18" t="n">
-        <v>-1</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>165</v>
+        <v>47</v>
       </c>
       <c r="L18" t="n">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="M18" t="n">
-        <v>2.8755</v>
+        <v>1.6316</v>
       </c>
       <c r="N18" t="n">
-        <v>206</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.583</v>
+        <v>2.5594</v>
       </c>
       <c r="C19" t="n">
-        <v>1.509</v>
+        <v>1.4952</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5281</v>
+        <v>0.5409</v>
       </c>
       <c r="E19" t="n">
-        <v>2.583</v>
+        <v>2.5594</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1448</v>
+        <v>2.5594</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4382</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1448</v>
+        <v>2.8769</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1152</v>
+        <v>2.951</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4382</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>47</v>
+        <v>130</v>
       </c>
       <c r="L19" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5534</v>
+        <v>2.951</v>
       </c>
       <c r="N19" t="n">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.4521</v>
+        <v>2.3628</v>
       </c>
       <c r="C20" t="n">
-        <v>1.4325</v>
+        <v>1.3804</v>
       </c>
       <c r="D20" t="n">
-        <v>0.469</v>
+        <v>0.4514</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4521</v>
+        <v>2.3628</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4521</v>
+        <v>2.3628</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4521</v>
+        <v>2.4466</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4521</v>
+        <v>2.4466</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.4521</v>
+        <v>2.4466</v>
       </c>
       <c r="N20" t="n">
         <v>127</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.2601</v>
+        <v>2.1009</v>
       </c>
       <c r="C21" t="n">
-        <v>1.3204</v>
+        <v>1.2274</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3823</v>
+        <v>0.3322</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2601</v>
+        <v>2.1009</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4436</v>
+        <v>2.3689</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1835</v>
+        <v>-0.268</v>
       </c>
       <c r="H21" t="n">
-        <v>3.1235</v>
+        <v>2.9217</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6241</v>
+        <v>1.5777</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1835</v>
+        <v>-0.268</v>
       </c>
       <c r="K21" t="n">
         <v>165</v>
@@ -1403,7 +1403,7 @@
         <v>41</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4406</v>
+        <v>1.3097</v>
       </c>
       <c r="N21" t="n">
         <v>206</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0755</v>
+        <v>2.0113</v>
       </c>
       <c r="C22" t="n">
-        <v>1.2125</v>
+        <v>1.175</v>
       </c>
       <c r="D22" t="n">
-        <v>0.299</v>
+        <v>0.2914</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0755</v>
+        <v>2.0113</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4024</v>
+        <v>2.0113</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6731</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4024</v>
+        <v>2.0113</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7292</v>
+        <v>2.0113</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6731</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L22" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4023</v>
+        <v>2.0113</v>
       </c>
       <c r="N22" t="n">
-        <v>323</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.0358</v>
+        <v>1.9769</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1893</v>
+        <v>1.1549</v>
       </c>
       <c r="D23" t="n">
-        <v>0.281</v>
+        <v>0.2757</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0358</v>
+        <v>1.9769</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0358</v>
+        <v>1.2872</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.6897</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0358</v>
+        <v>1.2872</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0358</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.6897</v>
       </c>
       <c r="K23" t="n">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M23" t="n">
-        <v>2.0358</v>
+        <v>1.3848</v>
       </c>
       <c r="N23" t="n">
-        <v>111</v>
+        <v>323</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9792</v>
+        <v>1.9044</v>
       </c>
       <c r="C24" t="n">
-        <v>1.1563</v>
+        <v>1.1126</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2555</v>
+        <v>0.2427</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9792</v>
+        <v>1.9044</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9792</v>
+        <v>1.9044</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9792</v>
+        <v>1.9044</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9792</v>
+        <v>1.9044</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9792</v>
+        <v>1.9044</v>
       </c>
       <c r="N24" t="n">
         <v>124</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.7813</v>
+        <v>1.7784</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0406</v>
+        <v>1.0389</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1662</v>
+        <v>0.1854</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7813</v>
+        <v>1.7784</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7813</v>
+        <v>1.7784</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7813</v>
+        <v>1.7784</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8546</v>
+        <v>1.8242</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.8546</v>
+        <v>1.8242</v>
       </c>
       <c r="N25" t="n">
         <v>130</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7352</v>
+        <v>1.6738</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0137</v>
+        <v>0.9778</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1453</v>
+        <v>0.1377</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7352</v>
+        <v>1.6738</v>
       </c>
       <c r="F26" t="n">
-        <v>1.7352</v>
+        <v>1.6738</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7352</v>
+        <v>1.6738</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7352</v>
+        <v>1.6738</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.7352</v>
+        <v>1.6738</v>
       </c>
       <c r="N26" t="n">
         <v>95</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7069</v>
+        <v>1.6109</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9972</v>
+        <v>0.9411</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1326</v>
+        <v>0.1091</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7069</v>
+        <v>1.6109</v>
       </c>
       <c r="F27" t="n">
-        <v>1.7069</v>
+        <v>1.6109</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.7069</v>
+        <v>1.6109</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7069</v>
+        <v>1.6109</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.7069</v>
+        <v>1.6109</v>
       </c>
       <c r="N27" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6526</v>
+        <v>1.5946</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9655</v>
+        <v>0.9316</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1081</v>
+        <v>0.1017</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6526</v>
+        <v>1.5946</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6526</v>
+        <v>1.5946</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6526</v>
+        <v>1.5946</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6526</v>
+        <v>1.5946</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.6526</v>
+        <v>1.5946</v>
       </c>
       <c r="N28" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.4247</v>
+        <v>1.3772</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8323</v>
+        <v>0.8046</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0052</v>
+        <v>0.0027</v>
       </c>
       <c r="E29" t="n">
-        <v>1.4247</v>
+        <v>1.3772</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4247</v>
+        <v>1.3772</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.4247</v>
+        <v>1.3772</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4247</v>
+        <v>1.3772</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.4247</v>
+        <v>1.3772</v>
       </c>
       <c r="N29" t="n">
         <v>124</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3995</v>
+        <v>1.3152</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8176</v>
+        <v>0.7683</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0062</v>
+        <v>-0.0255</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3995</v>
+        <v>1.3152</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3995</v>
+        <v>1.3152</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.3995</v>
+        <v>1.3152</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4571</v>
+        <v>1.3491</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4571</v>
+        <v>1.3491</v>
       </c>
       <c r="N30" t="n">
         <v>192</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.2476</v>
+        <v>1.1518</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7289</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.0999</v>
       </c>
       <c r="E31" t="n">
-        <v>1.2476</v>
+        <v>1.1518</v>
       </c>
       <c r="F31" t="n">
-        <v>1.2476</v>
+        <v>1.1518</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2476</v>
+        <v>1.1518</v>
       </c>
       <c r="I31" t="n">
-        <v>1.2476</v>
+        <v>1.1518</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.2476</v>
+        <v>1.1518</v>
       </c>
       <c r="N31" t="n">
         <v>95</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>starix</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.145</v>
+        <v>1.1133</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.6504</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1211</v>
+        <v>-0.1174</v>
       </c>
       <c r="E32" t="n">
-        <v>1.145</v>
+        <v>1.1133</v>
       </c>
       <c r="F32" t="n">
-        <v>1.145</v>
+        <v>1.1133</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.145</v>
+        <v>1.1133</v>
       </c>
       <c r="I32" t="n">
-        <v>1.145</v>
+        <v>1.1133</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.145</v>
+        <v>1.1133</v>
       </c>
       <c r="N32" t="n">
-        <v>61</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>starix</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1353</v>
+        <v>1.0984</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6632</v>
+        <v>0.6417</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1255</v>
+        <v>-0.1242</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1353</v>
+        <v>1.0984</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1353</v>
+        <v>1.0984</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1353</v>
+        <v>1.0984</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1353</v>
+        <v>1.0984</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1353</v>
+        <v>1.0984</v>
       </c>
       <c r="N33" t="n">
-        <v>111</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.1154</v>
+        <v>1.0764</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6516</v>
+        <v>0.6288</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1345</v>
+        <v>-0.1342</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1154</v>
+        <v>1.0764</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1154</v>
+        <v>1.0764</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.1154</v>
+        <v>1.0764</v>
       </c>
       <c r="I34" t="n">
-        <v>1.1154</v>
+        <v>1.0764</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1154</v>
+        <v>1.0764</v>
       </c>
       <c r="N34" t="n">
         <v>95</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.0516</v>
+        <v>1.013</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6143</v>
+        <v>0.5918</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1633</v>
+        <v>-0.1631</v>
       </c>
       <c r="E35" t="n">
-        <v>1.0516</v>
+        <v>1.013</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0516</v>
+        <v>1.013</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.0516</v>
+        <v>1.013</v>
       </c>
       <c r="I35" t="n">
-        <v>1.0516</v>
+        <v>1.013</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.0516</v>
+        <v>1.013</v>
       </c>
       <c r="N35" t="n">
         <v>70</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.0058</v>
+        <v>0.9607</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5876</v>
+        <v>0.5612</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1839</v>
+        <v>-0.1869</v>
       </c>
       <c r="E36" t="n">
-        <v>1.0058</v>
+        <v>0.9607</v>
       </c>
       <c r="F36" t="n">
-        <v>1.0058</v>
+        <v>0.9607</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.0058</v>
+        <v>0.9607</v>
       </c>
       <c r="I36" t="n">
-        <v>1.0058</v>
+        <v>0.9607</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.0058</v>
+        <v>0.9607</v>
       </c>
       <c r="N36" t="n">
         <v>52</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9222</v>
+        <v>0.8652</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2217</v>
+        <v>-0.2303</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9222</v>
+        <v>0.8652</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9222</v>
+        <v>0.8652</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9222</v>
+        <v>0.8652</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9222</v>
+        <v>0.8652</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.9222</v>
+        <v>0.8652</v>
       </c>
       <c r="N37" t="n">
         <v>95</v>
@@ -2148,139 +2148,139 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5256</v>
+        <v>0.4962</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2318</v>
+        <v>-0.2376</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8722</v>
+        <v>0.8168</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5095</v>
+        <v>0.4772</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2443</v>
+        <v>-0.2524</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8722</v>
+        <v>0.8168</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8722</v>
+        <v>0.8168</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8722</v>
+        <v>0.8168</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8722</v>
+        <v>0.8168</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8722</v>
+        <v>0.8168</v>
       </c>
       <c r="N39" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8549</v>
+        <v>0.7975</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4994</v>
+        <v>0.4659</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2521</v>
+        <v>-0.2612</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8549</v>
+        <v>0.7975</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8549</v>
+        <v>0.7975</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8549</v>
+        <v>0.7975</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8549</v>
+        <v>0.7975</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8549</v>
+        <v>0.7975</v>
       </c>
       <c r="N40" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6933</v>
+        <v>0.6865</v>
       </c>
       <c r="C41" t="n">
-        <v>0.405</v>
+        <v>0.4011</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.325</v>
+        <v>-0.3117</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6933</v>
+        <v>0.6865</v>
       </c>
       <c r="F41" t="n">
-        <v>1.0411</v>
+        <v>1.0559</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.3478</v>
+        <v>-0.3694</v>
       </c>
       <c r="H41" t="n">
-        <v>1.0411</v>
+        <v>1.0559</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5413</v>
+        <v>0.5702</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.3478</v>
+        <v>-0.3694</v>
       </c>
       <c r="K41" t="n">
         <v>188</v>
@@ -2323,7 +2323,7 @@
         <v>91</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1935</v>
+        <v>0.2008</v>
       </c>
       <c r="N41" t="n">
         <v>279</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.6424</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3719</v>
+        <v>0.3753</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3506</v>
+        <v>-0.3318</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.6424</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.6424</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.6424</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.659</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.659</v>
       </c>
       <c r="N42" t="n">
         <v>130</v>
@@ -2378,124 +2378,124 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5067</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3354</v>
+        <v>0.296</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3788</v>
+        <v>-0.3935</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5067</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5067</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5067</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5198</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5198</v>
       </c>
       <c r="N43" t="n">
-        <v>111</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5491</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3208</v>
+        <v>0.2953</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3901</v>
+        <v>-0.3941</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5491</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5491</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5491</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5717</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.5717</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>130</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4746</v>
+        <v>0.4785</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2773</v>
+        <v>0.2795</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4238</v>
+        <v>-0.4064</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4746</v>
+        <v>0.4785</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4746</v>
+        <v>0.4785</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.4746</v>
+        <v>0.4785</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4746</v>
+        <v>0.4785</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4746</v>
+        <v>0.4785</v>
       </c>
       <c r="N45" t="n">
         <v>127</v>
@@ -2516,185 +2516,185 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4446</v>
+        <v>0.4349</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2597</v>
+        <v>0.2541</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4373</v>
+        <v>-0.4262</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4446</v>
+        <v>0.4349</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4446</v>
+        <v>0.4349</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4446</v>
+        <v>0.4349</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4446</v>
+        <v>0.4349</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.4446</v>
+        <v>0.4349</v>
       </c>
       <c r="N46" t="n">
-        <v>52</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.442</v>
+        <v>0.4203</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2582</v>
+        <v>0.2455</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4385</v>
+        <v>-0.4329</v>
       </c>
       <c r="E47" t="n">
-        <v>0.442</v>
+        <v>0.4203</v>
       </c>
       <c r="F47" t="n">
-        <v>0.442</v>
+        <v>0.4203</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.442</v>
+        <v>0.4203</v>
       </c>
       <c r="I47" t="n">
-        <v>0.442</v>
+        <v>0.4203</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.442</v>
+        <v>0.4203</v>
       </c>
       <c r="N47" t="n">
-        <v>127</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.3902</v>
+        <v>0.3028</v>
       </c>
       <c r="C48" t="n">
-        <v>0.228</v>
+        <v>0.1769</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4619</v>
+        <v>-0.4864</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3902</v>
+        <v>0.3028</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3902</v>
+        <v>0.3028</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3902</v>
+        <v>0.3028</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3902</v>
+        <v>0.3028</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.3902</v>
+        <v>0.3028</v>
       </c>
       <c r="N48" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.3389</v>
+        <v>0.2966</v>
       </c>
       <c r="C49" t="n">
-        <v>0.198</v>
+        <v>0.1733</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.485</v>
+        <v>-0.4892</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3389</v>
+        <v>0.2966</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3389</v>
+        <v>0.2966</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3389</v>
+        <v>0.2966</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3389</v>
+        <v>0.2966</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.3389</v>
+        <v>0.2966</v>
       </c>
       <c r="N49" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50">
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.3162</v>
+        <v>0.2786</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1847</v>
+        <v>0.1628</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4953</v>
+        <v>-0.4974</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3162</v>
+        <v>0.2786</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3162</v>
+        <v>0.2786</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.3162</v>
+        <v>0.2786</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3162</v>
+        <v>0.2786</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.3162</v>
+        <v>0.2786</v>
       </c>
       <c r="N50" t="n">
         <v>52</v>
@@ -2746,185 +2746,185 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.3066</v>
+        <v>0.2562</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1791</v>
+        <v>0.1497</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4996</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3066</v>
+        <v>0.2562</v>
       </c>
       <c r="F51" t="n">
-        <v>0.3066</v>
+        <v>0.2562</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.3066</v>
+        <v>0.2562</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3066</v>
+        <v>0.2562</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.3066</v>
+        <v>0.2562</v>
       </c>
       <c r="N51" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.2784</v>
+        <v>0.2131</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1626</v>
+        <v>0.1245</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5123</v>
+        <v>-0.5272</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2784</v>
+        <v>0.2131</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2784</v>
+        <v>0.2131</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2784</v>
+        <v>0.2131</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2899</v>
+        <v>0.2131</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>192</v>
+        <v>110</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.2899</v>
+        <v>0.2131</v>
       </c>
       <c r="N52" t="n">
-        <v>192</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.2447</v>
+        <v>0.2018</v>
       </c>
       <c r="C53" t="n">
-        <v>0.143</v>
+        <v>0.1179</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5275</v>
+        <v>-0.5323</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2447</v>
+        <v>0.2018</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2447</v>
+        <v>0.2018</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2447</v>
+        <v>0.2018</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2447</v>
+        <v>0.2018</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>127</v>
+        <v>49</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.2447</v>
+        <v>0.2018</v>
       </c>
       <c r="N53" t="n">
-        <v>127</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.2101</v>
+        <v>0.18</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1227</v>
+        <v>0.1052</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5432</v>
+        <v>-0.5423</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2101</v>
+        <v>0.18</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2101</v>
+        <v>0.18</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2101</v>
+        <v>0.18</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2101</v>
+        <v>0.1846</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>49</v>
+        <v>192</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2101</v>
+        <v>0.1846</v>
       </c>
       <c r="N54" t="n">
-        <v>49</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55">
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.2052</v>
+        <v>0.1374</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1199</v>
+        <v>0.0803</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5454</v>
+        <v>-0.5617</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2052</v>
+        <v>0.1374</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2052</v>
+        <v>0.1374</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2052</v>
+        <v>0.1374</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2052</v>
+        <v>0.1374</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2052</v>
+        <v>0.1374</v>
       </c>
       <c r="N55" t="n">
         <v>111</v>
@@ -2976,185 +2976,185 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.0584</v>
+        <v>0.0214</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0341</v>
+        <v>0.0125</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6116</v>
+        <v>-0.6145</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0584</v>
+        <v>0.0214</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0584</v>
+        <v>0.0214</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0584</v>
+        <v>0.0214</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0608</v>
+        <v>0.0214</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>192</v>
+        <v>52</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.0608</v>
+        <v>0.0214</v>
       </c>
       <c r="N56" t="n">
-        <v>192</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.0295</v>
+        <v>0.0083</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0172</v>
+        <v>0.0048</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6247</v>
+        <v>-0.6204</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0295</v>
+        <v>0.0083</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0295</v>
+        <v>0.0083</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0295</v>
+        <v>0.0083</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0295</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>52</v>
+        <v>192</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.0295</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="N57" t="n">
-        <v>52</v>
+        <v>192</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.0237</v>
+        <v>0.0062</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0138</v>
+        <v>0.0036</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6273</v>
+        <v>-0.6214</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0237</v>
+        <v>0.0062</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0237</v>
+        <v>0.0062</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0237</v>
+        <v>0.0062</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0237</v>
+        <v>0.0064</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.0237</v>
+        <v>0.0064</v>
       </c>
       <c r="N58" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.0156</v>
+        <v>-0.0058</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.0091</v>
+        <v>-0.0034</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6451</v>
+        <v>-0.6268</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.0156</v>
+        <v>-0.0058</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.0156</v>
+        <v>-0.0058</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.0156</v>
+        <v>-0.0058</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0162</v>
+        <v>-0.0058</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.0162</v>
+        <v>-0.0058</v>
       </c>
       <c r="N59" t="n">
-        <v>130</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60">
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0828</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0389</v>
+        <v>-0.0484</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6681</v>
+        <v>-0.6619</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0828</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0828</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0828</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0828</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0828</v>
       </c>
       <c r="N60" t="n">
         <v>49</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.1417</v>
+        <v>-0.1447</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0828</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.702</v>
+        <v>-0.6901</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.1417</v>
+        <v>-0.1447</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.1417</v>
+        <v>-0.1447</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.1417</v>
+        <v>-0.1447</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1417</v>
+        <v>-0.1447</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.1417</v>
+        <v>-0.1447</v>
       </c>
       <c r="N61" t="n">
         <v>70</v>
@@ -3256,28 +3256,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.186</v>
+        <v>-0.2017</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1087</v>
+        <v>-0.1178</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.722</v>
+        <v>-0.716</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.186</v>
+        <v>-0.2017</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.186</v>
+        <v>-0.2017</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.186</v>
+        <v>-0.2017</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.186</v>
+        <v>-0.2017</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.186</v>
+        <v>-0.2017</v>
       </c>
       <c r="N62" t="n">
         <v>70</v>
@@ -3302,28 +3302,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.2057</v>
+        <v>-0.2045</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1202</v>
+        <v>-0.1195</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7309</v>
+        <v>-0.7173</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.2057</v>
+        <v>-0.2045</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.2057</v>
+        <v>-0.2045</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.2057</v>
+        <v>-0.2045</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2057</v>
+        <v>-0.2045</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.2057</v>
+        <v>-0.2045</v>
       </c>
       <c r="N63" t="n">
         <v>70</v>
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.2314</v>
+        <v>-0.2519</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1352</v>
+        <v>-0.1472</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7425</v>
+        <v>-0.7389</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.2314</v>
+        <v>-0.2519</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.2314</v>
+        <v>-0.2519</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.2314</v>
+        <v>-0.2519</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2314</v>
+        <v>-0.2519</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.2314</v>
+        <v>-0.2519</v>
       </c>
       <c r="N64" t="n">
         <v>42</v>
@@ -3390,93 +3390,93 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.2837</v>
+        <v>-0.3004</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1657</v>
+        <v>-0.1755</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7661</v>
+        <v>-0.761</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.2837</v>
+        <v>-0.3004</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.2837</v>
+        <v>-0.3004</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.2837</v>
+        <v>-0.3004</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2837</v>
+        <v>-0.3004</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.2837</v>
+        <v>-0.3004</v>
       </c>
       <c r="N65" t="n">
-        <v>124</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.285</v>
+        <v>-0.3122</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1665</v>
+        <v>-0.1824</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7667</v>
+        <v>-0.7663</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.285</v>
+        <v>-0.3122</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.285</v>
+        <v>-0.3122</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.285</v>
+        <v>-0.3122</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2967</v>
+        <v>-0.3122</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.2967</v>
+        <v>-0.3122</v>
       </c>
       <c r="N66" t="n">
-        <v>192</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67">
@@ -3486,28 +3486,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.3332</v>
+        <v>-0.3458</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1947</v>
+        <v>-0.202</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7884</v>
+        <v>-0.7816</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.3332</v>
+        <v>-0.3458</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.3332</v>
+        <v>-0.3458</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.3332</v>
+        <v>-0.3458</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.3332</v>
+        <v>-0.3458</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.3332</v>
+        <v>-0.3458</v>
       </c>
       <c r="N67" t="n">
         <v>49</v>
@@ -3532,28 +3532,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.3367</v>
+        <v>-0.3514</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.1967</v>
+        <v>-0.2053</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.79</v>
+        <v>-0.7842</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.3367</v>
+        <v>-0.3514</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.3367</v>
+        <v>-0.3514</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.3367</v>
+        <v>-0.3514</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3367</v>
+        <v>-0.3514</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.3367</v>
+        <v>-0.3514</v>
       </c>
       <c r="N68" t="n">
         <v>124</v>
@@ -3574,78 +3574,78 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.3558</v>
+        <v>-0.3608</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2079</v>
+        <v>-0.2108</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7986</v>
+        <v>-0.7884</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.3558</v>
+        <v>-0.3608</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.3558</v>
+        <v>-0.3608</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.3558</v>
+        <v>-0.3608</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3558</v>
+        <v>-0.3701</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.3558</v>
+        <v>-0.3701</v>
       </c>
       <c r="N69" t="n">
-        <v>42</v>
+        <v>192</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.3724</v>
+        <v>-0.3759</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.2176</v>
+        <v>-0.2196</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8061</v>
+        <v>-0.7953</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.3724</v>
+        <v>-0.3759</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.3724</v>
+        <v>-0.3759</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.3724</v>
+        <v>-0.3759</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3724</v>
+        <v>-0.3759</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.3724</v>
+        <v>-0.3759</v>
       </c>
       <c r="N70" t="n">
         <v>105</v>
@@ -3666,124 +3666,124 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.387</v>
+        <v>-0.4042</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.2261</v>
+        <v>-0.2361</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8127</v>
+        <v>-0.8082</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.387</v>
+        <v>-0.4042</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.387</v>
+        <v>-0.4042</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.387</v>
+        <v>-0.4042</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.387</v>
+        <v>-0.4042</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.387</v>
+        <v>-0.4042</v>
       </c>
       <c r="N71" t="n">
-        <v>105</v>
+        <v>42</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>innocent</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.4345</v>
+        <v>-0.4544</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.2538</v>
+        <v>-0.2655</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.4345</v>
+        <v>-0.4544</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.4345</v>
+        <v>-0.4544</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.4345</v>
+        <v>-0.4544</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.4345</v>
+        <v>-0.4544</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.4345</v>
+        <v>-0.4544</v>
       </c>
       <c r="N72" t="n">
-        <v>49</v>
+        <v>124</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>mouz</t>
+          <t>innocent</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.4644</v>
+        <v>-0.4682</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.2713</v>
+        <v>-0.2735</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8477</v>
+        <v>-0.8373</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.4644</v>
+        <v>-0.4682</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.4644</v>
+        <v>-0.4682</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.4644</v>
+        <v>-0.4682</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.4644</v>
+        <v>-0.4682</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.4644</v>
+        <v>-0.4682</v>
       </c>
       <c r="N73" t="n">
         <v>49</v>
@@ -3804,47 +3804,47 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>mouz</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.4886</v>
+        <v>-0.4977</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.2854</v>
+        <v>-0.2908</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8586</v>
+        <v>-0.8508</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.4886</v>
+        <v>-0.4977</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.4886</v>
+        <v>-0.4977</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.4886</v>
+        <v>-0.4977</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.4886</v>
+        <v>-0.4977</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.4886</v>
+        <v>-0.4977</v>
       </c>
       <c r="N74" t="n">
-        <v>124</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75">
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.4974</v>
+        <v>-0.5366</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.2906</v>
+        <v>-0.3135</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.8626</v>
+        <v>-0.8685</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.4974</v>
+        <v>-0.5366</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.4974</v>
+        <v>-0.5366</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.4974</v>
+        <v>-0.5366</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4974</v>
+        <v>-0.5366</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.4974</v>
+        <v>-0.5366</v>
       </c>
       <c r="N75" t="n">
         <v>110</v>
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.5255</v>
+        <v>-0.5677</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.307</v>
+        <v>-0.3317</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.8753</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.5255</v>
+        <v>-0.5677</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.5255</v>
+        <v>-0.5677</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.5255</v>
+        <v>-0.5677</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5255</v>
+        <v>-0.5677</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.5255</v>
+        <v>-0.5677</v>
       </c>
       <c r="N76" t="n">
         <v>42</v>
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.6231</v>
+        <v>-0.6484</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.364</v>
+        <v>-0.3788</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.9193</v>
+        <v>-0.9194</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.6231</v>
+        <v>-0.6484</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.6231</v>
+        <v>-0.6484</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.6231</v>
+        <v>-0.6484</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.6231</v>
+        <v>-0.6484</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.6231</v>
+        <v>-0.6484</v>
       </c>
       <c r="N77" t="n">
         <v>42</v>
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.7766</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.442</v>
+        <v>-0.4537</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.9796</v>
+        <v>-0.9777</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.7766</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.7766</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.7766</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.7766</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.7766</v>
       </c>
       <c r="N78" t="n">
         <v>52</v>
@@ -4034,93 +4034,93 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>pronax</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.7988</v>
+        <v>-0.7916</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.4667</v>
+        <v>-0.4625</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.9986</v>
+        <v>-0.9846</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.7988</v>
+        <v>-0.7916</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.7988</v>
+        <v>-0.2532</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>-0.5384</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.7988</v>
+        <v>-0.2532</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.7988</v>
+        <v>-0.1367</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>-0.5384</v>
       </c>
       <c r="K79" t="n">
-        <v>42</v>
+        <v>188</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.7988</v>
+        <v>-0.6751</v>
       </c>
       <c r="N79" t="n">
-        <v>42</v>
+        <v>279</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>pronax</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.8408</v>
+        <v>-0.828</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.4912</v>
+        <v>-0.4837</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.0176</v>
+        <v>-1.0011</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.8408</v>
+        <v>-0.828</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.336</v>
+        <v>-0.828</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.5048</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.336</v>
+        <v>-0.828</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1747</v>
+        <v>-0.828</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.5048</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>188</v>
+        <v>42</v>
       </c>
       <c r="L80" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-0.6795</v>
+        <v>-0.828</v>
       </c>
       <c r="N80" t="n">
-        <v>279</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81">
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.9954</v>
+        <v>-1.0397</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.5815</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.0874</v>
+        <v>-1.0975</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.9954</v>
+        <v>-1.0397</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.9954</v>
+        <v>-1.0397</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.9954</v>
+        <v>-1.0397</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.0363</v>
+        <v>-1.0665</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-1.0363</v>
+        <v>-1.0665</v>
       </c>
       <c r="N81" t="n">
         <v>192</v>
@@ -4176,31 +4176,31 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-4.9372</v>
+        <v>-4.4456</v>
       </c>
       <c r="C82" t="n">
-        <v>-2.8843</v>
+        <v>-2.5971</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.8669</v>
+        <v>-2.6479</v>
       </c>
       <c r="E82" t="n">
-        <v>-4.9372</v>
+        <v>-4.4456</v>
       </c>
       <c r="F82" t="n">
-        <v>-4.1069</v>
+        <v>-3.5839</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.8303</v>
+        <v>-0.8617</v>
       </c>
       <c r="H82" t="n">
-        <v>-4.1069</v>
+        <v>-3.5839</v>
       </c>
       <c r="I82" t="n">
-        <v>-2.1354</v>
+        <v>-1.9353</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.8303</v>
+        <v>-0.8617</v>
       </c>
       <c r="K82" t="n">
         <v>165</v>
@@ -4209,7 +4209,7 @@
         <v>41</v>
       </c>
       <c r="M82" t="n">
-        <v>-2.9657</v>
+        <v>-2.797</v>
       </c>
       <c r="N82" t="n">
         <v>206</v>
@@ -4315,10 +4315,10 @@
         <v>1.09</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2393</v>
+        <v>0.2425</v>
       </c>
       <c r="J2" t="n">
-        <v>7.179</v>
+        <v>7.275</v>
       </c>
     </row>
     <row r="3">
@@ -4355,10 +4355,10 @@
         <v>0.97</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0464</v>
+        <v>-0.0554</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.392</v>
+        <v>-1.662</v>
       </c>
     </row>
     <row r="4">
@@ -4395,10 +4395,10 @@
         <v>0.95</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0717</v>
+        <v>-0.0829</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.151</v>
+        <v>-2.487</v>
       </c>
     </row>
     <row r="5">
@@ -4435,10 +4435,10 @@
         <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1177</v>
+        <v>-0.1313</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.531</v>
+        <v>-3.939</v>
       </c>
     </row>
     <row r="6">
@@ -4475,10 +4475,10 @@
         <v>0.83</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2027</v>
+        <v>-0.2176</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.081</v>
+        <v>-6.528</v>
       </c>
     </row>
     <row r="7">
@@ -4515,10 +4515,10 @@
         <v>1.22</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6384</v>
+        <v>0.6091</v>
       </c>
       <c r="J7" t="n">
-        <v>19.152</v>
+        <v>18.273</v>
       </c>
     </row>
     <row r="8">
@@ -4555,10 +4555,10 @@
         <v>1.18</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5374</v>
+        <v>0.519</v>
       </c>
       <c r="J8" t="n">
-        <v>16.122</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="9">
@@ -4595,10 +4595,10 @@
         <v>1.11</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3529</v>
+        <v>0.3512</v>
       </c>
       <c r="J9" t="n">
-        <v>10.587</v>
+        <v>10.536</v>
       </c>
     </row>
     <row r="10">
@@ -4635,10 +4635,10 @@
         <v>0.97</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1516</v>
+        <v>-0.1503</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.548</v>
+        <v>-4.509</v>
       </c>
     </row>
     <row r="11">
@@ -4675,10 +4675,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.252</v>
+        <v>-0.2464</v>
       </c>
       <c r="J11" t="n">
-        <v>-7.56</v>
+        <v>-7.392</v>
       </c>
     </row>
     <row r="12">
@@ -4715,10 +4715,10 @@
         <v>1.27</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5753</v>
+        <v>0.5574</v>
       </c>
       <c r="J12" t="n">
-        <v>17.259</v>
+        <v>16.722</v>
       </c>
     </row>
     <row r="13">
@@ -4755,10 +4755,10 @@
         <v>1.02</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0712</v>
+        <v>0.077</v>
       </c>
       <c r="J13" t="n">
-        <v>2.136</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="14">
@@ -4795,10 +4795,10 @@
         <v>0.95</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0733</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.199</v>
+        <v>-2.523</v>
       </c>
     </row>
     <row r="15">
@@ -4835,10 +4835,10 @@
         <v>0.84</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1951</v>
+        <v>-0.2094</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.853</v>
+        <v>-6.282</v>
       </c>
     </row>
     <row r="16">
@@ -4875,10 +4875,10 @@
         <v>0.78</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2556</v>
+        <v>-0.2695</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.668</v>
+        <v>-8.085000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -4915,10 +4915,10 @@
         <v>1.3</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7941</v>
+        <v>0.7533</v>
       </c>
       <c r="J17" t="n">
-        <v>23.823</v>
+        <v>22.599</v>
       </c>
     </row>
     <row r="18">
@@ -4955,10 +4955,10 @@
         <v>1.27</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7246</v>
+        <v>0.6921</v>
       </c>
       <c r="J18" t="n">
-        <v>21.738</v>
+        <v>20.763</v>
       </c>
     </row>
     <row r="19">
@@ -4995,10 +4995,10 @@
         <v>1.23</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6309</v>
+        <v>0.6088</v>
       </c>
       <c r="J19" t="n">
-        <v>18.927</v>
+        <v>18.264</v>
       </c>
     </row>
     <row r="20">
@@ -5035,10 +5035,10 @@
         <v>1.13</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3851</v>
+        <v>0.3861</v>
       </c>
       <c r="J20" t="n">
-        <v>11.553</v>
+        <v>11.583</v>
       </c>
     </row>
     <row r="21">
@@ -5075,10 +5075,10 @@
         <v>1.06</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1846</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
-        <v>5.538</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -5115,10 +5115,10 @@
         <v>1.35</v>
       </c>
       <c r="I22" t="n">
-        <v>0.535</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>16.05</v>
+        <v>17.949</v>
       </c>
     </row>
     <row r="23">
@@ -5155,10 +5155,10 @@
         <v>1.25</v>
       </c>
       <c r="I23" t="n">
-        <v>0.435</v>
+        <v>0.4838</v>
       </c>
       <c r="J23" t="n">
-        <v>13.05</v>
+        <v>14.514</v>
       </c>
     </row>
     <row r="24">
@@ -5195,10 +5195,10 @@
         <v>1.03</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0814</v>
+        <v>0.0926</v>
       </c>
       <c r="J24" t="n">
-        <v>2.442</v>
+        <v>2.778</v>
       </c>
     </row>
     <row r="25">
@@ -5235,10 +5235,10 @@
         <v>0.92</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1199</v>
+        <v>-0.13</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.597</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="26">
@@ -5275,10 +5275,10 @@
         <v>0.83</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2172</v>
+        <v>-0.2289</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.516</v>
+        <v>-6.867</v>
       </c>
     </row>
     <row r="27">
@@ -5315,10 +5315,10 @@
         <v>1.65</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1241</v>
+        <v>1.2184</v>
       </c>
       <c r="J27" t="n">
-        <v>33.723</v>
+        <v>36.552</v>
       </c>
     </row>
     <row r="28">
@@ -5355,10 +5355,10 @@
         <v>1.09</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3127</v>
+        <v>0.3107</v>
       </c>
       <c r="J28" t="n">
-        <v>9.381</v>
+        <v>9.321</v>
       </c>
     </row>
     <row r="29">
@@ -5395,10 +5395,10 @@
         <v>0.95</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2025</v>
+        <v>-0.2039</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.075</v>
+        <v>-6.117</v>
       </c>
     </row>
     <row r="30">
@@ -5435,10 +5435,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.601</v>
+        <v>-0.5684</v>
       </c>
       <c r="J30" t="n">
-        <v>-18.03</v>
+        <v>-17.052</v>
       </c>
     </row>
     <row r="31">
@@ -5475,10 +5475,10 @@
         <v>0.6</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.1207</v>
+        <v>-1.0212</v>
       </c>
       <c r="J31" t="n">
-        <v>-33.621</v>
+        <v>-30.636</v>
       </c>
     </row>
     <row r="32">
@@ -5515,10 +5515,10 @@
         <v>1.53</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5366</v>
+        <v>0.6113</v>
       </c>
       <c r="J32" t="n">
-        <v>18.781</v>
+        <v>21.3955</v>
       </c>
     </row>
     <row r="33">
@@ -5555,10 +5555,10 @@
         <v>1.1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1617</v>
+        <v>0.1773</v>
       </c>
       <c r="J33" t="n">
-        <v>5.6595</v>
+        <v>6.2055</v>
       </c>
     </row>
     <row r="34">
@@ -5595,10 +5595,10 @@
         <v>1.08</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1333</v>
+        <v>0.1485</v>
       </c>
       <c r="J34" t="n">
-        <v>4.6655</v>
+        <v>5.1975</v>
       </c>
     </row>
     <row r="35">
@@ -5635,10 +5635,10 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.01</v>
+        <v>-0.0077</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.35</v>
+        <v>-0.2695</v>
       </c>
     </row>
     <row r="36">
@@ -5675,10 +5675,10 @@
         <v>0.85</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2003</v>
+        <v>-0.2111</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.0105</v>
+        <v>-7.3885</v>
       </c>
     </row>
     <row r="37">
@@ -5715,10 +5715,10 @@
         <v>1.16</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2931</v>
+        <v>0.2961</v>
       </c>
       <c r="J37" t="n">
-        <v>10.2585</v>
+        <v>10.3635</v>
       </c>
     </row>
     <row r="38">
@@ -5755,10 +5755,10 @@
         <v>1.01</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0374</v>
+        <v>0.0402</v>
       </c>
       <c r="J38" t="n">
-        <v>1.309</v>
+        <v>1.407</v>
       </c>
     </row>
     <row r="39">
@@ -5795,10 +5795,10 @@
         <v>0.95</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0712</v>
+        <v>-0.0825</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.492</v>
+        <v>-2.8875</v>
       </c>
     </row>
     <row r="40">
@@ -5835,10 +5835,10 @@
         <v>0.82</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2119</v>
+        <v>-0.227</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.4165</v>
+        <v>-7.945</v>
       </c>
     </row>
     <row r="41">
@@ -5875,10 +5875,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2618</v>
+        <v>-0.2763</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.163</v>
+        <v>-9.670500000000001</v>
       </c>
     </row>
     <row r="42">
@@ -5915,10 +5915,10 @@
         <v>1.14</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3257</v>
+        <v>0.3297</v>
       </c>
       <c r="J42" t="n">
-        <v>8.4682</v>
+        <v>8.5722</v>
       </c>
     </row>
     <row r="43">
@@ -5955,10 +5955,10 @@
         <v>1.09</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2278</v>
+        <v>0.2341</v>
       </c>
       <c r="J43" t="n">
-        <v>5.9228</v>
+        <v>6.0866</v>
       </c>
     </row>
     <row r="44">
@@ -5995,10 +5995,10 @@
         <v>0.97</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0493</v>
+        <v>-0.0577</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.2818</v>
+        <v>-1.5002</v>
       </c>
     </row>
     <row r="45">
@@ -6035,10 +6035,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0873</v>
+        <v>-0.0984</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.2698</v>
+        <v>-2.5584</v>
       </c>
     </row>
     <row r="46">
@@ -6075,10 +6075,10 @@
         <v>0.82</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2179</v>
+        <v>-0.2317</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.6654</v>
+        <v>-6.0242</v>
       </c>
     </row>
     <row r="47">
@@ -6115,10 +6115,10 @@
         <v>1.56</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9451000000000001</v>
+        <v>1.0396</v>
       </c>
       <c r="J47" t="n">
-        <v>24.5726</v>
+        <v>27.0296</v>
       </c>
     </row>
     <row r="48">
@@ -6155,10 +6155,10 @@
         <v>1.4</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7389</v>
+        <v>0.8177</v>
       </c>
       <c r="J48" t="n">
-        <v>19.2114</v>
+        <v>21.2602</v>
       </c>
     </row>
     <row r="49">
@@ -6195,10 +6195,10 @@
         <v>1.2</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4675</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>12.155</v>
+        <v>13.4576</v>
       </c>
     </row>
     <row r="50">
@@ -6235,10 +6235,10 @@
         <v>0.95</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2494</v>
+        <v>-0.2366</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.4844</v>
+        <v>-6.1516</v>
       </c>
     </row>
     <row r="51">
@@ -6275,10 +6275,10 @@
         <v>0.87</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4874</v>
+        <v>-0.457</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.6724</v>
+        <v>-11.882</v>
       </c>
     </row>
     <row r="52">
@@ -6315,10 +6315,10 @@
         <v>1.95</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3677</v>
+        <v>1.4929</v>
       </c>
       <c r="J52" t="n">
-        <v>31.4571</v>
+        <v>34.3367</v>
       </c>
     </row>
     <row r="53">
@@ -6355,10 +6355,10 @@
         <v>1.44</v>
       </c>
       <c r="I53" t="n">
-        <v>0.762</v>
+        <v>0.8489</v>
       </c>
       <c r="J53" t="n">
-        <v>17.526</v>
+        <v>19.5247</v>
       </c>
     </row>
     <row r="54">
@@ -6395,10 +6395,10 @@
         <v>1.27</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5467</v>
+        <v>0.6112</v>
       </c>
       <c r="J54" t="n">
-        <v>12.5741</v>
+        <v>14.0576</v>
       </c>
     </row>
     <row r="55">
@@ -6435,10 +6435,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.358</v>
+        <v>0.3847</v>
       </c>
       <c r="J55" t="n">
-        <v>8.234</v>
+        <v>8.848100000000001</v>
       </c>
     </row>
     <row r="56">
@@ -6475,10 +6475,10 @@
         <v>1.01</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0319</v>
+        <v>-0.0005</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.7337</v>
+        <v>-0.0115</v>
       </c>
     </row>
     <row r="57">
@@ -6515,10 +6515,10 @@
         <v>0.99</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0228</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>0.5244</v>
+        <v>0.0138</v>
       </c>
     </row>
     <row r="58">
@@ -6555,10 +6555,10 @@
         <v>0.99</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0228</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>0.5244</v>
+        <v>0.0138</v>
       </c>
     </row>
     <row r="59">
@@ -6595,10 +6595,10 @@
         <v>0.75</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2611</v>
+        <v>-0.2798</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.0053</v>
+        <v>-6.4354</v>
       </c>
     </row>
     <row r="60">
@@ -6635,10 +6635,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3463</v>
+        <v>-0.3625</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.9649</v>
+        <v>-8.3375</v>
       </c>
     </row>
     <row r="61">
@@ -6675,10 +6675,10 @@
         <v>0.54</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4585</v>
+        <v>-0.4692</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.5455</v>
+        <v>-10.7916</v>
       </c>
     </row>
     <row r="62">
@@ -6715,10 +6715,10 @@
         <v>1.66</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9953</v>
+        <v>1.1066</v>
       </c>
       <c r="J62" t="n">
-        <v>17.9154</v>
+        <v>19.9188</v>
       </c>
     </row>
     <row r="63">
@@ -6755,10 +6755,10 @@
         <v>1.66</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9953</v>
+        <v>1.1066</v>
       </c>
       <c r="J63" t="n">
-        <v>17.9154</v>
+        <v>19.9188</v>
       </c>
     </row>
     <row r="64">
@@ -6795,10 +6795,10 @@
         <v>1.64</v>
       </c>
       <c r="I64" t="n">
-        <v>0.9728</v>
+        <v>1.0824</v>
       </c>
       <c r="J64" t="n">
-        <v>17.5104</v>
+        <v>19.4832</v>
       </c>
     </row>
     <row r="65">
@@ -6835,10 +6835,10 @@
         <v>1.61</v>
       </c>
       <c r="I65" t="n">
-        <v>0.9391</v>
+        <v>1.0461</v>
       </c>
       <c r="J65" t="n">
-        <v>16.9038</v>
+        <v>18.8298</v>
       </c>
     </row>
     <row r="66">
@@ -6875,10 +6875,10 @@
         <v>1.33</v>
       </c>
       <c r="I66" t="n">
-        <v>0.6016</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="J66" t="n">
-        <v>10.8288</v>
+        <v>12.2022</v>
       </c>
     </row>
     <row r="67">
@@ -6915,10 +6915,10 @@
         <v>0.95</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0776</v>
+        <v>0.0118</v>
       </c>
       <c r="J67" t="n">
-        <v>1.3968</v>
+        <v>0.2124</v>
       </c>
     </row>
     <row r="68">
@@ -6955,10 +6955,10 @@
         <v>0.67</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.296</v>
+        <v>-0.3218</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.328</v>
+        <v>-5.7924</v>
       </c>
     </row>
     <row r="69">
@@ -6995,10 +6995,10 @@
         <v>0.47</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.484</v>
+        <v>-0.4992</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.712</v>
+        <v>-8.9856</v>
       </c>
     </row>
     <row r="70">
@@ -7035,10 +7035,10 @@
         <v>0.35</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5996</v>
+        <v>-0.6059</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.7928</v>
+        <v>-10.9062</v>
       </c>
     </row>
     <row r="71">
@@ -7075,10 +7075,10 @@
         <v>0.33</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6192</v>
+        <v>-0.6238</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.1456</v>
+        <v>-11.2284</v>
       </c>
     </row>
     <row r="72">
@@ -7115,10 +7115,10 @@
         <v>1.55</v>
       </c>
       <c r="I72" t="n">
-        <v>1.1937</v>
+        <v>1.1623</v>
       </c>
       <c r="J72" t="n">
-        <v>33.4236</v>
+        <v>32.5444</v>
       </c>
     </row>
     <row r="73">
@@ -7155,10 +7155,10 @@
         <v>1.38</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9569</v>
+        <v>0.9014</v>
       </c>
       <c r="J73" t="n">
-        <v>26.7932</v>
+        <v>25.2392</v>
       </c>
     </row>
     <row r="74">
@@ -7195,10 +7195,10 @@
         <v>1.23</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6239</v>
+        <v>0.6041</v>
       </c>
       <c r="J74" t="n">
-        <v>17.4692</v>
+        <v>16.9148</v>
       </c>
     </row>
     <row r="75">
@@ -7235,10 +7235,10 @@
         <v>1.1</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2917</v>
+        <v>0.3027</v>
       </c>
       <c r="J75" t="n">
-        <v>8.1676</v>
+        <v>8.4756</v>
       </c>
     </row>
     <row r="76">
@@ -7275,10 +7275,10 @@
         <v>0.97</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1934</v>
+        <v>-0.1795</v>
       </c>
       <c r="J76" t="n">
-        <v>-5.4152</v>
+        <v>-5.026</v>
       </c>
     </row>
     <row r="77">
@@ -7315,10 +7315,10 @@
         <v>1.19</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4397</v>
+        <v>0.4308</v>
       </c>
       <c r="J77" t="n">
-        <v>12.3116</v>
+        <v>12.0624</v>
       </c>
     </row>
     <row r="78">
@@ -7355,10 +7355,10 @@
         <v>1.1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2622</v>
+        <v>0.2639</v>
       </c>
       <c r="J78" t="n">
-        <v>7.3416</v>
+        <v>7.3892</v>
       </c>
     </row>
     <row r="79">
@@ -7395,10 +7395,10 @@
         <v>0.87</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1604</v>
+        <v>-0.1752</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.4912</v>
+        <v>-4.9056</v>
       </c>
     </row>
     <row r="80">
@@ -7435,10 +7435,10 @@
         <v>0.82</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2122</v>
+        <v>-0.2272</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.9416</v>
+        <v>-6.3616</v>
       </c>
     </row>
     <row r="81">
@@ -7475,10 +7475,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2913</v>
+        <v>-0.3052</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.1564</v>
+        <v>-8.5456</v>
       </c>
     </row>
     <row r="82">
@@ -7515,10 +7515,10 @@
         <v>1.42</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0393</v>
+        <v>0.987</v>
       </c>
       <c r="J82" t="n">
-        <v>29.1004</v>
+        <v>27.636</v>
       </c>
     </row>
     <row r="83">
@@ -7555,10 +7555,10 @@
         <v>1.29</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7738</v>
+        <v>0.735</v>
       </c>
       <c r="J83" t="n">
-        <v>21.6664</v>
+        <v>20.58</v>
       </c>
     </row>
     <row r="84">
@@ -7595,10 +7595,10 @@
         <v>1.12</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3605</v>
+        <v>0.363</v>
       </c>
       <c r="J84" t="n">
-        <v>10.094</v>
+        <v>10.164</v>
       </c>
     </row>
     <row r="85">
@@ -7635,10 +7635,10 @@
         <v>1.12</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3605</v>
+        <v>0.363</v>
       </c>
       <c r="J85" t="n">
-        <v>10.094</v>
+        <v>10.164</v>
       </c>
     </row>
     <row r="86">
@@ -7675,10 +7675,10 @@
         <v>0.99</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1005</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>-2.814</v>
+        <v>-2.5564</v>
       </c>
     </row>
     <row r="87">
@@ -7715,10 +7715,10 @@
         <v>1.44</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.8384</v>
       </c>
       <c r="J87" t="n">
-        <v>24.9648</v>
+        <v>23.4752</v>
       </c>
     </row>
     <row r="88">
@@ -7755,10 +7755,10 @@
         <v>0.92</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1046</v>
+        <v>-0.1182</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.9288</v>
+        <v>-3.3096</v>
       </c>
     </row>
     <row r="89">
@@ -7795,10 +7795,10 @@
         <v>0.85</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1795</v>
+        <v>-0.1949</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.026</v>
+        <v>-5.4572</v>
       </c>
     </row>
     <row r="90">
@@ -7835,10 +7835,10 @@
         <v>0.8</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2304</v>
+        <v>-0.2457</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.4512</v>
+        <v>-6.8796</v>
       </c>
     </row>
     <row r="91">
@@ -7875,10 +7875,10 @@
         <v>0.63</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3936</v>
+        <v>-0.4044</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.0208</v>
+        <v>-11.3232</v>
       </c>
     </row>
     <row r="92">
@@ -7915,10 +7915,10 @@
         <v>1.72</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8267</v>
+        <v>0.8176</v>
       </c>
       <c r="J92" t="n">
-        <v>19.0141</v>
+        <v>18.8048</v>
       </c>
     </row>
     <row r="93">
@@ -7955,10 +7955,10 @@
         <v>1.43</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5255</v>
+        <v>0.537</v>
       </c>
       <c r="J93" t="n">
-        <v>12.0865</v>
+        <v>12.351</v>
       </c>
     </row>
     <row r="94">
@@ -7995,10 +7995,10 @@
         <v>1.42</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5148</v>
+        <v>0.5269</v>
       </c>
       <c r="J94" t="n">
-        <v>11.8404</v>
+        <v>12.1187</v>
       </c>
     </row>
     <row r="95">
@@ -8035,10 +8035,10 @@
         <v>1.19</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2558</v>
+        <v>0.2768</v>
       </c>
       <c r="J95" t="n">
-        <v>5.8834</v>
+        <v>6.3664</v>
       </c>
     </row>
     <row r="96">
@@ -8075,10 +8075,10 @@
         <v>0.93</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1333</v>
+        <v>-0.1374</v>
       </c>
       <c r="J96" t="n">
-        <v>-3.0659</v>
+        <v>-3.1602</v>
       </c>
     </row>
     <row r="97">
@@ -8115,10 +8115,10 @@
         <v>1.19</v>
       </c>
       <c r="I97" t="n">
-        <v>0.395</v>
+        <v>0.3817</v>
       </c>
       <c r="J97" t="n">
-        <v>9.085000000000001</v>
+        <v>8.7791</v>
       </c>
     </row>
     <row r="98">
@@ -8155,10 +8155,10 @@
         <v>0.97</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0202</v>
+        <v>-0.0352</v>
       </c>
       <c r="J98" t="n">
-        <v>-0.4646</v>
+        <v>-0.8096</v>
       </c>
     </row>
     <row r="99">
@@ -8195,10 +8195,10 @@
         <v>0.6</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4033</v>
+        <v>-0.4168</v>
       </c>
       <c r="J99" t="n">
-        <v>-9.2759</v>
+        <v>-9.586399999999999</v>
       </c>
     </row>
     <row r="100">
@@ -8235,10 +8235,10 @@
         <v>0.6</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4033</v>
+        <v>-0.4168</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.2759</v>
+        <v>-9.586399999999999</v>
       </c>
     </row>
     <row r="101">
@@ -8275,10 +8275,10 @@
         <v>0.59</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4126</v>
+        <v>-0.4257</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.489800000000001</v>
+        <v>-9.7911</v>
       </c>
     </row>
     <row r="102">
@@ -8315,10 +8315,10 @@
         <v>1.08</v>
       </c>
       <c r="I102" t="n">
-        <v>0.226</v>
+        <v>0.2277</v>
       </c>
       <c r="J102" t="n">
-        <v>5.876</v>
+        <v>5.9202</v>
       </c>
     </row>
     <row r="103">
@@ -8355,10 +8355,10 @@
         <v>0.96</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.057</v>
+        <v>-0.0678</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.482</v>
+        <v>-1.7628</v>
       </c>
     </row>
     <row r="104">
@@ -8395,10 +8395,10 @@
         <v>0.93</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.1064</v>
       </c>
       <c r="J104" t="n">
-        <v>-2.4258</v>
+        <v>-2.7664</v>
       </c>
     </row>
     <row r="105">
@@ -8435,10 +8435,10 @@
         <v>0.86</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1687</v>
+        <v>-0.1841</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.3862</v>
+        <v>-4.7866</v>
       </c>
     </row>
     <row r="106">
@@ -8475,10 +8475,10 @@
         <v>0.79</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2398</v>
+        <v>-0.2551</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.2348</v>
+        <v>-6.6326</v>
       </c>
     </row>
     <row r="107">
@@ -8515,10 +8515,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>1.3016</v>
+        <v>1.2736</v>
       </c>
       <c r="J107" t="n">
-        <v>33.8416</v>
+        <v>33.1136</v>
       </c>
     </row>
     <row r="108">
@@ -8555,10 +8555,10 @@
         <v>1.47</v>
       </c>
       <c r="I108" t="n">
-        <v>1.1097</v>
+        <v>1.0685</v>
       </c>
       <c r="J108" t="n">
-        <v>28.8522</v>
+        <v>27.781</v>
       </c>
     </row>
     <row r="109">
@@ -8595,10 +8595,10 @@
         <v>1.16</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4677</v>
+        <v>0.4602</v>
       </c>
       <c r="J109" t="n">
-        <v>12.1602</v>
+        <v>11.9652</v>
       </c>
     </row>
     <row r="110">
@@ -8635,10 +8635,10 @@
         <v>1.03</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0915</v>
+        <v>0.109</v>
       </c>
       <c r="J110" t="n">
-        <v>2.379</v>
+        <v>2.834</v>
       </c>
     </row>
     <row r="111">
@@ -8675,10 +8675,10 @@
         <v>0.58</v>
       </c>
       <c r="I111" t="n">
-        <v>-1.2022</v>
+        <v>-1.0859</v>
       </c>
       <c r="J111" t="n">
-        <v>-31.2572</v>
+        <v>-28.2334</v>
       </c>
     </row>
     <row r="112">
@@ -8715,10 +8715,10 @@
         <v>1.22</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4941</v>
+        <v>0.4814</v>
       </c>
       <c r="J112" t="n">
-        <v>14.3289</v>
+        <v>13.9606</v>
       </c>
     </row>
     <row r="113">
@@ -8755,10 +8755,10 @@
         <v>1.11</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2815</v>
+        <v>0.2827</v>
       </c>
       <c r="J113" t="n">
-        <v>8.163500000000001</v>
+        <v>8.1983</v>
       </c>
     </row>
     <row r="114">
@@ -8795,10 +8795,10 @@
         <v>0.88</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1503</v>
+        <v>-0.1648</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.3587</v>
+        <v>-4.7792</v>
       </c>
     </row>
     <row r="115">
@@ -8835,10 +8835,10 @@
         <v>0.78</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2527</v>
+        <v>-0.2672</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.3283</v>
+        <v>-7.7488</v>
       </c>
     </row>
     <row r="116">
@@ -8875,10 +8875,10 @@
         <v>0.75</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2821</v>
+        <v>-0.2961</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.180899999999999</v>
+        <v>-8.5869</v>
       </c>
     </row>
     <row r="117">
@@ -8915,10 +8915,10 @@
         <v>1.45</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0866</v>
+        <v>1.0419</v>
       </c>
       <c r="J117" t="n">
-        <v>31.5114</v>
+        <v>30.2151</v>
       </c>
     </row>
     <row r="118">
@@ -8955,10 +8955,10 @@
         <v>1.26</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7114</v>
+        <v>0.6784</v>
       </c>
       <c r="J118" t="n">
-        <v>20.6306</v>
+        <v>19.6736</v>
       </c>
     </row>
     <row r="119">
@@ -8995,10 +8995,10 @@
         <v>1.08</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2544</v>
+        <v>0.2633</v>
       </c>
       <c r="J119" t="n">
-        <v>7.3776</v>
+        <v>7.6357</v>
       </c>
     </row>
     <row r="120">
@@ -9035,10 +9035,10 @@
         <v>1.05</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1622</v>
+        <v>0.1763</v>
       </c>
       <c r="J120" t="n">
-        <v>4.7038</v>
+        <v>5.1127</v>
       </c>
     </row>
     <row r="121">
@@ -9075,10 +9075,10 @@
         <v>0.96</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2068</v>
+        <v>-0.1982</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.9972</v>
+        <v>-5.7478</v>
       </c>
     </row>
     <row r="122">
@@ -9115,10 +9115,10 @@
         <v>1.34</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7391</v>
+        <v>0.699</v>
       </c>
       <c r="J122" t="n">
-        <v>20.6948</v>
+        <v>19.572</v>
       </c>
     </row>
     <row r="123">
@@ -9155,10 +9155,10 @@
         <v>0.89</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.1341</v>
+        <v>-0.1497</v>
       </c>
       <c r="J123" t="n">
-        <v>-3.7548</v>
+        <v>-4.1916</v>
       </c>
     </row>
     <row r="124">
@@ -9195,10 +9195,10 @@
         <v>0.84</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1854</v>
+        <v>-0.2019</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.1912</v>
+        <v>-5.6532</v>
       </c>
     </row>
     <row r="125">
@@ -9235,10 +9235,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2157</v>
+        <v>-0.2321</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.0396</v>
+        <v>-6.4988</v>
       </c>
     </row>
     <row r="126">
@@ -9275,10 +9275,10 @@
         <v>0.57</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4444</v>
+        <v>-0.4537</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.4432</v>
+        <v>-12.7036</v>
       </c>
     </row>
     <row r="127">
@@ -9315,10 +9315,10 @@
         <v>1.41</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0254</v>
+        <v>0.9706</v>
       </c>
       <c r="J127" t="n">
-        <v>28.7112</v>
+        <v>27.1768</v>
       </c>
     </row>
     <row r="128">
@@ -9355,10 +9355,10 @@
         <v>1.34</v>
       </c>
       <c r="I128" t="n">
-        <v>0.89</v>
+        <v>0.8366</v>
       </c>
       <c r="J128" t="n">
-        <v>24.92</v>
+        <v>23.4248</v>
       </c>
     </row>
     <row r="129">
@@ -9395,10 +9395,10 @@
         <v>1.33</v>
       </c>
       <c r="I129" t="n">
-        <v>0.8672</v>
+        <v>0.8166</v>
       </c>
       <c r="J129" t="n">
-        <v>24.2816</v>
+        <v>22.8648</v>
       </c>
     </row>
     <row r="130">
@@ -9435,10 +9435,10 @@
         <v>1.16</v>
       </c>
       <c r="I130" t="n">
-        <v>0.4657</v>
+        <v>0.4589</v>
       </c>
       <c r="J130" t="n">
-        <v>13.0396</v>
+        <v>12.8492</v>
       </c>
     </row>
     <row r="131">
@@ -9475,10 +9475,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.9693000000000001</v>
+        <v>-0.8844</v>
       </c>
       <c r="J131" t="n">
-        <v>-27.1404</v>
+        <v>-24.7632</v>
       </c>
     </row>
     <row r="132">
@@ -9515,10 +9515,10 @@
         <v>1.24</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5579</v>
+        <v>0.5351</v>
       </c>
       <c r="J132" t="n">
-        <v>13.3896</v>
+        <v>12.8424</v>
       </c>
     </row>
     <row r="133">
@@ -9555,10 +9555,10 @@
         <v>0.97</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0388</v>
+        <v>-0.0496</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.9312</v>
+        <v>-1.1904</v>
       </c>
     </row>
     <row r="134">
@@ -9595,10 +9595,10 @@
         <v>0.88</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1442</v>
+        <v>-0.1601</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.4608</v>
+        <v>-3.8424</v>
       </c>
     </row>
     <row r="135">
@@ -9635,10 +9635,10 @@
         <v>0.84</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1852</v>
+        <v>-0.2017</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.4448</v>
+        <v>-4.8408</v>
       </c>
     </row>
     <row r="136">
@@ -9675,10 +9675,10 @@
         <v>0.51</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.499</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.976</v>
+        <v>-12.132</v>
       </c>
     </row>
     <row r="137">
@@ -9715,10 +9715,10 @@
         <v>2.2</v>
       </c>
       <c r="I137" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J137" t="n">
-        <v>44.0112</v>
+        <v>46.4928</v>
       </c>
     </row>
     <row r="138">
@@ -9755,10 +9755,10 @@
         <v>1.11</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3137</v>
+        <v>0.3244</v>
       </c>
       <c r="J138" t="n">
-        <v>7.5288</v>
+        <v>7.7856</v>
       </c>
     </row>
     <row r="139">
@@ -9795,10 +9795,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1017</v>
+        <v>0.1256</v>
       </c>
       <c r="J139" t="n">
-        <v>2.4408</v>
+        <v>3.0144</v>
       </c>
     </row>
     <row r="140">
@@ -9835,10 +9835,10 @@
         <v>1.01</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0113</v>
+        <v>0.0139</v>
       </c>
       <c r="J140" t="n">
-        <v>-0.2712</v>
+        <v>0.3336</v>
       </c>
     </row>
     <row r="141">
@@ -9875,10 +9875,10 @@
         <v>1</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.0459</v>
       </c>
       <c r="J141" t="n">
-        <v>-1.5888</v>
+        <v>-1.1016</v>
       </c>
     </row>
     <row r="142">
@@ -9915,10 +9915,10 @@
         <v>1.4</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9966</v>
+        <v>0.9413</v>
       </c>
       <c r="J142" t="n">
-        <v>25.9116</v>
+        <v>24.4738</v>
       </c>
     </row>
     <row r="143">
@@ -9955,10 +9955,10 @@
         <v>1.33</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8526</v>
+        <v>0.8065</v>
       </c>
       <c r="J143" t="n">
-        <v>22.1676</v>
+        <v>20.969</v>
       </c>
     </row>
     <row r="144">
@@ -9995,10 +9995,10 @@
         <v>1.24</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6481</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>16.8506</v>
+        <v>16.263</v>
       </c>
     </row>
     <row r="145">
@@ -10035,10 +10035,10 @@
         <v>1.17</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4809</v>
+        <v>0.4749</v>
       </c>
       <c r="J145" t="n">
-        <v>12.5034</v>
+        <v>12.3474</v>
       </c>
     </row>
     <row r="146">
@@ -10075,10 +10075,10 @@
         <v>1.03</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0761</v>
+        <v>0.0983</v>
       </c>
       <c r="J146" t="n">
-        <v>1.9786</v>
+        <v>2.5558</v>
       </c>
     </row>
     <row r="147">
@@ -10115,10 +10115,10 @@
         <v>1.19</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4551</v>
+        <v>0.4422</v>
       </c>
       <c r="J147" t="n">
-        <v>11.8326</v>
+        <v>11.4972</v>
       </c>
     </row>
     <row r="148">
@@ -10155,10 +10155,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0799</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.0774</v>
+        <v>-2.4128</v>
       </c>
     </row>
     <row r="149">
@@ -10195,10 +10195,10 @@
         <v>0.83</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1974</v>
+        <v>-0.2135</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.1324</v>
+        <v>-5.551</v>
       </c>
     </row>
     <row r="150">
@@ -10235,10 +10235,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2176</v>
+        <v>-0.2336</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.6576</v>
+        <v>-6.0736</v>
       </c>
     </row>
     <row r="151">
@@ -10275,10 +10275,10 @@
         <v>0.76</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2671</v>
+        <v>-0.2824</v>
       </c>
       <c r="J151" t="n">
-        <v>-6.9446</v>
+        <v>-7.3424</v>
       </c>
     </row>
     <row r="152">
@@ -10315,10 +10315,10 @@
         <v>1.75</v>
       </c>
       <c r="I152" t="n">
-        <v>1.3944</v>
+        <v>1.3832</v>
       </c>
       <c r="J152" t="n">
-        <v>29.2824</v>
+        <v>29.0472</v>
       </c>
     </row>
     <row r="153">
@@ -10355,10 +10355,10 @@
         <v>1.65</v>
       </c>
       <c r="I153" t="n">
-        <v>1.2779</v>
+        <v>1.2593</v>
       </c>
       <c r="J153" t="n">
-        <v>26.8359</v>
+        <v>26.4453</v>
       </c>
     </row>
     <row r="154">
@@ -10395,10 +10395,10 @@
         <v>1.45</v>
       </c>
       <c r="I154" t="n">
-        <v>1.0391</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="J154" t="n">
-        <v>21.8211</v>
+        <v>20.9265</v>
       </c>
     </row>
     <row r="155">
@@ -10435,10 +10435,10 @@
         <v>1.22</v>
       </c>
       <c r="I155" t="n">
-        <v>0.5623</v>
+        <v>0.5567</v>
       </c>
       <c r="J155" t="n">
-        <v>11.8083</v>
+        <v>11.6907</v>
       </c>
     </row>
     <row r="156">
@@ -10475,10 +10475,10 @@
         <v>1.09</v>
       </c>
       <c r="I156" t="n">
-        <v>0.2212</v>
+        <v>0.2469</v>
       </c>
       <c r="J156" t="n">
-        <v>4.6452</v>
+        <v>5.1849</v>
       </c>
     </row>
     <row r="157">
@@ -10515,10 +10515,10 @@
         <v>0.99</v>
       </c>
       <c r="I157" t="n">
-        <v>0.0333</v>
+        <v>0.0083</v>
       </c>
       <c r="J157" t="n">
-        <v>0.6993</v>
+        <v>0.1743</v>
       </c>
     </row>
     <row r="158">
@@ -10555,10 +10555,10 @@
         <v>0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0138</v>
+        <v>-0.0301</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.2898</v>
+        <v>-0.6321</v>
       </c>
     </row>
     <row r="159">
@@ -10595,10 +10595,10 @@
         <v>0.93</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0677</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.4217</v>
+        <v>-1.8165</v>
       </c>
     </row>
     <row r="160">
@@ -10635,10 +10635,10 @@
         <v>0.48</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.511</v>
+        <v>-0.519</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.731</v>
+        <v>-10.899</v>
       </c>
     </row>
     <row r="161">
@@ -10675,10 +10675,10 @@
         <v>0.45</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5387</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.3127</v>
+        <v>-11.4429</v>
       </c>
     </row>
     <row r="162">
@@ -10715,10 +10715,10 @@
         <v>1.62</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2893</v>
+        <v>1.2627</v>
       </c>
       <c r="J162" t="n">
-        <v>32.2325</v>
+        <v>31.5675</v>
       </c>
     </row>
     <row r="163">
@@ -10755,10 +10755,10 @@
         <v>1.21</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5819</v>
+        <v>0.5653</v>
       </c>
       <c r="J163" t="n">
-        <v>14.5475</v>
+        <v>14.1325</v>
       </c>
     </row>
     <row r="164">
@@ -10795,10 +10795,10 @@
         <v>1.14</v>
       </c>
       <c r="I164" t="n">
-        <v>0.4081</v>
+        <v>0.4078</v>
       </c>
       <c r="J164" t="n">
-        <v>10.2025</v>
+        <v>10.195</v>
       </c>
     </row>
     <row r="165">
@@ -10835,10 +10835,10 @@
         <v>1.06</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1807</v>
+        <v>0.1973</v>
       </c>
       <c r="J165" t="n">
-        <v>4.5175</v>
+        <v>4.9325</v>
       </c>
     </row>
     <row r="166">
@@ -10875,10 +10875,10 @@
         <v>1.04</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1158</v>
+        <v>0.1354</v>
       </c>
       <c r="J166" t="n">
-        <v>2.895</v>
+        <v>3.385</v>
       </c>
     </row>
     <row r="167">
@@ -10915,10 +10915,10 @@
         <v>1.21</v>
       </c>
       <c r="I167" t="n">
-        <v>0.482</v>
+        <v>0.469</v>
       </c>
       <c r="J167" t="n">
-        <v>12.05</v>
+        <v>11.725</v>
       </c>
     </row>
     <row r="168">
@@ -10955,10 +10955,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0303</v>
+        <v>-0.0384</v>
       </c>
       <c r="J168" t="n">
-        <v>-0.7575</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="169">
@@ -10995,10 +10995,10 @@
         <v>0.86</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1696</v>
+        <v>-0.1848</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.24</v>
+        <v>-4.62</v>
       </c>
     </row>
     <row r="170">
@@ -11035,10 +11035,10 @@
         <v>0.82</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2107</v>
+        <v>-0.2261</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.2675</v>
+        <v>-5.6525</v>
       </c>
     </row>
     <row r="171">
@@ -11075,10 +11075,10 @@
         <v>0.79</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2408</v>
+        <v>-0.2559</v>
       </c>
       <c r="J171" t="n">
-        <v>-6.02</v>
+        <v>-6.3975</v>
       </c>
     </row>
     <row r="172">
@@ -11115,10 +11115,10 @@
         <v>1.28</v>
       </c>
       <c r="I172" t="n">
-        <v>0.7741</v>
+        <v>0.7308</v>
       </c>
       <c r="J172" t="n">
-        <v>23.223</v>
+        <v>21.924</v>
       </c>
     </row>
     <row r="173">
@@ -11155,10 +11155,10 @@
         <v>1.27</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7501</v>
+        <v>0.7098</v>
       </c>
       <c r="J173" t="n">
-        <v>22.503</v>
+        <v>21.294</v>
       </c>
     </row>
     <row r="174">
@@ -11195,10 +11195,10 @@
         <v>1.21</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6037</v>
+        <v>0.5802</v>
       </c>
       <c r="J174" t="n">
-        <v>18.111</v>
+        <v>17.406</v>
       </c>
     </row>
     <row r="175">
@@ -11235,10 +11235,10 @@
         <v>1.05</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1734</v>
+        <v>0.1841</v>
       </c>
       <c r="J175" t="n">
-        <v>5.202</v>
+        <v>5.523</v>
       </c>
     </row>
     <row r="176">
@@ -11275,10 +11275,10 @@
         <v>0.76</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7557</v>
+        <v>-0.7005</v>
       </c>
       <c r="J176" t="n">
-        <v>-22.671</v>
+        <v>-21.015</v>
       </c>
     </row>
     <row r="177">
@@ -11315,10 +11315,10 @@
         <v>1.34</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6745</v>
+        <v>0.6513</v>
       </c>
       <c r="J177" t="n">
-        <v>20.235</v>
+        <v>19.539</v>
       </c>
     </row>
     <row r="178">
@@ -11355,10 +11355,10 @@
         <v>1.22</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4657</v>
+        <v>0.4605</v>
       </c>
       <c r="J178" t="n">
-        <v>13.971</v>
+        <v>13.815</v>
       </c>
     </row>
     <row r="179">
@@ -11395,10 +11395,10 @@
         <v>1.03</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0877</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>2.631</v>
+        <v>2.913</v>
       </c>
     </row>
     <row r="180">
@@ -11435,10 +11435,10 @@
         <v>0.86</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1809</v>
+        <v>-0.1936</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.427</v>
+        <v>-5.808</v>
       </c>
     </row>
     <row r="181">
@@ -11475,10 +11475,10 @@
         <v>0.7</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3395</v>
+        <v>-0.3503</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.185</v>
+        <v>-10.509</v>
       </c>
     </row>
     <row r="182">
@@ -11515,10 +11515,10 @@
         <v>1.52</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1393</v>
+        <v>1.1073</v>
       </c>
       <c r="J182" t="n">
-        <v>23.9253</v>
+        <v>23.2533</v>
       </c>
     </row>
     <row r="183">
@@ -11555,10 +11555,10 @@
         <v>1.43</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0246</v>
+        <v>0.9765</v>
       </c>
       <c r="J183" t="n">
-        <v>21.5166</v>
+        <v>20.5065</v>
       </c>
     </row>
     <row r="184">
@@ -11595,10 +11595,10 @@
         <v>1.27</v>
       </c>
       <c r="I184" t="n">
-        <v>0.7013</v>
+        <v>0.6763</v>
       </c>
       <c r="J184" t="n">
-        <v>14.7273</v>
+        <v>14.2023</v>
       </c>
     </row>
     <row r="185">
@@ -11635,10 +11635,10 @@
         <v>1.23</v>
       </c>
       <c r="I185" t="n">
-        <v>0.6078</v>
+        <v>0.5931</v>
       </c>
       <c r="J185" t="n">
-        <v>12.7638</v>
+        <v>12.4551</v>
       </c>
     </row>
     <row r="186">
@@ -11675,10 +11675,10 @@
         <v>1.2</v>
       </c>
       <c r="I186" t="n">
-        <v>0.5351</v>
+        <v>0.5281</v>
       </c>
       <c r="J186" t="n">
-        <v>11.2371</v>
+        <v>11.0901</v>
       </c>
     </row>
     <row r="187">
@@ -11715,10 +11715,10 @@
         <v>1</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0801</v>
+        <v>0.0584</v>
       </c>
       <c r="J187" t="n">
-        <v>1.6821</v>
+        <v>1.2264</v>
       </c>
     </row>
     <row r="188">
@@ -11755,10 +11755,10 @@
         <v>0.91</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.1095</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.8774</v>
+        <v>-2.2995</v>
       </c>
     </row>
     <row r="189">
@@ -11795,10 +11795,10 @@
         <v>0.72</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.285</v>
+        <v>-0.3041</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.985</v>
+        <v>-6.3861</v>
       </c>
     </row>
     <row r="190">
@@ -11835,10 +11835,10 @@
         <v>0.6</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3975</v>
+        <v>-0.4123</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.3475</v>
+        <v>-8.658300000000001</v>
       </c>
     </row>
     <row r="191">
@@ -11875,10 +11875,10 @@
         <v>0.53</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4629</v>
+        <v>-0.4741</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.7209</v>
+        <v>-9.956099999999999</v>
       </c>
     </row>
     <row r="192">
@@ -11915,10 +11915,10 @@
         <v>1.18</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3122</v>
+        <v>0.3164</v>
       </c>
       <c r="J192" t="n">
-        <v>7.805</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="193">
@@ -11955,10 +11955,10 @@
         <v>1.15</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2685</v>
+        <v>0.2746</v>
       </c>
       <c r="J193" t="n">
-        <v>6.7125</v>
+        <v>6.865</v>
       </c>
     </row>
     <row r="194">
@@ -11995,10 +11995,10 @@
         <v>1.14</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2537</v>
+        <v>0.2603</v>
       </c>
       <c r="J194" t="n">
-        <v>6.3425</v>
+        <v>6.5075</v>
       </c>
     </row>
     <row r="195">
@@ -12035,10 +12035,10 @@
         <v>0.82</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2165</v>
+        <v>-0.2306</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.4125</v>
+        <v>-5.765</v>
       </c>
     </row>
     <row r="196">
@@ -12075,10 +12075,10 @@
         <v>0.61</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.418</v>
+        <v>-0.4268</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.45</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="197">
@@ -12115,10 +12115,10 @@
         <v>1.42</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5566</v>
+        <v>0.5587</v>
       </c>
       <c r="J197" t="n">
-        <v>13.915</v>
+        <v>13.9675</v>
       </c>
     </row>
     <row r="198">
@@ -12155,10 +12155,10 @@
         <v>1.17</v>
       </c>
       <c r="I198" t="n">
-        <v>0.255</v>
+        <v>0.2703</v>
       </c>
       <c r="J198" t="n">
-        <v>6.375</v>
+        <v>6.7575</v>
       </c>
     </row>
     <row r="199">
@@ -12195,10 +12195,10 @@
         <v>1.14</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2159</v>
+        <v>0.2317</v>
       </c>
       <c r="J199" t="n">
-        <v>5.3975</v>
+        <v>5.7925</v>
       </c>
     </row>
     <row r="200">
@@ -12235,10 +12235,10 @@
         <v>1.05</v>
       </c>
       <c r="I200" t="n">
-        <v>0.0888</v>
+        <v>0.1022</v>
       </c>
       <c r="J200" t="n">
-        <v>2.22</v>
+        <v>2.555</v>
       </c>
     </row>
     <row r="201">
@@ -12275,10 +12275,10 @@
         <v>0.72</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3278</v>
+        <v>-0.3375</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.195</v>
+        <v>-8.4375</v>
       </c>
     </row>
     <row r="202">
@@ -12315,10 +12315,10 @@
         <v>1.37</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.9034</v>
       </c>
       <c r="J202" t="n">
-        <v>26.9976</v>
+        <v>25.2952</v>
       </c>
     </row>
     <row r="203">
@@ -12355,10 +12355,10 @@
         <v>1.29</v>
       </c>
       <c r="I203" t="n">
-        <v>0.784</v>
+        <v>0.7421</v>
       </c>
       <c r="J203" t="n">
-        <v>21.952</v>
+        <v>20.7788</v>
       </c>
     </row>
     <row r="204">
@@ -12395,10 +12395,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3942</v>
+        <v>0.3923</v>
       </c>
       <c r="J204" t="n">
-        <v>11.0376</v>
+        <v>10.9844</v>
       </c>
     </row>
     <row r="205">
@@ -12435,10 +12435,10 @@
         <v>1.04</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1307</v>
+        <v>0.1458</v>
       </c>
       <c r="J205" t="n">
-        <v>3.6596</v>
+        <v>4.0824</v>
       </c>
     </row>
     <row r="206">
@@ -12475,10 +12475,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2708</v>
+        <v>-0.2595</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.5824</v>
+        <v>-7.266</v>
       </c>
     </row>
     <row r="207">
@@ -12515,10 +12515,10 @@
         <v>1.14</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3671</v>
+        <v>0.3583</v>
       </c>
       <c r="J207" t="n">
-        <v>10.2788</v>
+        <v>10.0324</v>
       </c>
     </row>
     <row r="208">
@@ -12555,10 +12555,10 @@
         <v>1.02</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0953</v>
+        <v>0.0945</v>
       </c>
       <c r="J208" t="n">
-        <v>2.6684</v>
+        <v>2.646</v>
       </c>
     </row>
     <row r="209">
@@ -12595,10 +12595,10 @@
         <v>0.92</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1006</v>
+        <v>-0.1152</v>
       </c>
       <c r="J209" t="n">
-        <v>-2.8168</v>
+        <v>-3.2256</v>
       </c>
     </row>
     <row r="210">
@@ -12635,10 +12635,10 @@
         <v>0.7</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3218</v>
+        <v>-0.3364</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.010400000000001</v>
+        <v>-9.4192</v>
       </c>
     </row>
     <row r="211">
@@ -12675,10 +12675,10 @@
         <v>0.63</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3879</v>
+        <v>-0.3999</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.8612</v>
+        <v>-11.1972</v>
       </c>
     </row>
     <row r="212">
@@ -12715,10 +12715,10 @@
         <v>1.64</v>
       </c>
       <c r="I212" t="n">
-        <v>1.3159</v>
+        <v>1.2906</v>
       </c>
       <c r="J212" t="n">
-        <v>46.0565</v>
+        <v>45.171</v>
       </c>
     </row>
     <row r="213">
@@ -12755,10 +12755,10 @@
         <v>1.41</v>
       </c>
       <c r="I213" t="n">
-        <v>1.0194</v>
+        <v>0.965</v>
       </c>
       <c r="J213" t="n">
-        <v>35.679</v>
+        <v>33.775</v>
       </c>
     </row>
     <row r="214">
@@ -12795,10 +12795,10 @@
         <v>1.11</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3286</v>
+        <v>0.3347</v>
       </c>
       <c r="J214" t="n">
-        <v>11.501</v>
+        <v>11.7145</v>
       </c>
     </row>
     <row r="215">
@@ -12835,10 +12835,10 @@
         <v>1</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0506</v>
+        <v>-0.035</v>
       </c>
       <c r="J215" t="n">
-        <v>-1.771</v>
+        <v>-1.225</v>
       </c>
     </row>
     <row r="216">
@@ -12875,10 +12875,10 @@
         <v>0.88</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4625</v>
+        <v>-0.4337</v>
       </c>
       <c r="J216" t="n">
-        <v>-16.1875</v>
+        <v>-15.1795</v>
       </c>
     </row>
     <row r="217">
@@ -12915,10 +12915,10 @@
         <v>1.11</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3045</v>
+        <v>0.2996</v>
       </c>
       <c r="J217" t="n">
-        <v>10.6575</v>
+        <v>10.486</v>
       </c>
     </row>
     <row r="218">
@@ -12955,10 +12955,10 @@
         <v>1.01</v>
       </c>
       <c r="I218" t="n">
-        <v>0.0649</v>
+        <v>0.063</v>
       </c>
       <c r="J218" t="n">
-        <v>2.2715</v>
+        <v>2.205</v>
       </c>
     </row>
     <row r="219">
@@ -12995,10 +12995,10 @@
         <v>0.85</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1746</v>
+        <v>-0.1911</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.111</v>
+        <v>-6.6885</v>
       </c>
     </row>
     <row r="220">
@@ -13035,10 +13035,10 @@
         <v>0.82</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2049</v>
+        <v>-0.2216</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.1715</v>
+        <v>-7.756</v>
       </c>
     </row>
     <row r="221">
@@ -13075,10 +13075,10 @@
         <v>0.63</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3881</v>
+        <v>-0.4001</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.5835</v>
+        <v>-14.0035</v>
       </c>
     </row>
     <row r="222">
@@ -13115,10 +13115,10 @@
         <v>2.08</v>
       </c>
       <c r="I222" t="n">
-        <v>1.8133</v>
+        <v>1.8156</v>
       </c>
       <c r="J222" t="n">
-        <v>43.5192</v>
+        <v>43.5744</v>
       </c>
     </row>
     <row r="223">
@@ -13155,10 +13155,10 @@
         <v>1.33</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8394</v>
+        <v>0.7974</v>
       </c>
       <c r="J223" t="n">
-        <v>20.1456</v>
+        <v>19.1376</v>
       </c>
     </row>
     <row r="224">
@@ -13195,10 +13195,10 @@
         <v>1.12</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3366</v>
+        <v>0.3465</v>
       </c>
       <c r="J224" t="n">
-        <v>8.0784</v>
+        <v>8.316000000000001</v>
       </c>
     </row>
     <row r="225">
@@ -13235,10 +13235,10 @@
         <v>0.97</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2043</v>
+        <v>-0.1871</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.9032</v>
+        <v>-4.4904</v>
       </c>
     </row>
     <row r="226">
@@ -13275,10 +13275,10 @@
         <v>0.96</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2393</v>
+        <v>-0.221</v>
       </c>
       <c r="J226" t="n">
-        <v>-5.7432</v>
+        <v>-5.304</v>
       </c>
     </row>
     <row r="227">
@@ -13315,10 +13315,10 @@
         <v>0.98</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.0106</v>
+        <v>-0.0231</v>
       </c>
       <c r="J227" t="n">
-        <v>-0.2544</v>
+        <v>-0.5544</v>
       </c>
     </row>
     <row r="228">
@@ -13355,10 +13355,10 @@
         <v>0.84</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1782</v>
+        <v>-0.1964</v>
       </c>
       <c r="J228" t="n">
-        <v>-4.2768</v>
+        <v>-4.7136</v>
       </c>
     </row>
     <row r="229">
@@ -13395,10 +13395,10 @@
         <v>0.83</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1881</v>
+        <v>-0.2064</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.5144</v>
+        <v>-4.9536</v>
       </c>
     </row>
     <row r="230">
@@ -13435,10 +13435,10 @@
         <v>0.78</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2359</v>
+        <v>-0.2542</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.6616</v>
+        <v>-6.1008</v>
       </c>
     </row>
     <row r="231">
@@ -13475,10 +13475,10 @@
         <v>0.64</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3693</v>
+        <v>-0.3837</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.863200000000001</v>
+        <v>-9.2088</v>
       </c>
     </row>
     <row r="232">
@@ -13515,10 +13515,10 @@
         <v>1.62</v>
       </c>
       <c r="I232" t="n">
-        <v>1.3124</v>
+        <v>1.2832</v>
       </c>
       <c r="J232" t="n">
-        <v>39.372</v>
+        <v>38.496</v>
       </c>
     </row>
     <row r="233">
@@ -13555,10 +13555,10 @@
         <v>1.29</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7894</v>
+        <v>0.7458</v>
       </c>
       <c r="J233" t="n">
-        <v>23.682</v>
+        <v>22.374</v>
       </c>
     </row>
     <row r="234">
@@ -13595,10 +13595,10 @@
         <v>1.05</v>
       </c>
       <c r="I234" t="n">
-        <v>0.1676</v>
+        <v>0.1801</v>
       </c>
       <c r="J234" t="n">
-        <v>5.028</v>
+        <v>5.403</v>
       </c>
     </row>
     <row r="235">
@@ -13635,10 +13635,10 @@
         <v>0.99</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0876</v>
+        <v>-0.0823</v>
       </c>
       <c r="J235" t="n">
-        <v>-2.628</v>
+        <v>-2.469</v>
       </c>
     </row>
     <row r="236">
@@ -13675,10 +13675,10 @@
         <v>0.74</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.8119</v>
+        <v>-0.7488</v>
       </c>
       <c r="J236" t="n">
-        <v>-24.357</v>
+        <v>-22.464</v>
       </c>
     </row>
     <row r="237">
@@ -13715,10 +13715,10 @@
         <v>1.31</v>
       </c>
       <c r="I237" t="n">
-        <v>0.6069</v>
+        <v>0.5928</v>
       </c>
       <c r="J237" t="n">
-        <v>18.207</v>
+        <v>17.784</v>
       </c>
     </row>
     <row r="238">
@@ -13755,10 +13755,10 @@
         <v>1.19</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3985</v>
+        <v>0.4007</v>
       </c>
       <c r="J238" t="n">
-        <v>11.955</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="239">
@@ -13795,10 +13795,10 @@
         <v>1.16</v>
       </c>
       <c r="I239" t="n">
-        <v>0.344</v>
+        <v>0.3495</v>
       </c>
       <c r="J239" t="n">
-        <v>10.32</v>
+        <v>10.485</v>
       </c>
     </row>
     <row r="240">
@@ -13835,10 +13835,10 @@
         <v>0.91</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1318</v>
+        <v>-0.1422</v>
       </c>
       <c r="J240" t="n">
-        <v>-3.954</v>
+        <v>-4.266</v>
       </c>
     </row>
     <row r="241">
@@ -13875,10 +13875,10 @@
         <v>0.83</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2176</v>
+        <v>-0.2292</v>
       </c>
       <c r="J241" t="n">
-        <v>-6.528</v>
+        <v>-6.876</v>
       </c>
     </row>
     <row r="242">
@@ -13915,10 +13915,10 @@
         <v>0.87</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.1394</v>
+        <v>-0.1591</v>
       </c>
       <c r="J242" t="n">
-        <v>-3.2062</v>
+        <v>-3.6593</v>
       </c>
     </row>
     <row r="243">
@@ -13955,10 +13955,10 @@
         <v>0.82</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1925</v>
+        <v>-0.2121</v>
       </c>
       <c r="J243" t="n">
-        <v>-4.4275</v>
+        <v>-4.8783</v>
       </c>
     </row>
     <row r="244">
@@ -13995,10 +13995,10 @@
         <v>0.78</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2317</v>
+        <v>-0.2511</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.3291</v>
+        <v>-5.7753</v>
       </c>
     </row>
     <row r="245">
@@ -14035,10 +14035,10 @@
         <v>0.73</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.278</v>
+        <v>-0.2967</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.394</v>
+        <v>-6.8241</v>
       </c>
     </row>
     <row r="246">
@@ -14075,10 +14075,10 @@
         <v>0.65</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3534</v>
+        <v>-0.3697</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.1282</v>
+        <v>-8.5031</v>
       </c>
     </row>
     <row r="247">
@@ -14115,10 +14115,10 @@
         <v>1.53</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6332</v>
+        <v>0.6379</v>
       </c>
       <c r="J247" t="n">
-        <v>14.5636</v>
+        <v>14.6717</v>
       </c>
     </row>
     <row r="248">
@@ -14155,10 +14155,10 @@
         <v>1.5</v>
       </c>
       <c r="I248" t="n">
-        <v>0.6016</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="J248" t="n">
-        <v>13.8368</v>
+        <v>13.9932</v>
       </c>
     </row>
     <row r="249">
@@ -14195,10 +14195,10 @@
         <v>1.31</v>
       </c>
       <c r="I249" t="n">
-        <v>0.3982</v>
+        <v>0.4149</v>
       </c>
       <c r="J249" t="n">
-        <v>9.1586</v>
+        <v>9.5427</v>
       </c>
     </row>
     <row r="250">
@@ -14235,10 +14235,10 @@
         <v>1.17</v>
       </c>
       <c r="I250" t="n">
-        <v>0.232</v>
+        <v>0.2531</v>
       </c>
       <c r="J250" t="n">
-        <v>5.336</v>
+        <v>5.8213</v>
       </c>
     </row>
     <row r="251">
@@ -14275,10 +14275,10 @@
         <v>1.11</v>
       </c>
       <c r="I251" t="n">
-        <v>0.1517</v>
+        <v>0.1734</v>
       </c>
       <c r="J251" t="n">
-        <v>3.4891</v>
+        <v>3.9882</v>
       </c>
     </row>
     <row r="252">
@@ -14315,10 +14315,10 @@
         <v>1.26</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7347</v>
+        <v>0.6946</v>
       </c>
       <c r="J252" t="n">
-        <v>20.5716</v>
+        <v>19.4488</v>
       </c>
     </row>
     <row r="253">
@@ -14355,10 +14355,10 @@
         <v>1.15</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4581</v>
+        <v>0.4478</v>
       </c>
       <c r="J253" t="n">
-        <v>12.8268</v>
+        <v>12.5384</v>
       </c>
     </row>
     <row r="254">
@@ -14395,10 +14395,10 @@
         <v>1.07</v>
       </c>
       <c r="I254" t="n">
-        <v>0.2402</v>
+        <v>0.2461</v>
       </c>
       <c r="J254" t="n">
-        <v>6.7256</v>
+        <v>6.8908</v>
       </c>
     </row>
     <row r="255">
@@ -14435,10 +14435,10 @@
         <v>1</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0203</v>
+        <v>-0.0139</v>
       </c>
       <c r="J255" t="n">
-        <v>-0.5684</v>
+        <v>-0.3892</v>
       </c>
     </row>
     <row r="256">
@@ -14475,10 +14475,10 @@
         <v>0.97</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1532</v>
+        <v>-0.1515</v>
       </c>
       <c r="J256" t="n">
-        <v>-4.2896</v>
+        <v>-4.242</v>
       </c>
     </row>
     <row r="257">
@@ -14515,10 +14515,10 @@
         <v>1.33</v>
       </c>
       <c r="I257" t="n">
-        <v>0.6714</v>
+        <v>0.6462</v>
       </c>
       <c r="J257" t="n">
-        <v>18.7992</v>
+        <v>18.0936</v>
       </c>
     </row>
     <row r="258">
@@ -14555,10 +14555,10 @@
         <v>1.08</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2063</v>
+        <v>0.2134</v>
       </c>
       <c r="J258" t="n">
-        <v>5.7764</v>
+        <v>5.9752</v>
       </c>
     </row>
     <row r="259">
@@ -14595,10 +14595,10 @@
         <v>0.99</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.0202</v>
+        <v>-0.0249</v>
       </c>
       <c r="J259" t="n">
-        <v>-0.5656</v>
+        <v>-0.6972</v>
       </c>
     </row>
     <row r="260">
@@ -14635,10 +14635,10 @@
         <v>0.97</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.0495</v>
+        <v>-0.0578</v>
       </c>
       <c r="J260" t="n">
-        <v>-1.386</v>
+        <v>-1.6184</v>
       </c>
     </row>
     <row r="261">
@@ -14675,10 +14675,10 @@
         <v>0.6</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4286</v>
+        <v>-0.4367</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.0008</v>
+        <v>-12.2276</v>
       </c>
     </row>
     <row r="262">
@@ -14715,10 +14715,10 @@
         <v>1.42</v>
       </c>
       <c r="I262" t="n">
-        <v>1.0359</v>
+        <v>0.9837</v>
       </c>
       <c r="J262" t="n">
-        <v>25.8975</v>
+        <v>24.5925</v>
       </c>
     </row>
     <row r="263">
@@ -14755,10 +14755,10 @@
         <v>1.33</v>
       </c>
       <c r="I263" t="n">
-        <v>0.8616</v>
+        <v>0.8127</v>
       </c>
       <c r="J263" t="n">
-        <v>21.54</v>
+        <v>20.3175</v>
       </c>
     </row>
     <row r="264">
@@ -14795,10 +14795,10 @@
         <v>1.22</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6067</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="J264" t="n">
-        <v>15.1675</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="265">
@@ -14835,10 +14835,10 @@
         <v>1.06</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1836</v>
+        <v>0.1993</v>
       </c>
       <c r="J265" t="n">
-        <v>4.59</v>
+        <v>4.9825</v>
       </c>
     </row>
     <row r="266">
@@ -14875,10 +14875,10 @@
         <v>0.98</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.1452</v>
+        <v>-0.1352</v>
       </c>
       <c r="J266" t="n">
-        <v>-3.63</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="267">
@@ -14915,10 +14915,10 @@
         <v>1.16</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4054</v>
+        <v>0.3944</v>
       </c>
       <c r="J267" t="n">
-        <v>10.135</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="268">
@@ -14955,10 +14955,10 @@
         <v>0.9</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1233</v>
+        <v>-0.1386</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.0825</v>
+        <v>-3.465</v>
       </c>
     </row>
     <row r="269">
@@ -14995,10 +14995,10 @@
         <v>0.86</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1646</v>
+        <v>-0.181</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.115</v>
+        <v>-4.525</v>
       </c>
     </row>
     <row r="270">
@@ -15035,10 +15035,10 @@
         <v>0.82</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2051</v>
+        <v>-0.2217</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.1275</v>
+        <v>-5.5425</v>
       </c>
     </row>
     <row r="271">
@@ -15075,10 +15075,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3319</v>
+        <v>-0.346</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.297499999999999</v>
+        <v>-8.65</v>
       </c>
     </row>
     <row r="272">
@@ -15115,10 +15115,10 @@
         <v>1.16</v>
       </c>
       <c r="I272" t="n">
-        <v>0.3646</v>
+        <v>0.3645</v>
       </c>
       <c r="J272" t="n">
-        <v>9.115</v>
+        <v>9.112500000000001</v>
       </c>
     </row>
     <row r="273">
@@ -15155,10 +15155,10 @@
         <v>1.08</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2054</v>
+        <v>0.2127</v>
       </c>
       <c r="J273" t="n">
-        <v>5.135</v>
+        <v>5.3175</v>
       </c>
     </row>
     <row r="274">
@@ -15195,10 +15195,10 @@
         <v>1.01</v>
       </c>
       <c r="I274" t="n">
-        <v>0.038</v>
+        <v>0.0435</v>
       </c>
       <c r="J274" t="n">
-        <v>0.95</v>
+        <v>1.0875</v>
       </c>
     </row>
     <row r="275">
@@ -15235,10 +15235,10 @@
         <v>0.91</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1228</v>
+        <v>-0.1353</v>
       </c>
       <c r="J275" t="n">
-        <v>-3.07</v>
+        <v>-3.3825</v>
       </c>
     </row>
     <row r="276">
@@ -15275,10 +15275,10 @@
         <v>0.83</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2084</v>
+        <v>-0.222</v>
       </c>
       <c r="J276" t="n">
-        <v>-5.21</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="277">
@@ -15315,10 +15315,10 @@
         <v>1.2</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5837</v>
+        <v>0.5613</v>
       </c>
       <c r="J277" t="n">
-        <v>14.5925</v>
+        <v>14.0325</v>
       </c>
     </row>
     <row r="278">
@@ -15355,10 +15355,10 @@
         <v>1.18</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5332</v>
+        <v>0.5161</v>
       </c>
       <c r="J278" t="n">
-        <v>13.33</v>
+        <v>12.9025</v>
       </c>
     </row>
     <row r="279">
@@ -15395,10 +15395,10 @@
         <v>1.17</v>
       </c>
       <c r="I279" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.4931</v>
       </c>
       <c r="J279" t="n">
-        <v>12.69</v>
+        <v>12.3275</v>
       </c>
     </row>
     <row r="280">
@@ -15435,10 +15435,10 @@
         <v>1.13</v>
       </c>
       <c r="I280" t="n">
-        <v>0.4035</v>
+        <v>0.3985</v>
       </c>
       <c r="J280" t="n">
-        <v>10.0875</v>
+        <v>9.9625</v>
       </c>
     </row>
     <row r="281">
@@ -15475,10 +15475,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6232</v>
+        <v>-0.584</v>
       </c>
       <c r="J281" t="n">
-        <v>-15.58</v>
+        <v>-14.6</v>
       </c>
     </row>
     <row r="282">
@@ -15515,10 +15515,10 @@
         <v>1.64</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3385</v>
+        <v>1.3107</v>
       </c>
       <c r="J282" t="n">
-        <v>45.509</v>
+        <v>44.5638</v>
       </c>
     </row>
     <row r="283">
@@ -15555,10 +15555,10 @@
         <v>1.2</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5728</v>
+        <v>0.5538</v>
       </c>
       <c r="J283" t="n">
-        <v>19.4752</v>
+        <v>18.8292</v>
       </c>
     </row>
     <row r="284">
@@ -15595,10 +15595,10 @@
         <v>1.04</v>
       </c>
       <c r="I284" t="n">
-        <v>0.1351</v>
+        <v>0.1489</v>
       </c>
       <c r="J284" t="n">
-        <v>4.5934</v>
+        <v>5.0626</v>
       </c>
     </row>
     <row r="285">
@@ -15635,10 +15635,10 @@
         <v>0.91</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3577</v>
+        <v>-0.3416</v>
       </c>
       <c r="J285" t="n">
-        <v>-12.1618</v>
+        <v>-11.6144</v>
       </c>
     </row>
     <row r="286">
@@ -15675,10 +15675,10 @@
         <v>0.89</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4158</v>
+        <v>-0.3949</v>
       </c>
       <c r="J286" t="n">
-        <v>-14.1372</v>
+        <v>-13.4266</v>
       </c>
     </row>
     <row r="287">
@@ -15715,10 +15715,10 @@
         <v>1.13</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3274</v>
+        <v>0.3251</v>
       </c>
       <c r="J287" t="n">
-        <v>11.1316</v>
+        <v>11.0534</v>
       </c>
     </row>
     <row r="288">
@@ -15755,10 +15755,10 @@
         <v>1.02</v>
       </c>
       <c r="I288" t="n">
-        <v>0.0805</v>
+        <v>0.0838</v>
       </c>
       <c r="J288" t="n">
-        <v>2.737</v>
+        <v>2.8492</v>
       </c>
     </row>
     <row r="289">
@@ -15795,10 +15795,10 @@
         <v>1.02</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0805</v>
+        <v>0.0838</v>
       </c>
       <c r="J289" t="n">
-        <v>2.737</v>
+        <v>2.8492</v>
       </c>
     </row>
     <row r="290">
@@ -15835,10 +15835,10 @@
         <v>0.79</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2408</v>
+        <v>-0.2559</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.187200000000001</v>
+        <v>-8.7006</v>
       </c>
     </row>
     <row r="291">
@@ -15875,10 +15875,10 @@
         <v>0.7</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3282</v>
+        <v>-0.3414</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.1588</v>
+        <v>-11.6076</v>
       </c>
     </row>
     <row r="292">
@@ -15915,10 +15915,10 @@
         <v>0.95</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.0517</v>
+        <v>-0.0675</v>
       </c>
       <c r="J292" t="n">
-        <v>-1.1891</v>
+        <v>-1.5525</v>
       </c>
     </row>
     <row r="293">
@@ -15955,10 +15955,10 @@
         <v>0.88</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.1351</v>
+        <v>-0.1532</v>
       </c>
       <c r="J293" t="n">
-        <v>-3.1073</v>
+        <v>-3.5236</v>
       </c>
     </row>
     <row r="294">
@@ -15995,10 +15995,10 @@
         <v>0.82</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1973</v>
+        <v>-0.2158</v>
       </c>
       <c r="J294" t="n">
-        <v>-4.5379</v>
+        <v>-4.9634</v>
       </c>
     </row>
     <row r="295">
@@ -16035,10 +16035,10 @@
         <v>0.78</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2352</v>
+        <v>-0.2537</v>
       </c>
       <c r="J295" t="n">
-        <v>-5.4096</v>
+        <v>-5.8351</v>
       </c>
     </row>
     <row r="296">
@@ -16075,10 +16075,10 @@
         <v>0.61</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3965</v>
+        <v>-0.4099</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.1195</v>
+        <v>-9.4277</v>
       </c>
     </row>
     <row r="297">
@@ -16115,10 +16115,10 @@
         <v>1.71</v>
       </c>
       <c r="I297" t="n">
-        <v>1.3905</v>
+        <v>1.3715</v>
       </c>
       <c r="J297" t="n">
-        <v>31.9815</v>
+        <v>31.5445</v>
       </c>
     </row>
     <row r="298">
@@ -16155,10 +16155,10 @@
         <v>1.62</v>
       </c>
       <c r="I298" t="n">
-        <v>1.2802</v>
+        <v>1.2547</v>
       </c>
       <c r="J298" t="n">
-        <v>29.4446</v>
+        <v>28.8581</v>
       </c>
     </row>
     <row r="299">
@@ -16195,10 +16195,10 @@
         <v>1.22</v>
       </c>
       <c r="I299" t="n">
-        <v>0.6002</v>
+        <v>0.5829</v>
       </c>
       <c r="J299" t="n">
-        <v>13.8046</v>
+        <v>13.4067</v>
       </c>
     </row>
     <row r="300">
@@ -16235,10 +16235,10 @@
         <v>0.96</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2289</v>
+        <v>-0.2137</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.2647</v>
+        <v>-4.9151</v>
       </c>
     </row>
     <row r="301">
@@ -16275,10 +16275,10 @@
         <v>0.73</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.8618</v>
+        <v>-0.7883</v>
       </c>
       <c r="J301" t="n">
-        <v>-19.8214</v>
+        <v>-18.1309</v>
       </c>
     </row>
     <row r="302">
@@ -16315,10 +16315,10 @@
         <v>1.34</v>
       </c>
       <c r="I302" t="n">
-        <v>0.6911</v>
+        <v>0.6635</v>
       </c>
       <c r="J302" t="n">
-        <v>19.3508</v>
+        <v>18.578</v>
       </c>
     </row>
     <row r="303">
@@ -16355,10 +16355,10 @@
         <v>1.1</v>
       </c>
       <c r="I303" t="n">
-        <v>0.2495</v>
+        <v>0.2547</v>
       </c>
       <c r="J303" t="n">
-        <v>6.986</v>
+        <v>7.1316</v>
       </c>
     </row>
     <row r="304">
@@ -16395,10 +16395,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J304" t="n">
-        <v>-2.4332</v>
+        <v>-2.7468</v>
       </c>
     </row>
     <row r="305">
@@ -16435,10 +16435,10 @@
         <v>0.93</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.0988</v>
+        <v>-0.1105</v>
       </c>
       <c r="J305" t="n">
-        <v>-2.7664</v>
+        <v>-3.094</v>
       </c>
     </row>
     <row r="306">
@@ -16475,10 +16475,10 @@
         <v>0.63</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4004</v>
+        <v>-0.4098</v>
       </c>
       <c r="J306" t="n">
-        <v>-11.2112</v>
+        <v>-11.4744</v>
       </c>
     </row>
     <row r="307">
@@ -16515,10 +16515,10 @@
         <v>1.38</v>
       </c>
       <c r="I307" t="n">
-        <v>0.9872</v>
+        <v>0.9261</v>
       </c>
       <c r="J307" t="n">
-        <v>27.6416</v>
+        <v>25.9308</v>
       </c>
     </row>
     <row r="308">
@@ -16555,10 +16555,10 @@
         <v>1.29</v>
       </c>
       <c r="I308" t="n">
-        <v>0.788</v>
+        <v>0.7448</v>
       </c>
       <c r="J308" t="n">
-        <v>22.064</v>
+        <v>20.8544</v>
       </c>
     </row>
     <row r="309">
@@ -16595,10 +16595,10 @@
         <v>1.17</v>
       </c>
       <c r="I309" t="n">
-        <v>0.4969</v>
+        <v>0.4857</v>
       </c>
       <c r="J309" t="n">
-        <v>13.9132</v>
+        <v>13.5996</v>
       </c>
     </row>
     <row r="310">
@@ -16635,10 +16635,10 @@
         <v>1.03</v>
       </c>
       <c r="I310" t="n">
-        <v>0.099</v>
+        <v>0.1143</v>
       </c>
       <c r="J310" t="n">
-        <v>2.772</v>
+        <v>3.2004</v>
       </c>
     </row>
     <row r="311">
@@ -16675,10 +16675,10 @@
         <v>0.84</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5554</v>
+        <v>-0.5212</v>
       </c>
       <c r="J311" t="n">
-        <v>-15.5512</v>
+        <v>-14.5936</v>
       </c>
     </row>
     <row r="312">
@@ -16715,10 +16715,10 @@
         <v>1.13</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3267</v>
+        <v>0.3246</v>
       </c>
       <c r="J312" t="n">
-        <v>7.8408</v>
+        <v>7.7904</v>
       </c>
     </row>
     <row r="313">
@@ -16755,10 +16755,10 @@
         <v>1.03</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1066</v>
+        <v>0.1106</v>
       </c>
       <c r="J313" t="n">
-        <v>2.5584</v>
+        <v>2.6544</v>
       </c>
     </row>
     <row r="314">
@@ -16795,10 +16795,10 @@
         <v>1.01</v>
       </c>
       <c r="I314" t="n">
-        <v>0.0508</v>
+        <v>0.0527</v>
       </c>
       <c r="J314" t="n">
-        <v>1.2192</v>
+        <v>1.2648</v>
       </c>
     </row>
     <row r="315">
@@ -16835,10 +16835,10 @@
         <v>0.76</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2706</v>
+        <v>-0.2852</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.4944</v>
+        <v>-6.8448</v>
       </c>
     </row>
     <row r="316">
@@ -16875,10 +16875,10 @@
         <v>0.74</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.2901</v>
+        <v>-0.3042</v>
       </c>
       <c r="J316" t="n">
-        <v>-6.9624</v>
+        <v>-7.3008</v>
       </c>
     </row>
     <row r="317">
@@ -16915,10 +16915,10 @@
         <v>1.59</v>
       </c>
       <c r="I317" t="n">
-        <v>1.2383</v>
+        <v>1.2109</v>
       </c>
       <c r="J317" t="n">
-        <v>29.7192</v>
+        <v>29.0616</v>
       </c>
     </row>
     <row r="318">
@@ -16955,10 +16955,10 @@
         <v>1.52</v>
       </c>
       <c r="I318" t="n">
-        <v>1.1513</v>
+        <v>1.1178</v>
       </c>
       <c r="J318" t="n">
-        <v>27.6312</v>
+        <v>26.8272</v>
       </c>
     </row>
     <row r="319">
@@ -16995,10 +16995,10 @@
         <v>1.13</v>
       </c>
       <c r="I319" t="n">
-        <v>0.3693</v>
+        <v>0.3751</v>
       </c>
       <c r="J319" t="n">
-        <v>8.863200000000001</v>
+        <v>9.0024</v>
       </c>
     </row>
     <row r="320">
@@ -17035,10 +17035,10 @@
         <v>1.08</v>
       </c>
       <c r="I320" t="n">
-        <v>0.2286</v>
+        <v>0.2454</v>
       </c>
       <c r="J320" t="n">
-        <v>5.4864</v>
+        <v>5.8896</v>
       </c>
     </row>
     <row r="321">
@@ -17075,10 +17075,10 @@
         <v>1.02</v>
       </c>
       <c r="I321" t="n">
-        <v>0.0307</v>
+        <v>0.056</v>
       </c>
       <c r="J321" t="n">
-        <v>0.7368</v>
+        <v>1.344</v>
       </c>
     </row>
     <row r="322">
@@ -17115,10 +17115,10 @@
         <v>1.54</v>
       </c>
       <c r="I322" t="n">
-        <v>1.1677</v>
+        <v>1.137</v>
       </c>
       <c r="J322" t="n">
-        <v>28.0248</v>
+        <v>27.288</v>
       </c>
     </row>
     <row r="323">
@@ -17155,10 +17155,10 @@
         <v>1.45</v>
       </c>
       <c r="I323" t="n">
-        <v>1.0555</v>
+        <v>1.0119</v>
       </c>
       <c r="J323" t="n">
-        <v>25.332</v>
+        <v>24.2856</v>
       </c>
     </row>
     <row r="324">
@@ -17195,10 +17195,10 @@
         <v>1.24</v>
       </c>
       <c r="I324" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.617</v>
       </c>
       <c r="J324" t="n">
-        <v>15.2544</v>
+        <v>14.808</v>
       </c>
     </row>
     <row r="325">
@@ -17235,10 +17235,10 @@
         <v>1.18</v>
       </c>
       <c r="I325" t="n">
-        <v>0.4897</v>
+        <v>0.4863</v>
       </c>
       <c r="J325" t="n">
-        <v>11.7528</v>
+        <v>11.6712</v>
       </c>
     </row>
     <row r="326">
@@ -17275,10 +17275,10 @@
         <v>1.14</v>
       </c>
       <c r="I326" t="n">
-        <v>0.3864</v>
+        <v>0.3928</v>
       </c>
       <c r="J326" t="n">
-        <v>9.2736</v>
+        <v>9.427199999999999</v>
       </c>
     </row>
     <row r="327">
@@ -17315,10 +17315,10 @@
         <v>1.07</v>
       </c>
       <c r="I327" t="n">
-        <v>0.2312</v>
+        <v>0.2263</v>
       </c>
       <c r="J327" t="n">
-        <v>5.5488</v>
+        <v>5.4312</v>
       </c>
     </row>
     <row r="328">
@@ -17355,10 +17355,10 @@
         <v>0.93</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J328" t="n">
-        <v>-2.028</v>
+        <v>-2.3904</v>
       </c>
     </row>
     <row r="329">
@@ -17395,10 +17395,10 @@
         <v>0.77</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.2501</v>
+        <v>-0.2672</v>
       </c>
       <c r="J329" t="n">
-        <v>-6.0024</v>
+        <v>-6.4128</v>
       </c>
     </row>
     <row r="330">
@@ -17435,10 +17435,10 @@
         <v>0.76</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2598</v>
+        <v>-0.2768</v>
       </c>
       <c r="J330" t="n">
-        <v>-6.2352</v>
+        <v>-6.6432</v>
       </c>
     </row>
     <row r="331">
@@ -17475,10 +17475,10 @@
         <v>0.72</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.2984</v>
+        <v>-0.3145</v>
       </c>
       <c r="J331" t="n">
-        <v>-7.1616</v>
+        <v>-7.548</v>
       </c>
     </row>
     <row r="332">
@@ -17515,10 +17515,10 @@
         <v>1.55</v>
       </c>
       <c r="I332" t="n">
-        <v>0.9849</v>
+        <v>0.9392</v>
       </c>
       <c r="J332" t="n">
-        <v>40.3809</v>
+        <v>38.5072</v>
       </c>
     </row>
     <row r="333">
@@ -17555,10 +17555,10 @@
         <v>1.15</v>
       </c>
       <c r="I333" t="n">
-        <v>0.3243</v>
+        <v>0.3312</v>
       </c>
       <c r="J333" t="n">
-        <v>13.2963</v>
+        <v>13.5792</v>
       </c>
     </row>
     <row r="334">
@@ -17595,10 +17595,10 @@
         <v>1.06</v>
       </c>
       <c r="I334" t="n">
-        <v>0.149</v>
+        <v>0.1611</v>
       </c>
       <c r="J334" t="n">
-        <v>6.109</v>
+        <v>6.6051</v>
       </c>
     </row>
     <row r="335">
@@ -17635,10 +17635,10 @@
         <v>0.88</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.1657</v>
+        <v>-0.1767</v>
       </c>
       <c r="J335" t="n">
-        <v>-6.7937</v>
+        <v>-7.2447</v>
       </c>
     </row>
     <row r="336">
@@ -17675,10 +17675,10 @@
         <v>0.79</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2585</v>
+        <v>-0.2698</v>
       </c>
       <c r="J336" t="n">
-        <v>-10.5985</v>
+        <v>-11.0618</v>
       </c>
     </row>
     <row r="337">
@@ -17715,10 +17715,10 @@
         <v>1.5</v>
       </c>
       <c r="I337" t="n">
-        <v>1.1568</v>
+        <v>1.1178</v>
       </c>
       <c r="J337" t="n">
-        <v>47.4288</v>
+        <v>45.8298</v>
       </c>
     </row>
     <row r="338">
@@ -17755,10 +17755,10 @@
         <v>1.41</v>
       </c>
       <c r="I338" t="n">
-        <v>1.0367</v>
+        <v>0.9813</v>
       </c>
       <c r="J338" t="n">
-        <v>42.5047</v>
+        <v>40.2333</v>
       </c>
     </row>
     <row r="339">
@@ -17795,10 +17795,10 @@
         <v>1.13</v>
       </c>
       <c r="I339" t="n">
-        <v>0.3963</v>
+        <v>0.3937</v>
       </c>
       <c r="J339" t="n">
-        <v>16.2483</v>
+        <v>16.1417</v>
       </c>
     </row>
     <row r="340">
@@ -17835,10 +17835,10 @@
         <v>0.87</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4736</v>
+        <v>-0.4473</v>
       </c>
       <c r="J340" t="n">
-        <v>-19.4176</v>
+        <v>-18.3393</v>
       </c>
     </row>
     <row r="341">
@@ -17875,10 +17875,10 @@
         <v>0.8</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.6153</v>
       </c>
       <c r="J341" t="n">
-        <v>-27.0928</v>
+        <v>-25.2273</v>
       </c>
     </row>
     <row r="342">
@@ -17915,10 +17915,10 @@
         <v>1.01</v>
       </c>
       <c r="I342" t="n">
-        <v>0.0523</v>
+        <v>0.0538</v>
       </c>
       <c r="J342" t="n">
-        <v>1.569</v>
+        <v>1.614</v>
       </c>
     </row>
     <row r="343">
@@ -17955,10 +17955,10 @@
         <v>0.98</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.0298</v>
+        <v>-0.038</v>
       </c>
       <c r="J343" t="n">
-        <v>-0.894</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="344">
@@ -17995,10 +17995,10 @@
         <v>0.96</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.0574</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="J344" t="n">
-        <v>-1.722</v>
+        <v>-2.043</v>
       </c>
     </row>
     <row r="345">
@@ -18035,10 +18035,10 @@
         <v>0.89</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1374</v>
+        <v>-0.1521</v>
       </c>
       <c r="J345" t="n">
-        <v>-4.122</v>
+        <v>-4.563</v>
       </c>
     </row>
     <row r="346">
@@ -18075,10 +18075,10 @@
         <v>0.8</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2304</v>
+        <v>-0.2457</v>
       </c>
       <c r="J346" t="n">
-        <v>-6.912</v>
+        <v>-7.371</v>
       </c>
     </row>
     <row r="347">
@@ -18115,10 +18115,10 @@
         <v>1.33</v>
       </c>
       <c r="I347" t="n">
-        <v>0.8622</v>
+        <v>0.8132</v>
       </c>
       <c r="J347" t="n">
-        <v>25.866</v>
+        <v>24.396</v>
       </c>
     </row>
     <row r="348">
@@ -18155,10 +18155,10 @@
         <v>1.32</v>
       </c>
       <c r="I348" t="n">
-        <v>0.8394</v>
+        <v>0.7932</v>
       </c>
       <c r="J348" t="n">
-        <v>25.182</v>
+        <v>23.796</v>
       </c>
     </row>
     <row r="349">
@@ -18195,10 +18195,10 @@
         <v>1.25</v>
       </c>
       <c r="I349" t="n">
-        <v>0.6775</v>
+        <v>0.6504</v>
       </c>
       <c r="J349" t="n">
-        <v>20.325</v>
+        <v>19.512</v>
       </c>
     </row>
     <row r="350">
@@ -18235,10 +18235,10 @@
         <v>1.13</v>
       </c>
       <c r="I350" t="n">
-        <v>0.3847</v>
+        <v>0.3858</v>
       </c>
       <c r="J350" t="n">
-        <v>11.541</v>
+        <v>11.574</v>
       </c>
     </row>
     <row r="351">
@@ -18275,10 +18275,10 @@
         <v>0.97</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.182</v>
+        <v>-0.1715</v>
       </c>
       <c r="J351" t="n">
-        <v>-5.46</v>
+        <v>-5.145</v>
       </c>
     </row>
     <row r="352">
@@ -18315,10 +18315,10 @@
         <v>1.77</v>
       </c>
       <c r="I352" t="n">
-        <v>1.4719</v>
+        <v>1.4558</v>
       </c>
       <c r="J352" t="n">
-        <v>35.3256</v>
+        <v>34.9392</v>
       </c>
     </row>
     <row r="353">
@@ -18355,10 +18355,10 @@
         <v>1.52</v>
       </c>
       <c r="I353" t="n">
-        <v>1.1621</v>
+        <v>1.1273</v>
       </c>
       <c r="J353" t="n">
-        <v>27.8904</v>
+        <v>27.0552</v>
       </c>
     </row>
     <row r="354">
@@ -18395,10 +18395,10 @@
         <v>1.18</v>
       </c>
       <c r="I354" t="n">
-        <v>0.5088</v>
+        <v>0.4995</v>
       </c>
       <c r="J354" t="n">
-        <v>12.2112</v>
+        <v>11.988</v>
       </c>
     </row>
     <row r="355">
@@ -18435,10 +18435,10 @@
         <v>1.04</v>
       </c>
       <c r="I355" t="n">
-        <v>0.1143</v>
+        <v>0.1344</v>
       </c>
       <c r="J355" t="n">
-        <v>2.7432</v>
+        <v>3.2256</v>
       </c>
     </row>
     <row r="356">
@@ -18475,10 +18475,10 @@
         <v>0.59</v>
       </c>
       <c r="I356" t="n">
-        <v>-1.1884</v>
+        <v>-1.0727</v>
       </c>
       <c r="J356" t="n">
-        <v>-28.5216</v>
+        <v>-25.7448</v>
       </c>
     </row>
     <row r="357">
@@ -18515,10 +18515,10 @@
         <v>1.63</v>
       </c>
       <c r="I357" t="n">
-        <v>1.0927</v>
+        <v>1.0588</v>
       </c>
       <c r="J357" t="n">
-        <v>26.2248</v>
+        <v>25.4112</v>
       </c>
     </row>
     <row r="358">
@@ -18555,10 +18555,10 @@
         <v>1.26</v>
       </c>
       <c r="I358" t="n">
-        <v>0.5434</v>
+        <v>0.5308</v>
       </c>
       <c r="J358" t="n">
-        <v>13.0416</v>
+        <v>12.7392</v>
       </c>
     </row>
     <row r="359">
@@ -18595,10 +18595,10 @@
         <v>0.82</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.22</v>
+        <v>-0.2333</v>
       </c>
       <c r="J359" t="n">
-        <v>-5.28</v>
+        <v>-5.5992</v>
       </c>
     </row>
     <row r="360">
@@ -18635,10 +18635,10 @@
         <v>0.68</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.3562</v>
+        <v>-0.3668</v>
       </c>
       <c r="J360" t="n">
-        <v>-8.5488</v>
+        <v>-8.8032</v>
       </c>
     </row>
     <row r="361">
@@ -18675,10 +18675,10 @@
         <v>0.66</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3749</v>
+        <v>-0.3849</v>
       </c>
       <c r="J361" t="n">
-        <v>-8.9976</v>
+        <v>-9.2376</v>
       </c>
     </row>
     <row r="362">
@@ -18715,10 +18715,10 @@
         <v>0.98</v>
       </c>
       <c r="I362" t="n">
-        <v>0.0149</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="J362" t="n">
-        <v>0.2682</v>
+        <v>-0.1512</v>
       </c>
     </row>
     <row r="363">
@@ -18755,10 +18755,10 @@
         <v>0.78</v>
       </c>
       <c r="I363" t="n">
-        <v>-0.2279</v>
+        <v>-0.2481</v>
       </c>
       <c r="J363" t="n">
-        <v>-4.1022</v>
+        <v>-4.4658</v>
       </c>
     </row>
     <row r="364">
@@ -18795,10 +18795,10 @@
         <v>0.68</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.3207</v>
+        <v>-0.3391</v>
       </c>
       <c r="J364" t="n">
-        <v>-5.7726</v>
+        <v>-6.1038</v>
       </c>
     </row>
     <row r="365">
@@ -18835,10 +18835,10 @@
         <v>0.64</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.3582</v>
+        <v>-0.3751</v>
       </c>
       <c r="J365" t="n">
-        <v>-6.4476</v>
+        <v>-6.7518</v>
       </c>
     </row>
     <row r="366">
@@ -18875,10 +18875,10 @@
         <v>0.62</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.3769</v>
+        <v>-0.393</v>
       </c>
       <c r="J366" t="n">
-        <v>-6.7842</v>
+        <v>-7.074</v>
       </c>
     </row>
     <row r="367">
@@ -18915,10 +18915,10 @@
         <v>1.83</v>
       </c>
       <c r="I367" t="n">
-        <v>1.4795</v>
+        <v>1.4743</v>
       </c>
       <c r="J367" t="n">
-        <v>26.631</v>
+        <v>26.5374</v>
       </c>
     </row>
     <row r="368">
@@ -18955,10 +18955,10 @@
         <v>1.47</v>
       </c>
       <c r="I368" t="n">
-        <v>1.0614</v>
+        <v>1.0237</v>
       </c>
       <c r="J368" t="n">
-        <v>19.1052</v>
+        <v>18.4266</v>
       </c>
     </row>
     <row r="369">
@@ -18995,10 +18995,10 @@
         <v>1.42</v>
       </c>
       <c r="I369" t="n">
-        <v>0.9927</v>
+        <v>0.9455</v>
       </c>
       <c r="J369" t="n">
-        <v>17.8686</v>
+        <v>17.019</v>
       </c>
     </row>
     <row r="370">
@@ -19035,10 +19035,10 @@
         <v>1.31</v>
       </c>
       <c r="I370" t="n">
-        <v>0.7655</v>
+        <v>0.7382</v>
       </c>
       <c r="J370" t="n">
-        <v>13.779</v>
+        <v>13.2876</v>
       </c>
     </row>
     <row r="371">
@@ -19075,10 +19075,10 @@
         <v>1.3</v>
       </c>
       <c r="I371" t="n">
-        <v>0.7429</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="J371" t="n">
-        <v>13.3722</v>
+        <v>12.9276</v>
       </c>
     </row>
     <row r="372">
@@ -19115,10 +19115,10 @@
         <v>1.62</v>
       </c>
       <c r="I372" t="n">
-        <v>1.2833</v>
+        <v>1.2574</v>
       </c>
       <c r="J372" t="n">
-        <v>32.0825</v>
+        <v>31.435</v>
       </c>
     </row>
     <row r="373">
@@ -19155,10 +19155,10 @@
         <v>1.37</v>
       </c>
       <c r="I373" t="n">
-        <v>0.9395</v>
+        <v>0.8842</v>
       </c>
       <c r="J373" t="n">
-        <v>23.4875</v>
+        <v>22.105</v>
       </c>
     </row>
     <row r="374">
@@ -19195,10 +19195,10 @@
         <v>1.23</v>
       </c>
       <c r="I374" t="n">
-        <v>0.6253</v>
+        <v>0.6051</v>
       </c>
       <c r="J374" t="n">
-        <v>15.6325</v>
+        <v>15.1275</v>
       </c>
     </row>
     <row r="375">
@@ -19235,10 +19235,10 @@
         <v>1.16</v>
       </c>
       <c r="I375" t="n">
-        <v>0.4551</v>
+        <v>0.4517</v>
       </c>
       <c r="J375" t="n">
-        <v>11.3775</v>
+        <v>11.2925</v>
       </c>
     </row>
     <row r="376">
@@ -19275,10 +19275,10 @@
         <v>0.8</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.6835</v>
+        <v>-0.6313</v>
       </c>
       <c r="J376" t="n">
-        <v>-17.0875</v>
+        <v>-15.7825</v>
       </c>
     </row>
     <row r="377">
@@ -19315,10 +19315,10 @@
         <v>1.01</v>
       </c>
       <c r="I377" t="n">
-        <v>0.1035</v>
+        <v>0.0912</v>
       </c>
       <c r="J377" t="n">
-        <v>2.5875</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="378">
@@ -19355,10 +19355,10 @@
         <v>0.85</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.1639</v>
+        <v>-0.183</v>
       </c>
       <c r="J378" t="n">
-        <v>-4.0975</v>
+        <v>-4.575</v>
       </c>
     </row>
     <row r="379">
@@ -19395,10 +19395,10 @@
         <v>0.84</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.1743</v>
+        <v>-0.1935</v>
       </c>
       <c r="J379" t="n">
-        <v>-4.3575</v>
+        <v>-4.8375</v>
       </c>
     </row>
     <row r="380">
@@ -19435,10 +19435,10 @@
         <v>0.62</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.384</v>
+        <v>-0.3985</v>
       </c>
       <c r="J380" t="n">
-        <v>-9.6</v>
+        <v>-9.9625</v>
       </c>
     </row>
     <row r="381">
@@ -19475,10 +19475,10 @@
         <v>0.61</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3933</v>
+        <v>-0.4074</v>
       </c>
       <c r="J381" t="n">
-        <v>-9.8325</v>
+        <v>-10.185</v>
       </c>
     </row>
     <row r="382">
@@ -19515,10 +19515,10 @@
         <v>0.86</v>
       </c>
       <c r="I382" t="n">
-        <v>-0.096</v>
+        <v>-0.1274</v>
       </c>
       <c r="J382" t="n">
-        <v>-1.728</v>
+        <v>-2.2932</v>
       </c>
     </row>
     <row r="383">
@@ -19555,10 +19555,10 @@
         <v>0.7</v>
       </c>
       <c r="I383" t="n">
-        <v>-0.2754</v>
+        <v>-0.3005</v>
       </c>
       <c r="J383" t="n">
-        <v>-4.9572</v>
+        <v>-5.409</v>
       </c>
     </row>
     <row r="384">
@@ -19595,10 +19595,10 @@
         <v>0.5</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.4626</v>
+        <v>-0.4782</v>
       </c>
       <c r="J384" t="n">
-        <v>-8.3268</v>
+        <v>-8.6076</v>
       </c>
     </row>
     <row r="385">
@@ -19635,10 +19635,10 @@
         <v>0.46</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.5004</v>
+        <v>-0.5135</v>
       </c>
       <c r="J385" t="n">
-        <v>-9.007199999999999</v>
+        <v>-9.243</v>
       </c>
     </row>
     <row r="386">
@@ -19675,10 +19675,10 @@
         <v>0.42</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.5386</v>
+        <v>-0.5488</v>
       </c>
       <c r="J386" t="n">
-        <v>-9.694800000000001</v>
+        <v>-9.878399999999999</v>
       </c>
     </row>
     <row r="387">
@@ -19715,10 +19715,10 @@
         <v>1.79</v>
       </c>
       <c r="I387" t="n">
-        <v>1.4151</v>
+        <v>1.4097</v>
       </c>
       <c r="J387" t="n">
-        <v>25.4718</v>
+        <v>25.3746</v>
       </c>
     </row>
     <row r="388">
@@ -19755,10 +19755,10 @@
         <v>1.74</v>
       </c>
       <c r="I388" t="n">
-        <v>1.3592</v>
+        <v>1.3502</v>
       </c>
       <c r="J388" t="n">
-        <v>24.4656</v>
+        <v>24.3036</v>
       </c>
     </row>
     <row r="389">
@@ -19795,10 +19795,10 @@
         <v>1.56</v>
       </c>
       <c r="I389" t="n">
-        <v>1.1574</v>
+        <v>1.1331</v>
       </c>
       <c r="J389" t="n">
-        <v>20.8332</v>
+        <v>20.3958</v>
       </c>
     </row>
     <row r="390">
@@ -19835,10 +19835,10 @@
         <v>1.43</v>
       </c>
       <c r="I390" t="n">
-        <v>0.9937</v>
+        <v>0.95</v>
       </c>
       <c r="J390" t="n">
-        <v>17.8866</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="391">
@@ -19875,10 +19875,10 @@
         <v>1.37</v>
       </c>
       <c r="I391" t="n">
-        <v>0.8767</v>
+        <v>0.8397</v>
       </c>
       <c r="J391" t="n">
-        <v>15.7806</v>
+        <v>15.1146</v>
       </c>
     </row>
     <row r="392">
@@ -19915,10 +19915,10 @@
         <v>1.39</v>
       </c>
       <c r="I392" t="n">
-        <v>1.0099</v>
+        <v>0.9495</v>
       </c>
       <c r="J392" t="n">
-        <v>27.2673</v>
+        <v>25.6365</v>
       </c>
     </row>
     <row r="393">
@@ -19955,10 +19955,10 @@
         <v>1.38</v>
       </c>
       <c r="I393" t="n">
-        <v>0.9925</v>
+        <v>0.9306</v>
       </c>
       <c r="J393" t="n">
-        <v>26.7975</v>
+        <v>25.1262</v>
       </c>
     </row>
     <row r="394">
@@ -19995,10 +19995,10 @@
         <v>1.14</v>
       </c>
       <c r="I394" t="n">
-        <v>0.424</v>
+        <v>0.4186</v>
       </c>
       <c r="J394" t="n">
-        <v>11.448</v>
+        <v>11.3022</v>
       </c>
     </row>
     <row r="395">
@@ -20035,10 +20035,10 @@
         <v>0.89</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.4131</v>
+        <v>-0.3931</v>
       </c>
       <c r="J395" t="n">
-        <v>-11.1537</v>
+        <v>-10.6137</v>
       </c>
     </row>
     <row r="396">
@@ -20075,10 +20075,10 @@
         <v>0.83</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.5779</v>
+        <v>-0.5422</v>
       </c>
       <c r="J396" t="n">
-        <v>-15.6033</v>
+        <v>-14.6394</v>
       </c>
     </row>
     <row r="397">
@@ -20115,10 +20115,10 @@
         <v>1.08</v>
       </c>
       <c r="I397" t="n">
-        <v>0.2273</v>
+        <v>0.2287</v>
       </c>
       <c r="J397" t="n">
-        <v>6.1371</v>
+        <v>6.1749</v>
       </c>
     </row>
     <row r="398">
@@ -20155,10 +20155,10 @@
         <v>1.05</v>
       </c>
       <c r="I398" t="n">
-        <v>0.1596</v>
+        <v>0.1625</v>
       </c>
       <c r="J398" t="n">
-        <v>4.3092</v>
+        <v>4.3875</v>
       </c>
     </row>
     <row r="399">
@@ -20195,10 +20195,10 @@
         <v>1.03</v>
       </c>
       <c r="I399" t="n">
-        <v>0.1105</v>
+        <v>0.1134</v>
       </c>
       <c r="J399" t="n">
-        <v>2.9835</v>
+        <v>3.0618</v>
       </c>
     </row>
     <row r="400">
@@ -20235,10 +20235,10 @@
         <v>0.88</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.1472</v>
+        <v>-0.1624</v>
       </c>
       <c r="J400" t="n">
-        <v>-3.9744</v>
+        <v>-4.3848</v>
       </c>
     </row>
     <row r="401">
@@ -20275,10 +20275,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.4571</v>
+        <v>-0.4652</v>
       </c>
       <c r="J401" t="n">
-        <v>-12.3417</v>
+        <v>-12.5604</v>
       </c>
     </row>
     <row r="402">
@@ -20315,10 +20315,10 @@
         <v>1.25</v>
       </c>
       <c r="I402" t="n">
-        <v>0.5306</v>
+        <v>0.5181</v>
       </c>
       <c r="J402" t="n">
-        <v>15.3874</v>
+        <v>15.0249</v>
       </c>
     </row>
     <row r="403">
@@ -20355,10 +20355,10 @@
         <v>1.04</v>
       </c>
       <c r="I403" t="n">
-        <v>0.1168</v>
+        <v>0.1251</v>
       </c>
       <c r="J403" t="n">
-        <v>3.3872</v>
+        <v>3.6279</v>
       </c>
     </row>
     <row r="404">
@@ -20395,10 +20395,10 @@
         <v>1.02</v>
       </c>
       <c r="I404" t="n">
-        <v>0.0667</v>
+        <v>0.0738</v>
       </c>
       <c r="J404" t="n">
-        <v>1.9343</v>
+        <v>2.1402</v>
       </c>
     </row>
     <row r="405">
@@ -20435,10 +20435,10 @@
         <v>0.99</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.0203</v>
+        <v>-0.025</v>
       </c>
       <c r="J405" t="n">
-        <v>-0.5887</v>
+        <v>-0.725</v>
       </c>
     </row>
     <row r="406">
@@ -20475,10 +20475,10 @@
         <v>0.68</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.3547</v>
+        <v>-0.3656</v>
       </c>
       <c r="J406" t="n">
-        <v>-10.2863</v>
+        <v>-10.6024</v>
       </c>
     </row>
     <row r="407">
@@ -20515,10 +20515,10 @@
         <v>1.26</v>
       </c>
       <c r="I407" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.6776</v>
       </c>
       <c r="J407" t="n">
-        <v>20.5958</v>
+        <v>19.6504</v>
       </c>
     </row>
     <row r="408">
@@ -20555,10 +20555,10 @@
         <v>1.26</v>
       </c>
       <c r="I408" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.6776</v>
       </c>
       <c r="J408" t="n">
-        <v>20.5958</v>
+        <v>19.6504</v>
       </c>
     </row>
     <row r="409">
@@ -20595,10 +20595,10 @@
         <v>1.24</v>
       </c>
       <c r="I409" t="n">
-        <v>0.6626</v>
+        <v>0.6354</v>
       </c>
       <c r="J409" t="n">
-        <v>19.2154</v>
+        <v>18.4266</v>
       </c>
     </row>
     <row r="410">
@@ -20635,10 +20635,10 @@
         <v>1.15</v>
       </c>
       <c r="I410" t="n">
-        <v>0.4439</v>
+        <v>0.4382</v>
       </c>
       <c r="J410" t="n">
-        <v>12.8731</v>
+        <v>12.7078</v>
       </c>
     </row>
     <row r="411">
@@ -20675,10 +20675,10 @@
         <v>0.91</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.3651</v>
+        <v>-0.3467</v>
       </c>
       <c r="J411" t="n">
-        <v>-10.5879</v>
+        <v>-10.0543</v>
       </c>
     </row>
     <row r="412">
@@ -20715,10 +20715,10 @@
         <v>1.79</v>
       </c>
       <c r="I412" t="n">
-        <v>1.4366</v>
+        <v>1.4285</v>
       </c>
       <c r="J412" t="n">
-        <v>33.0418</v>
+        <v>32.8555</v>
       </c>
     </row>
     <row r="413">
@@ -20755,10 +20755,10 @@
         <v>1.74</v>
       </c>
       <c r="I413" t="n">
-        <v>1.3791</v>
+        <v>1.3676</v>
       </c>
       <c r="J413" t="n">
-        <v>31.7193</v>
+        <v>31.4548</v>
       </c>
     </row>
     <row r="414">
@@ -20795,10 +20795,10 @@
         <v>1.59</v>
       </c>
       <c r="I414" t="n">
-        <v>1.2043</v>
+        <v>1.1811</v>
       </c>
       <c r="J414" t="n">
-        <v>27.6989</v>
+        <v>27.1653</v>
       </c>
     </row>
     <row r="415">
@@ -20835,10 +20835,10 @@
         <v>1.1</v>
       </c>
       <c r="I415" t="n">
-        <v>0.2457</v>
+        <v>0.2706</v>
       </c>
       <c r="J415" t="n">
-        <v>5.6511</v>
+        <v>6.2238</v>
       </c>
     </row>
     <row r="416">
@@ -20875,10 +20875,10 @@
         <v>1.04</v>
       </c>
       <c r="I416" t="n">
-        <v>0.062</v>
+        <v>0.0977</v>
       </c>
       <c r="J416" t="n">
-        <v>1.426</v>
+        <v>2.2471</v>
       </c>
     </row>
     <row r="417">
@@ -20915,10 +20915,10 @@
         <v>1.02</v>
       </c>
       <c r="I417" t="n">
-        <v>0.1563</v>
+        <v>0.1393</v>
       </c>
       <c r="J417" t="n">
-        <v>3.5949</v>
+        <v>3.2039</v>
       </c>
     </row>
     <row r="418">
@@ -20955,10 +20955,10 @@
         <v>1.01</v>
       </c>
       <c r="I418" t="n">
-        <v>0.1252</v>
+        <v>0.1072</v>
       </c>
       <c r="J418" t="n">
-        <v>2.8796</v>
+        <v>2.4656</v>
       </c>
     </row>
     <row r="419">
@@ -20995,10 +20995,10 @@
         <v>0.59</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.4057</v>
+        <v>-0.4202</v>
       </c>
       <c r="J419" t="n">
-        <v>-9.331099999999999</v>
+        <v>-9.6646</v>
       </c>
     </row>
     <row r="420">
@@ -21035,10 +21035,10 @@
         <v>0.58</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.415</v>
+        <v>-0.4291</v>
       </c>
       <c r="J420" t="n">
-        <v>-9.545</v>
+        <v>-9.869300000000001</v>
       </c>
     </row>
     <row r="421">
@@ -21075,10 +21075,10 @@
         <v>0.52</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.471</v>
+        <v>-0.4819</v>
       </c>
       <c r="J421" t="n">
-        <v>-10.833</v>
+        <v>-11.0837</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2099/event_2099_evp_summary.xlsx
+++ b/database/event/2099/event_2099_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.5731</v>
+        <v>6.4143</v>
       </c>
       <c r="C2" t="n">
-        <v>3.84</v>
+        <v>3.7473</v>
       </c>
       <c r="D2" t="n">
-        <v>2.368</v>
+        <v>2.3162</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5731</v>
+        <v>6.4143</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2948</v>
+        <v>3.2217</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2783</v>
+        <v>3.1927</v>
       </c>
       <c r="H2" t="n">
-        <v>5.9766</v>
+        <v>5.6529</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2273</v>
+        <v>3.1739</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2783</v>
+        <v>3.1927</v>
       </c>
       <c r="K2" t="n">
         <v>108</v>
@@ -529,7 +529,7 @@
         <v>101</v>
       </c>
       <c r="M2" t="n">
-        <v>6.5056</v>
+        <v>6.3666</v>
       </c>
       <c r="N2" t="n">
         <v>209</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5303</v>
+        <v>5.2984</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2308</v>
+        <v>3.0953</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8933</v>
+        <v>1.8079</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5303</v>
+        <v>5.2984</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3784</v>
+        <v>4.2001</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1519</v>
+        <v>1.0983</v>
       </c>
       <c r="H3" t="n">
-        <v>9.5518</v>
+        <v>9.3263</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1579</v>
+        <v>5.2364</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1519</v>
+        <v>1.0983</v>
       </c>
       <c r="K3" t="n">
         <v>188</v>
@@ -575,7 +575,7 @@
         <v>91</v>
       </c>
       <c r="M3" t="n">
-        <v>6.309799999999999</v>
+        <v>6.3347</v>
       </c>
       <c r="N3" t="n">
         <v>279</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3397</v>
+        <v>5.227</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1195</v>
+        <v>3.0536</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8065</v>
+        <v>1.7754</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3397</v>
+        <v>5.227</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5909</v>
+        <v>3.4819</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7488</v>
+        <v>1.7451</v>
       </c>
       <c r="H4" t="n">
-        <v>6.9534</v>
+        <v>6.6301</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7548</v>
+        <v>3.7226</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7488</v>
+        <v>1.7451</v>
       </c>
       <c r="K4" t="n">
         <v>172</v>
@@ -621,7 +621,7 @@
         <v>151</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5036</v>
+        <v>5.4677</v>
       </c>
       <c r="N4" t="n">
         <v>323</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.9642</v>
+        <v>4.7773</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9001</v>
+        <v>2.7909</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6356</v>
+        <v>1.5705</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9642</v>
+        <v>4.7773</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5477</v>
+        <v>3.4161</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4165</v>
+        <v>1.3612</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8108</v>
+        <v>6.3829</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6778</v>
+        <v>3.5838</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4165</v>
+        <v>1.3612</v>
       </c>
       <c r="K5" t="n">
         <v>172</v>
@@ -667,7 +667,7 @@
         <v>151</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0943</v>
+        <v>4.945</v>
       </c>
       <c r="N5" t="n">
         <v>323</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4975</v>
+        <v>4.5575</v>
       </c>
       <c r="C6" t="n">
-        <v>2.6275</v>
+        <v>2.6625</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4232</v>
+        <v>1.4704</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4975</v>
+        <v>4.5575</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7574</v>
+        <v>2.7991</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7401</v>
+        <v>1.7584</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2036</v>
+        <v>4.0665</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2699</v>
+        <v>2.2832</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7401</v>
+        <v>1.7584</v>
       </c>
       <c r="K6" t="n">
         <v>108</v>
@@ -713,7 +713,7 @@
         <v>101</v>
       </c>
       <c r="M6" t="n">
-        <v>4.01</v>
+        <v>4.0416</v>
       </c>
       <c r="N6" t="n">
         <v>209</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9984</v>
+        <v>3.8324</v>
       </c>
       <c r="C7" t="n">
-        <v>2.3359</v>
+        <v>2.2389</v>
       </c>
       <c r="D7" t="n">
-        <v>1.196</v>
+        <v>1.1401</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9984</v>
+        <v>3.8324</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0967</v>
+        <v>3.0235</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9016999999999999</v>
+        <v>0.8089</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3229</v>
+        <v>4.9087</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8743</v>
+        <v>2.7561</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9016999999999999</v>
+        <v>0.8089</v>
       </c>
       <c r="K7" t="n">
         <v>172</v>
@@ -759,7 +759,7 @@
         <v>151</v>
       </c>
       <c r="M7" t="n">
-        <v>3.776</v>
+        <v>3.565</v>
       </c>
       <c r="N7" t="n">
         <v>323</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8934</v>
+        <v>3.6942</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2745</v>
+        <v>2.1582</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1482</v>
+        <v>1.0771</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8934</v>
+        <v>3.6942</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2938</v>
+        <v>3.2088</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5996</v>
+        <v>0.4854</v>
       </c>
       <c r="H8" t="n">
-        <v>5.9732</v>
+        <v>5.6048</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2255</v>
+        <v>3.1469</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5996</v>
+        <v>0.4854</v>
       </c>
       <c r="K8" t="n">
         <v>188</v>
@@ -805,7 +805,7 @@
         <v>91</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8251</v>
+        <v>3.6323</v>
       </c>
       <c r="N8" t="n">
         <v>279</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.614</v>
+        <v>3.6702</v>
       </c>
       <c r="C9" t="n">
-        <v>2.1113</v>
+        <v>2.1441</v>
       </c>
       <c r="D9" t="n">
-        <v>1.021</v>
+        <v>1.0662</v>
       </c>
       <c r="E9" t="n">
-        <v>3.614</v>
+        <v>3.6702</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7476</v>
+        <v>2.4469</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8663999999999999</v>
+        <v>1.2233</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1712</v>
+        <v>2.7442</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2524</v>
+        <v>1.5408</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8663999999999999</v>
+        <v>1.2233</v>
       </c>
       <c r="K9" t="n">
-        <v>188</v>
+        <v>108</v>
       </c>
       <c r="L9" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1188</v>
+        <v>2.7641</v>
       </c>
       <c r="N9" t="n">
-        <v>279</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5265</v>
+        <v>3.526</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0602</v>
+        <v>2.0599</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9811</v>
+        <v>1.0005</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5265</v>
+        <v>3.526</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3</v>
+        <v>2.7818</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2265</v>
+        <v>0.7442</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6945</v>
+        <v>4.0016</v>
       </c>
       <c r="I10" t="n">
-        <v>1.455</v>
+        <v>2.2468</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2265</v>
+        <v>0.7442</v>
       </c>
       <c r="K10" t="n">
-        <v>108</v>
+        <v>188</v>
       </c>
       <c r="L10" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6815</v>
+        <v>2.991</v>
       </c>
       <c r="N10" t="n">
-        <v>209</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9744</v>
+        <v>2.8398</v>
       </c>
       <c r="C11" t="n">
-        <v>1.7377</v>
+        <v>1.659</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7298</v>
+        <v>0.6879</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9744</v>
+        <v>2.8398</v>
       </c>
       <c r="F11" t="n">
-        <v>3.5976</v>
+        <v>3.4695</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6232</v>
+        <v>-0.6297</v>
       </c>
       <c r="H11" t="n">
-        <v>6.9757</v>
+        <v>6.5833</v>
       </c>
       <c r="I11" t="n">
-        <v>3.7668</v>
+        <v>3.6963</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6232</v>
+        <v>-0.6297</v>
       </c>
       <c r="K11" t="n">
         <v>165</v>
@@ -943,7 +943,7 @@
         <v>41</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1436</v>
+        <v>3.0666</v>
       </c>
       <c r="N11" t="n">
         <v>206</v>
@@ -952,369 +952,369 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.942</v>
+        <v>2.801</v>
       </c>
       <c r="C12" t="n">
-        <v>1.7187</v>
+        <v>1.6364</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7151</v>
+        <v>0.6702</v>
       </c>
       <c r="E12" t="n">
-        <v>2.942</v>
+        <v>2.801</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6371</v>
+        <v>2.801</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3049</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6371</v>
+        <v>3.469</v>
       </c>
       <c r="I12" t="n">
-        <v>0.884</v>
+        <v>3.469</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3049</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L12" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1889</v>
+        <v>3.469</v>
       </c>
       <c r="N12" t="n">
-        <v>209</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8632</v>
+        <v>2.7962</v>
       </c>
       <c r="C13" t="n">
-        <v>1.6727</v>
+        <v>1.6335</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6792</v>
+        <v>0.668</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8632</v>
+        <v>2.7962</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8632</v>
+        <v>1.4669</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.3293</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5418</v>
+        <v>1.4669</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5418</v>
+        <v>0.8236</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.3293</v>
       </c>
       <c r="K13" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5418</v>
+        <v>2.1529</v>
       </c>
       <c r="N13" t="n">
-        <v>105</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.737</v>
+        <v>2.7104</v>
       </c>
       <c r="C14" t="n">
-        <v>1.599</v>
+        <v>1.5834</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6217</v>
+        <v>0.6289</v>
       </c>
       <c r="E14" t="n">
-        <v>2.737</v>
+        <v>2.7104</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0582</v>
+        <v>2.5447</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3212</v>
+        <v>0.1657</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1958</v>
+        <v>3.1113</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8057</v>
+        <v>1.7469</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3212</v>
+        <v>0.1657</v>
       </c>
       <c r="K14" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="L14" t="n">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4845</v>
+        <v>1.9126</v>
       </c>
       <c r="N14" t="n">
-        <v>206</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6288</v>
+        <v>2.6749</v>
       </c>
       <c r="C15" t="n">
-        <v>1.5358</v>
+        <v>1.5627</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5725</v>
+        <v>0.6128</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6288</v>
+        <v>2.6749</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6288</v>
+        <v>2.9783</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.3034</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0287</v>
+        <v>4.7392</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0287</v>
+        <v>2.6609</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.3034</v>
       </c>
       <c r="K15" t="n">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0287</v>
+        <v>2.3575</v>
       </c>
       <c r="N15" t="n">
-        <v>127</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6197</v>
+        <v>2.5394</v>
       </c>
       <c r="C16" t="n">
-        <v>1.5304</v>
+        <v>1.4835</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5683</v>
+        <v>0.551</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6197</v>
+        <v>2.5394</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4861</v>
+        <v>2.5394</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1336</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3084</v>
+        <v>2.8694</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7865</v>
+        <v>2.8694</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1336</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="L16" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9201</v>
+        <v>2.8694</v>
       </c>
       <c r="N16" t="n">
-        <v>323</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.5663</v>
+        <v>2.4895</v>
       </c>
       <c r="C17" t="n">
-        <v>1.4992</v>
+        <v>1.4544</v>
       </c>
       <c r="D17" t="n">
-        <v>0.544</v>
+        <v>0.5283</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5663</v>
+        <v>2.4895</v>
       </c>
       <c r="F17" t="n">
-        <v>3.5663</v>
+        <v>2.4895</v>
       </c>
       <c r="G17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>6.8725</v>
+        <v>2.7551</v>
       </c>
       <c r="I17" t="n">
-        <v>3.7111</v>
+        <v>2.8287</v>
       </c>
       <c r="J17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="L17" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7111</v>
+        <v>2.8287</v>
       </c>
       <c r="N17" t="n">
-        <v>206</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.5642</v>
+        <v>2.451</v>
       </c>
       <c r="C18" t="n">
-        <v>1.498</v>
+        <v>1.4319</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5431</v>
+        <v>0.5108</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5642</v>
+        <v>2.451</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0274</v>
+        <v>3.451</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5368000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0274</v>
+        <v>6.5138</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0948</v>
+        <v>3.6573</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5368000000000001</v>
+        <v>-1</v>
       </c>
       <c r="K18" t="n">
-        <v>47</v>
+        <v>165</v>
       </c>
       <c r="L18" t="n">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6316</v>
+        <v>2.6573</v>
       </c>
       <c r="N18" t="n">
-        <v>148</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.5594</v>
+        <v>2.4407</v>
       </c>
       <c r="C19" t="n">
-        <v>1.4952</v>
+        <v>1.4259</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5409</v>
+        <v>0.5061</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5594</v>
+        <v>2.4407</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5594</v>
+        <v>1.9216</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.5191</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8769</v>
+        <v>1.9216</v>
       </c>
       <c r="I19" t="n">
-        <v>2.951</v>
+        <v>1.0789</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.5191</v>
       </c>
       <c r="K19" t="n">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M19" t="n">
-        <v>2.951</v>
+        <v>1.598</v>
       </c>
       <c r="N19" t="n">
-        <v>130</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.3628</v>
+        <v>2.2984</v>
       </c>
       <c r="C20" t="n">
-        <v>1.3804</v>
+        <v>1.3427</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4514</v>
+        <v>0.4412</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3628</v>
+        <v>2.2984</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3628</v>
+        <v>2.2984</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4466</v>
+        <v>2.317</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4466</v>
+        <v>2.317</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.4466</v>
+        <v>2.317</v>
       </c>
       <c r="N20" t="n">
         <v>127</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.1009</v>
+        <v>2.2218</v>
       </c>
       <c r="C21" t="n">
-        <v>1.2274</v>
+        <v>1.298</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3322</v>
+        <v>0.4063</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1009</v>
+        <v>2.2218</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3689</v>
+        <v>2.4189</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.268</v>
+        <v>-0.1971</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9217</v>
+        <v>2.639</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5777</v>
+        <v>1.4817</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.268</v>
+        <v>-0.1971</v>
       </c>
       <c r="K21" t="n">
         <v>165</v>
@@ -1403,7 +1403,7 @@
         <v>41</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3097</v>
+        <v>1.2846</v>
       </c>
       <c r="N21" t="n">
         <v>206</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0113</v>
+        <v>2.0194</v>
       </c>
       <c r="C22" t="n">
-        <v>1.175</v>
+        <v>1.1797</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2914</v>
+        <v>0.3141</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0113</v>
+        <v>2.0194</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0113</v>
+        <v>1.2921</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0113</v>
+        <v>1.2921</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0113</v>
+        <v>0.7255</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M22" t="n">
-        <v>2.0113</v>
+        <v>1.4528</v>
       </c>
       <c r="N22" t="n">
-        <v>111</v>
+        <v>323</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.9769</v>
+        <v>1.9414</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1549</v>
+        <v>1.1342</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2757</v>
+        <v>0.2786</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9769</v>
+        <v>1.9414</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2872</v>
+        <v>1.9414</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6897</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2872</v>
+        <v>1.9414</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6951000000000001</v>
+        <v>1.9414</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6897</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L23" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3848</v>
+        <v>1.9414</v>
       </c>
       <c r="N23" t="n">
-        <v>323</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9044</v>
+        <v>1.7313</v>
       </c>
       <c r="C24" t="n">
-        <v>1.1126</v>
+        <v>1.0114</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2427</v>
+        <v>0.1829</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9044</v>
+        <v>1.7313</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9044</v>
+        <v>1.7313</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9044</v>
+        <v>1.7313</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9044</v>
+        <v>1.7313</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9044</v>
+        <v>1.7313</v>
       </c>
       <c r="N24" t="n">
         <v>124</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.7784</v>
+        <v>1.73</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0389</v>
+        <v>1.0107</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1854</v>
+        <v>0.1823</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7784</v>
+        <v>1.73</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7784</v>
+        <v>1.73</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7784</v>
+        <v>1.73</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8242</v>
+        <v>1.7763</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.8242</v>
+        <v>1.7763</v>
       </c>
       <c r="N25" t="n">
         <v>130</v>
@@ -1596,139 +1596,139 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6738</v>
+        <v>1.6206</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9778</v>
+        <v>0.9468</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1377</v>
+        <v>0.1325</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6738</v>
+        <v>1.6206</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6738</v>
+        <v>1.6206</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6738</v>
+        <v>1.6206</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6738</v>
+        <v>1.6206</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.6738</v>
+        <v>1.6206</v>
       </c>
       <c r="N26" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6109</v>
+        <v>1.6096</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9411</v>
+        <v>0.9403</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1091</v>
+        <v>0.1275</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6109</v>
+        <v>1.6096</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6109</v>
+        <v>1.6096</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6109</v>
+        <v>1.6096</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6109</v>
+        <v>1.6096</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6109</v>
+        <v>1.6096</v>
       </c>
       <c r="N27" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5946</v>
+        <v>1.4379</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9316</v>
+        <v>0.84</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1017</v>
+        <v>0.0492</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5946</v>
+        <v>1.4379</v>
       </c>
       <c r="F28" t="n">
-        <v>1.5946</v>
+        <v>1.4379</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.5946</v>
+        <v>1.4379</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5946</v>
+        <v>1.4379</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.5946</v>
+        <v>1.4379</v>
       </c>
       <c r="N28" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.3772</v>
+        <v>1.3569</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8046</v>
+        <v>0.7927</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0027</v>
+        <v>0.0123</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3772</v>
+        <v>1.3569</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3772</v>
+        <v>1.3569</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.3772</v>
+        <v>1.3569</v>
       </c>
       <c r="I29" t="n">
-        <v>1.3772</v>
+        <v>1.3569</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3772</v>
+        <v>1.3569</v>
       </c>
       <c r="N29" t="n">
         <v>124</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3152</v>
+        <v>1.1755</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7683</v>
+        <v>0.6867</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0255</v>
+        <v>-0.0703</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3152</v>
+        <v>1.1755</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3152</v>
+        <v>1.1755</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.3152</v>
+        <v>1.1755</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3491</v>
+        <v>1.2069</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.3491</v>
+        <v>1.2069</v>
       </c>
       <c r="N30" t="n">
         <v>192</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.1518</v>
+        <v>1.1476</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6704</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0999</v>
+        <v>-0.083</v>
       </c>
       <c r="E31" t="n">
-        <v>1.1518</v>
+        <v>1.1476</v>
       </c>
       <c r="F31" t="n">
-        <v>1.1518</v>
+        <v>1.1476</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1518</v>
+        <v>1.1476</v>
       </c>
       <c r="I31" t="n">
-        <v>1.1518</v>
+        <v>1.1476</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1518</v>
+        <v>1.1476</v>
       </c>
       <c r="N31" t="n">
         <v>95</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1133</v>
+        <v>1.1082</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6504</v>
+        <v>0.6474</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1174</v>
+        <v>-0.1009</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1133</v>
+        <v>1.1082</v>
       </c>
       <c r="F32" t="n">
-        <v>1.1133</v>
+        <v>1.1082</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.1133</v>
+        <v>1.1082</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1133</v>
+        <v>1.1082</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1133</v>
+        <v>1.1082</v>
       </c>
       <c r="N32" t="n">
         <v>111</v>
@@ -1918,185 +1918,185 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>starix</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.0984</v>
+        <v>1.0722</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6417</v>
+        <v>0.6264</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1242</v>
+        <v>-0.1173</v>
       </c>
       <c r="E33" t="n">
-        <v>1.0984</v>
+        <v>1.0722</v>
       </c>
       <c r="F33" t="n">
-        <v>1.0984</v>
+        <v>1.0722</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.0984</v>
+        <v>1.0722</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0984</v>
+        <v>1.0722</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.0984</v>
+        <v>1.0722</v>
       </c>
       <c r="N33" t="n">
-        <v>61</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>starix</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.0764</v>
+        <v>1.0617</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6288</v>
+        <v>0.6202</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1342</v>
+        <v>-0.1221</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0764</v>
+        <v>1.0617</v>
       </c>
       <c r="F34" t="n">
-        <v>1.0764</v>
+        <v>1.0617</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.0764</v>
+        <v>1.0617</v>
       </c>
       <c r="I34" t="n">
-        <v>1.0764</v>
+        <v>1.0617</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.0764</v>
+        <v>1.0617</v>
       </c>
       <c r="N34" t="n">
-        <v>95</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.013</v>
+        <v>0.9536</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5918</v>
+        <v>0.5571</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1631</v>
+        <v>-0.1714</v>
       </c>
       <c r="E35" t="n">
-        <v>1.013</v>
+        <v>0.9536</v>
       </c>
       <c r="F35" t="n">
-        <v>1.013</v>
+        <v>0.9536</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.013</v>
+        <v>0.9536</v>
       </c>
       <c r="I35" t="n">
-        <v>1.013</v>
+        <v>0.9536</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.013</v>
+        <v>0.9536</v>
       </c>
       <c r="N35" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9607</v>
+        <v>0.9403</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5612</v>
+        <v>0.5493</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1869</v>
+        <v>-0.1774</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9607</v>
+        <v>0.9403</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9607</v>
+        <v>0.9403</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9607</v>
+        <v>0.9403</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9607</v>
+        <v>0.9403</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9607</v>
+        <v>0.9403</v>
       </c>
       <c r="N36" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8652</v>
+        <v>0.8374</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4892</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2303</v>
+        <v>-0.2243</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8652</v>
+        <v>0.8374</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8652</v>
+        <v>0.8374</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8652</v>
+        <v>0.8374</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8652</v>
+        <v>0.8374</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8652</v>
+        <v>0.8374</v>
       </c>
       <c r="N37" t="n">
         <v>95</v>
@@ -2148,47 +2148,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.7803</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4962</v>
+        <v>0.4559</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2376</v>
+        <v>-0.2503</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.7803</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.7803</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.7803</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.7803</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.7803</v>
       </c>
       <c r="N38" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8168</v>
+        <v>0.7713</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4772</v>
+        <v>0.4506</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2524</v>
+        <v>-0.2544</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8168</v>
+        <v>0.7713</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8168</v>
+        <v>0.7713</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8168</v>
+        <v>0.7713</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8168</v>
+        <v>0.7713</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8168</v>
+        <v>0.7713</v>
       </c>
       <c r="N39" t="n">
         <v>110</v>
@@ -2240,262 +2240,262 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7975</v>
+        <v>0.7341</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4659</v>
+        <v>0.4289</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2612</v>
+        <v>-0.2714</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7975</v>
+        <v>0.7341</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7975</v>
+        <v>0.7341</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7975</v>
+        <v>0.7341</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7975</v>
+        <v>0.7341</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7975</v>
+        <v>0.7341</v>
       </c>
       <c r="N40" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pauf</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6865</v>
+        <v>0.5697</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4011</v>
+        <v>0.3328</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3117</v>
+        <v>-0.3463</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6865</v>
+        <v>0.5697</v>
       </c>
       <c r="F41" t="n">
-        <v>1.0559</v>
+        <v>0.5697</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.3694</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.0559</v>
+        <v>0.5697</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5702</v>
+        <v>0.585</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.3694</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>188</v>
+        <v>130</v>
       </c>
       <c r="L41" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2008</v>
+        <v>0.585</v>
       </c>
       <c r="N41" t="n">
-        <v>279</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>pauf</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6424</v>
+        <v>0.5462</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3753</v>
+        <v>0.3191</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3318</v>
+        <v>-0.357</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6424</v>
+        <v>0.5462</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6424</v>
+        <v>0.8738</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-0.3276</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6424</v>
+        <v>0.8738</v>
       </c>
       <c r="I42" t="n">
-        <v>0.659</v>
+        <v>0.4906</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-0.3276</v>
       </c>
       <c r="K42" t="n">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M42" t="n">
-        <v>0.659</v>
+        <v>0.163</v>
       </c>
       <c r="N42" t="n">
-        <v>130</v>
+        <v>279</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5067</v>
+        <v>0.5111</v>
       </c>
       <c r="C43" t="n">
-        <v>0.296</v>
+        <v>0.2986</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3935</v>
+        <v>-0.373</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5067</v>
+        <v>0.5111</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5067</v>
+        <v>0.5111</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5067</v>
+        <v>0.5111</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5198</v>
+        <v>0.5111</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5198</v>
+        <v>0.5111</v>
       </c>
       <c r="N43" t="n">
-        <v>130</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.487</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2953</v>
+        <v>0.2845</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3941</v>
+        <v>-0.3839</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.487</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.487</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.487</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="N44" t="n">
-        <v>111</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4785</v>
+        <v>0.4602</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2795</v>
+        <v>0.2689</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4064</v>
+        <v>-0.3961</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4785</v>
+        <v>0.4602</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4785</v>
+        <v>0.4602</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.4785</v>
+        <v>0.4602</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4785</v>
+        <v>0.4602</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4785</v>
+        <v>0.4602</v>
       </c>
       <c r="N45" t="n">
         <v>127</v>
@@ -2516,369 +2516,369 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4349</v>
+        <v>0.3751</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2541</v>
+        <v>0.2191</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4262</v>
+        <v>-0.4349</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4349</v>
+        <v>0.3751</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4349</v>
+        <v>0.3751</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4349</v>
+        <v>0.3751</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4349</v>
+        <v>0.3751</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.4349</v>
+        <v>0.3751</v>
       </c>
       <c r="N46" t="n">
-        <v>127</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4203</v>
+        <v>0.3568</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2455</v>
+        <v>0.2084</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4329</v>
+        <v>-0.4432</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4203</v>
+        <v>0.3568</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4203</v>
+        <v>0.3568</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4203</v>
+        <v>0.3568</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4203</v>
+        <v>0.3568</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4203</v>
+        <v>0.3568</v>
       </c>
       <c r="N47" t="n">
-        <v>52</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.3028</v>
+        <v>0.3493</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1769</v>
+        <v>0.2041</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4864</v>
+        <v>-0.4467</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3028</v>
+        <v>0.3493</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3028</v>
+        <v>0.3493</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3028</v>
+        <v>0.3493</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3028</v>
+        <v>0.3493</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.3028</v>
+        <v>0.3493</v>
       </c>
       <c r="N48" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.2966</v>
+        <v>0.297</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1733</v>
+        <v>0.1735</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4892</v>
+        <v>-0.4705</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2966</v>
+        <v>0.297</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2966</v>
+        <v>0.297</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2966</v>
+        <v>0.297</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2966</v>
+        <v>0.297</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.2966</v>
+        <v>0.297</v>
       </c>
       <c r="N49" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.2786</v>
+        <v>0.2496</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1628</v>
+        <v>0.1458</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4974</v>
+        <v>-0.4921</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2786</v>
+        <v>0.2496</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2786</v>
+        <v>0.2496</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2786</v>
+        <v>0.2496</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2786</v>
+        <v>0.2496</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.2786</v>
+        <v>0.2496</v>
       </c>
       <c r="N50" t="n">
-        <v>52</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.2562</v>
+        <v>0.229</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1497</v>
+        <v>0.1338</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2562</v>
+        <v>0.229</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2562</v>
+        <v>0.229</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2562</v>
+        <v>0.229</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2562</v>
+        <v>0.229</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2562</v>
+        <v>0.229</v>
       </c>
       <c r="N51" t="n">
-        <v>127</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.2131</v>
+        <v>0.2216</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1245</v>
+        <v>0.1295</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5272</v>
+        <v>-0.5048</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2131</v>
+        <v>0.2216</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2131</v>
+        <v>0.2216</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2131</v>
+        <v>0.2216</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2131</v>
+        <v>0.2216</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.2131</v>
+        <v>0.2216</v>
       </c>
       <c r="N52" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.2018</v>
+        <v>0.203</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1179</v>
+        <v>0.1186</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5323</v>
+        <v>-0.5133</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2018</v>
+        <v>0.203</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2018</v>
+        <v>0.203</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2018</v>
+        <v>0.203</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2018</v>
+        <v>0.203</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.2018</v>
+        <v>0.203</v>
       </c>
       <c r="N53" t="n">
-        <v>49</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.18</v>
+        <v>0.1706</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1052</v>
+        <v>0.0997</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5423</v>
+        <v>-0.5281</v>
       </c>
       <c r="E54" t="n">
-        <v>0.18</v>
+        <v>0.1706</v>
       </c>
       <c r="F54" t="n">
-        <v>0.18</v>
+        <v>0.1706</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.18</v>
+        <v>0.1706</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1846</v>
+        <v>0.1752</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1846</v>
+        <v>0.1752</v>
       </c>
       <c r="N54" t="n">
         <v>192</v>
@@ -2930,231 +2930,231 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.1374</v>
+        <v>0.153</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0803</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5617</v>
+        <v>-0.5361</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1374</v>
+        <v>0.153</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1374</v>
+        <v>0.153</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1374</v>
+        <v>0.153</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1374</v>
+        <v>0.153</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1374</v>
+        <v>0.153</v>
       </c>
       <c r="N55" t="n">
-        <v>111</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.0214</v>
+        <v>0.0839</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0125</v>
+        <v>0.049</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6145</v>
+        <v>-0.5676</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0214</v>
+        <v>0.0839</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0214</v>
+        <v>0.0839</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0214</v>
+        <v>0.0839</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0214</v>
+        <v>0.0861</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>52</v>
+        <v>192</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.0214</v>
+        <v>0.0861</v>
       </c>
       <c r="N56" t="n">
-        <v>52</v>
+        <v>192</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.0083</v>
+        <v>0.0276</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0048</v>
+        <v>0.0161</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6204</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0083</v>
+        <v>0.0276</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0083</v>
+        <v>0.0276</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0083</v>
+        <v>0.0276</v>
       </c>
       <c r="I57" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0276</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>192</v>
+        <v>105</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0276</v>
       </c>
       <c r="N57" t="n">
-        <v>192</v>
+        <v>105</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.0062</v>
+        <v>-0.0065</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0036</v>
+        <v>-0.0038</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6214</v>
+        <v>-0.6087</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0062</v>
+        <v>-0.0065</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0062</v>
+        <v>-0.0065</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0062</v>
+        <v>-0.0065</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0064</v>
+        <v>-0.0065</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.0064</v>
+        <v>-0.0065</v>
       </c>
       <c r="N58" t="n">
-        <v>130</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.0058</v>
+        <v>-0.0335</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.0034</v>
+        <v>-0.0196</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6268</v>
+        <v>-0.621</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.0058</v>
+        <v>-0.0335</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.0058</v>
+        <v>-0.0335</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.0058</v>
+        <v>-0.0335</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0058</v>
+        <v>-0.0344</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.0058</v>
+        <v>-0.0344</v>
       </c>
       <c r="N59" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60">
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.0828</v>
+        <v>-0.1259</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0484</v>
+        <v>-0.0736</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6619</v>
+        <v>-0.6631</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.0828</v>
+        <v>-0.1259</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.0828</v>
+        <v>-0.1259</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.0828</v>
+        <v>-0.1259</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0828</v>
+        <v>-0.1259</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.0828</v>
+        <v>-0.1259</v>
       </c>
       <c r="N60" t="n">
         <v>49</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.1447</v>
+        <v>-0.1571</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6901</v>
+        <v>-0.6774</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.1447</v>
+        <v>-0.1571</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.1447</v>
+        <v>-0.1571</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.1447</v>
+        <v>-0.1571</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1447</v>
+        <v>-0.1571</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.1447</v>
+        <v>-0.1571</v>
       </c>
       <c r="N61" t="n">
         <v>70</v>
@@ -3256,28 +3256,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.2017</v>
+        <v>-0.1743</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1178</v>
+        <v>-0.1018</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.716</v>
+        <v>-0.6852</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.2017</v>
+        <v>-0.1743</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.2017</v>
+        <v>-0.1743</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.2017</v>
+        <v>-0.1743</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2017</v>
+        <v>-0.1743</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.2017</v>
+        <v>-0.1743</v>
       </c>
       <c r="N62" t="n">
         <v>70</v>
@@ -3302,28 +3302,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.2045</v>
+        <v>-0.2252</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1195</v>
+        <v>-0.1316</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7173</v>
+        <v>-0.7084</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.2045</v>
+        <v>-0.2252</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.2045</v>
+        <v>-0.2252</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.2045</v>
+        <v>-0.2252</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2045</v>
+        <v>-0.2252</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.2045</v>
+        <v>-0.2252</v>
       </c>
       <c r="N63" t="n">
         <v>70</v>
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.2519</v>
+        <v>-0.2919</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1472</v>
+        <v>-0.1705</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7389</v>
+        <v>-0.7388</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.2519</v>
+        <v>-0.2919</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.2519</v>
+        <v>-0.2919</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.2519</v>
+        <v>-0.2919</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2519</v>
+        <v>-0.2919</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.2519</v>
+        <v>-0.2919</v>
       </c>
       <c r="N64" t="n">
         <v>42</v>
@@ -3390,400 +3390,400 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.3004</v>
+        <v>-0.3125</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1755</v>
+        <v>-0.1826</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.761</v>
+        <v>-0.7481</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.3004</v>
+        <v>-0.3125</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.3004</v>
+        <v>-0.3125</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.3004</v>
+        <v>-0.3125</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3004</v>
+        <v>-0.3209</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.3004</v>
+        <v>-0.3209</v>
       </c>
       <c r="N65" t="n">
-        <v>105</v>
+        <v>192</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>SZPERO</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.3122</v>
+        <v>-0.3515</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1824</v>
+        <v>-0.2053</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7663</v>
+        <v>-0.7659</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.3122</v>
+        <v>-0.3515</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.3122</v>
+        <v>-0.3515</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.3122</v>
+        <v>-0.3515</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3122</v>
+        <v>-0.3515</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.3122</v>
+        <v>-0.3515</v>
       </c>
       <c r="N66" t="n">
-        <v>124</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SZPERO</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.3458</v>
+        <v>-0.3551</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.202</v>
+        <v>-0.2075</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7816</v>
+        <v>-0.7675999999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.3458</v>
+        <v>-0.3551</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.3458</v>
+        <v>-0.3551</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.3458</v>
+        <v>-0.3551</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.3458</v>
+        <v>-0.3551</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.3458</v>
+        <v>-0.3551</v>
       </c>
       <c r="N67" t="n">
-        <v>49</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.3514</v>
+        <v>-0.3633</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2053</v>
+        <v>-0.2122</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7842</v>
+        <v>-0.7713</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.3514</v>
+        <v>-0.3633</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.3514</v>
+        <v>-0.3633</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.3514</v>
+        <v>-0.3633</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3514</v>
+        <v>-0.3633</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.3514</v>
+        <v>-0.3633</v>
       </c>
       <c r="N68" t="n">
-        <v>124</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.3608</v>
+        <v>-0.3838</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2108</v>
+        <v>-0.2242</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7884</v>
+        <v>-0.7806</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.3608</v>
+        <v>-0.3838</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.3608</v>
+        <v>-0.3838</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.3608</v>
+        <v>-0.3838</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3701</v>
+        <v>-0.3838</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>192</v>
+        <v>105</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.3701</v>
+        <v>-0.3838</v>
       </c>
       <c r="N69" t="n">
-        <v>192</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.3759</v>
+        <v>-0.3968</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.2196</v>
+        <v>-0.2318</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.7953</v>
+        <v>-0.7865</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.3759</v>
+        <v>-0.3968</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.3759</v>
+        <v>-0.3968</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.3759</v>
+        <v>-0.3968</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3759</v>
+        <v>-0.3968</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.3759</v>
+        <v>-0.3968</v>
       </c>
       <c r="N70" t="n">
-        <v>105</v>
+        <v>124</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.4042</v>
+        <v>-0.3993</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.2361</v>
+        <v>-0.2333</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8082</v>
+        <v>-0.7877</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.4042</v>
+        <v>-0.3993</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.4042</v>
+        <v>-0.3993</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.4042</v>
+        <v>-0.3993</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4042</v>
+        <v>-0.3993</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.4042</v>
+        <v>-0.3993</v>
       </c>
       <c r="N71" t="n">
-        <v>42</v>
+        <v>105</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>innocent</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.4544</v>
+        <v>-0.4331</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.2655</v>
+        <v>-0.253</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.8031</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.4544</v>
+        <v>-0.4331</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.4544</v>
+        <v>-0.4331</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.4544</v>
+        <v>-0.4331</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.4544</v>
+        <v>-0.4331</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.4544</v>
+        <v>-0.4331</v>
       </c>
       <c r="N72" t="n">
-        <v>124</v>
+        <v>49</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>innocent</t>
+          <t>mouz</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.4682</v>
+        <v>-0.4634</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.2735</v>
+        <v>-0.2707</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8373</v>
+        <v>-0.8169</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.4682</v>
+        <v>-0.4634</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.4682</v>
+        <v>-0.4634</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.4682</v>
+        <v>-0.4634</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.4682</v>
+        <v>-0.4634</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.4682</v>
+        <v>-0.4634</v>
       </c>
       <c r="N73" t="n">
         <v>49</v>
@@ -3804,47 +3804,47 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>mouz</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.4977</v>
+        <v>-0.4944</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.2908</v>
+        <v>-0.2888</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8508</v>
+        <v>-0.831</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.4977</v>
+        <v>-0.4944</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.4977</v>
+        <v>-0.4944</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.4977</v>
+        <v>-0.4944</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.4977</v>
+        <v>-0.4944</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.4977</v>
+        <v>-0.4944</v>
       </c>
       <c r="N74" t="n">
-        <v>49</v>
+        <v>124</v>
       </c>
     </row>
     <row r="75">
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.5366</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.3135</v>
+        <v>-0.3042</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.8685</v>
+        <v>-0.843</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.5366</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.5366</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.5366</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5366</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.5366</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="N75" t="n">
         <v>110</v>
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.5677</v>
+        <v>-0.5379</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.3317</v>
+        <v>-0.3142</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.8508</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.5677</v>
+        <v>-0.5379</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.5677</v>
+        <v>-0.5379</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.5677</v>
+        <v>-0.5379</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5677</v>
+        <v>-0.5379</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.5677</v>
+        <v>-0.5379</v>
       </c>
       <c r="N76" t="n">
         <v>42</v>
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.6484</v>
+        <v>-0.6382</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.3788</v>
+        <v>-0.3728</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.9194</v>
+        <v>-0.8965</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.6484</v>
+        <v>-0.6382</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.6484</v>
+        <v>-0.6382</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.6484</v>
+        <v>-0.6382</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.6484</v>
+        <v>-0.6382</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.6484</v>
+        <v>-0.6382</v>
       </c>
       <c r="N77" t="n">
         <v>42</v>
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.7766</v>
+        <v>-0.7541</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.4537</v>
+        <v>-0.4405</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.9777</v>
+        <v>-0.9493</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.7766</v>
+        <v>-0.7541</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.7766</v>
+        <v>-0.7541</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.7766</v>
+        <v>-0.7541</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.7766</v>
+        <v>-0.7541</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.7766</v>
+        <v>-0.7541</v>
       </c>
       <c r="N78" t="n">
         <v>52</v>
@@ -4038,31 +4038,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.7916</v>
+        <v>-0.7719</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.4625</v>
+        <v>-0.4509</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.9846</v>
+        <v>-0.9574</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.7916</v>
+        <v>-0.7719</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.2532</v>
+        <v>-0.2907</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.5384</v>
+        <v>-0.4812</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.2532</v>
+        <v>-0.2907</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1367</v>
+        <v>-0.1632</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.5384</v>
+        <v>-0.4812</v>
       </c>
       <c r="K79" t="n">
         <v>188</v>
@@ -4071,7 +4071,7 @@
         <v>91</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.6751</v>
+        <v>-0.6444000000000001</v>
       </c>
       <c r="N79" t="n">
         <v>279</v>
@@ -4084,28 +4084,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.828</v>
+        <v>-0.8104</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.4837</v>
+        <v>-0.4734</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.0011</v>
+        <v>-0.975</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.828</v>
+        <v>-0.8104</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.828</v>
+        <v>-0.8104</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.828</v>
+        <v>-0.8104</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.828</v>
+        <v>-0.8104</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-0.828</v>
+        <v>-0.8104</v>
       </c>
       <c r="N80" t="n">
         <v>42</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-1.0397</v>
+        <v>-0.9273</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.5417</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.0975</v>
+        <v>-1.0282</v>
       </c>
       <c r="E81" t="n">
-        <v>-1.0397</v>
+        <v>-0.9273</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.0397</v>
+        <v>-0.9273</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.0397</v>
+        <v>-0.9273</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.0665</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-1.0665</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="N81" t="n">
         <v>192</v>
@@ -4176,31 +4176,31 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-4.4456</v>
+        <v>-4.2036</v>
       </c>
       <c r="C82" t="n">
-        <v>-2.5971</v>
+        <v>-2.4558</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.6479</v>
+        <v>-2.5207</v>
       </c>
       <c r="E82" t="n">
-        <v>-4.4456</v>
+        <v>-4.2036</v>
       </c>
       <c r="F82" t="n">
-        <v>-3.5839</v>
+        <v>-3.3573</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.8617</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>-3.5839</v>
+        <v>-3.3573</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.9353</v>
+        <v>-1.885</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.8617</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="K82" t="n">
         <v>165</v>
@@ -4209,7 +4209,7 @@
         <v>41</v>
       </c>
       <c r="M82" t="n">
-        <v>-2.797</v>
+        <v>-2.7313</v>
       </c>
       <c r="N82" t="n">
         <v>206</v>
@@ -4315,10 +4315,10 @@
         <v>1.09</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2425</v>
+        <v>0.1965</v>
       </c>
       <c r="J2" t="n">
-        <v>7.275</v>
+        <v>5.895</v>
       </c>
     </row>
     <row r="3">
@@ -4355,10 +4355,10 @@
         <v>0.97</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0554</v>
+        <v>-0.0443</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.662</v>
+        <v>-1.329</v>
       </c>
     </row>
     <row r="4">
@@ -4395,10 +4395,10 @@
         <v>0.95</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0829</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.487</v>
+        <v>-2.055</v>
       </c>
     </row>
     <row r="5">
@@ -4435,10 +4435,10 @@
         <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1313</v>
+        <v>-0.1131</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.939</v>
+        <v>-3.393</v>
       </c>
     </row>
     <row r="6">
@@ -4475,10 +4475,10 @@
         <v>0.83</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2176</v>
+        <v>-0.1972</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.528</v>
+        <v>-5.916</v>
       </c>
     </row>
     <row r="7">
@@ -4515,10 +4515,10 @@
         <v>1.22</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6091</v>
+        <v>0.5714</v>
       </c>
       <c r="J7" t="n">
-        <v>18.273</v>
+        <v>17.142</v>
       </c>
     </row>
     <row r="8">
@@ -4555,10 +4555,10 @@
         <v>1.18</v>
       </c>
       <c r="I8" t="n">
-        <v>0.519</v>
+        <v>0.4789</v>
       </c>
       <c r="J8" t="n">
-        <v>15.57</v>
+        <v>14.367</v>
       </c>
     </row>
     <row r="9">
@@ -4595,10 +4595,10 @@
         <v>1.11</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3512</v>
+        <v>0.3124</v>
       </c>
       <c r="J9" t="n">
-        <v>10.536</v>
+        <v>9.372</v>
       </c>
     </row>
     <row r="10">
@@ -4635,10 +4635,10 @@
         <v>0.97</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1503</v>
+        <v>-0.1194</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.509</v>
+        <v>-3.582</v>
       </c>
     </row>
     <row r="11">
@@ -4675,10 +4675,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2464</v>
+        <v>-0.2076</v>
       </c>
       <c r="J11" t="n">
-        <v>-7.392</v>
+        <v>-6.228</v>
       </c>
     </row>
     <row r="12">
@@ -4715,10 +4715,10 @@
         <v>1.27</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5574</v>
+        <v>0.4988</v>
       </c>
       <c r="J12" t="n">
-        <v>16.722</v>
+        <v>14.964</v>
       </c>
     </row>
     <row r="13">
@@ -4755,10 +4755,10 @@
         <v>1.02</v>
       </c>
       <c r="I13" t="n">
-        <v>0.077</v>
+        <v>0.0547</v>
       </c>
       <c r="J13" t="n">
-        <v>2.31</v>
+        <v>1.641</v>
       </c>
     </row>
     <row r="14">
@@ -4795,10 +4795,10 @@
         <v>0.95</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.523</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="15">
@@ -4835,10 +4835,10 @@
         <v>0.84</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2094</v>
+        <v>-0.1888</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.282</v>
+        <v>-5.664</v>
       </c>
     </row>
     <row r="16">
@@ -4875,10 +4875,10 @@
         <v>0.78</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2695</v>
+        <v>-0.2501</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.085000000000001</v>
+        <v>-7.503</v>
       </c>
     </row>
     <row r="17">
@@ -4915,10 +4915,10 @@
         <v>1.3</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7533</v>
+        <v>0.7261</v>
       </c>
       <c r="J17" t="n">
-        <v>22.599</v>
+        <v>21.783</v>
       </c>
     </row>
     <row r="18">
@@ -4955,10 +4955,10 @@
         <v>1.27</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6921</v>
+        <v>0.6619</v>
       </c>
       <c r="J18" t="n">
-        <v>20.763</v>
+        <v>19.857</v>
       </c>
     </row>
     <row r="19">
@@ -4995,10 +4995,10 @@
         <v>1.23</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6088</v>
+        <v>0.5758</v>
       </c>
       <c r="J19" t="n">
-        <v>18.264</v>
+        <v>17.274</v>
       </c>
     </row>
     <row r="20">
@@ -5035,10 +5035,10 @@
         <v>1.13</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3861</v>
+        <v>0.3518</v>
       </c>
       <c r="J20" t="n">
-        <v>11.583</v>
+        <v>10.554</v>
       </c>
     </row>
     <row r="21">
@@ -5075,10 +5075,10 @@
         <v>1.06</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>0.1719</v>
       </c>
       <c r="J21" t="n">
-        <v>6</v>
+        <v>5.157</v>
       </c>
     </row>
     <row r="22">
@@ -5115,10 +5115,10 @@
         <v>1.35</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.5698</v>
       </c>
       <c r="J22" t="n">
-        <v>17.949</v>
+        <v>17.094</v>
       </c>
     </row>
     <row r="23">
@@ -5155,10 +5155,10 @@
         <v>1.25</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4838</v>
+        <v>0.4407</v>
       </c>
       <c r="J23" t="n">
-        <v>14.514</v>
+        <v>13.221</v>
       </c>
     </row>
     <row r="24">
@@ -5195,10 +5195,10 @@
         <v>1.03</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0926</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>2.778</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="25">
@@ -5235,10 +5235,10 @@
         <v>0.92</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.13</v>
+        <v>-0.1108</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.9</v>
+        <v>-3.324</v>
       </c>
     </row>
     <row r="26">
@@ -5275,10 +5275,10 @@
         <v>0.83</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2289</v>
+        <v>-0.2087</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.867</v>
+        <v>-6.261</v>
       </c>
     </row>
     <row r="27">
@@ -5315,10 +5315,10 @@
         <v>1.65</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2184</v>
+        <v>1.2279</v>
       </c>
       <c r="J27" t="n">
-        <v>36.552</v>
+        <v>36.837</v>
       </c>
     </row>
     <row r="28">
@@ -5355,10 +5355,10 @@
         <v>1.09</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3107</v>
+        <v>0.2704</v>
       </c>
       <c r="J28" t="n">
-        <v>9.321</v>
+        <v>8.112</v>
       </c>
     </row>
     <row r="29">
@@ -5395,10 +5395,10 @@
         <v>0.95</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2039</v>
+        <v>-0.1686</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.117</v>
+        <v>-5.058</v>
       </c>
     </row>
     <row r="30">
@@ -5435,10 +5435,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5684</v>
+        <v>-0.5284</v>
       </c>
       <c r="J30" t="n">
-        <v>-17.052</v>
+        <v>-15.852</v>
       </c>
     </row>
     <row r="31">
@@ -5475,10 +5475,10 @@
         <v>0.6</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.0212</v>
+        <v>-1.0205</v>
       </c>
       <c r="J31" t="n">
-        <v>-30.636</v>
+        <v>-30.615</v>
       </c>
     </row>
     <row r="32">
@@ -5515,10 +5515,10 @@
         <v>1.53</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6113</v>
+        <v>0.5738</v>
       </c>
       <c r="J32" t="n">
-        <v>21.3955</v>
+        <v>20.083</v>
       </c>
     </row>
     <row r="33">
@@ -5555,10 +5555,10 @@
         <v>1.1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1773</v>
+        <v>0.1384</v>
       </c>
       <c r="J33" t="n">
-        <v>6.2055</v>
+        <v>4.844</v>
       </c>
     </row>
     <row r="34">
@@ -5595,10 +5595,10 @@
         <v>1.08</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1485</v>
+        <v>0.1142</v>
       </c>
       <c r="J34" t="n">
-        <v>5.1975</v>
+        <v>3.997</v>
       </c>
     </row>
     <row r="35">
@@ -5635,10 +5635,10 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0077</v>
+        <v>-0.0055</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.2695</v>
+        <v>-0.1925</v>
       </c>
     </row>
     <row r="36">
@@ -5675,10 +5675,10 @@
         <v>0.85</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2111</v>
+        <v>-0.1908</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.3885</v>
+        <v>-6.678</v>
       </c>
     </row>
     <row r="37">
@@ -5715,10 +5715,10 @@
         <v>1.16</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2961</v>
+        <v>0.284</v>
       </c>
       <c r="J37" t="n">
-        <v>10.3635</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="38">
@@ -5755,10 +5755,10 @@
         <v>1.01</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0402</v>
+        <v>0.0303</v>
       </c>
       <c r="J38" t="n">
-        <v>1.407</v>
+        <v>1.0605</v>
       </c>
     </row>
     <row r="39">
@@ -5795,10 +5795,10 @@
         <v>0.95</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0825</v>
+        <v>-0.0683</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.8875</v>
+        <v>-2.3905</v>
       </c>
     </row>
     <row r="40">
@@ -5835,10 +5835,10 @@
         <v>0.82</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.227</v>
+        <v>-0.2068</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.945</v>
+        <v>-7.238</v>
       </c>
     </row>
     <row r="41">
@@ -5875,10 +5875,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2763</v>
+        <v>-0.2572</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.670500000000001</v>
+        <v>-9.002000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -5915,10 +5915,10 @@
         <v>1.14</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3297</v>
+        <v>0.277</v>
       </c>
       <c r="J42" t="n">
-        <v>8.5722</v>
+        <v>7.202</v>
       </c>
     </row>
     <row r="43">
@@ -5955,10 +5955,10 @@
         <v>1.09</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2341</v>
+        <v>0.1893</v>
       </c>
       <c r="J43" t="n">
-        <v>6.0866</v>
+        <v>4.9218</v>
       </c>
     </row>
     <row r="44">
@@ -5995,10 +5995,10 @@
         <v>0.97</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0577</v>
+        <v>-0.0453</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.5002</v>
+        <v>-1.1778</v>
       </c>
     </row>
     <row r="45">
@@ -6035,10 +6035,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0984</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.5584</v>
+        <v>-2.1242</v>
       </c>
     </row>
     <row r="46">
@@ -6075,10 +6075,10 @@
         <v>0.82</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2317</v>
+        <v>-0.2113</v>
       </c>
       <c r="J46" t="n">
-        <v>-6.0242</v>
+        <v>-5.4938</v>
       </c>
     </row>
     <row r="47">
@@ -6115,10 +6115,10 @@
         <v>1.56</v>
       </c>
       <c r="I47" t="n">
-        <v>1.0396</v>
+        <v>1.0286</v>
       </c>
       <c r="J47" t="n">
-        <v>27.0296</v>
+        <v>26.7436</v>
       </c>
     </row>
     <row r="48">
@@ -6155,10 +6155,10 @@
         <v>1.4</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8177</v>
+        <v>0.8021</v>
       </c>
       <c r="J48" t="n">
-        <v>21.2602</v>
+        <v>20.8546</v>
       </c>
     </row>
     <row r="49">
@@ -6195,10 +6195,10 @@
         <v>1.2</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5078</v>
       </c>
       <c r="J49" t="n">
-        <v>13.4576</v>
+        <v>13.2028</v>
       </c>
     </row>
     <row r="50">
@@ -6235,10 +6235,10 @@
         <v>0.95</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2366</v>
+        <v>-0.1999</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.1516</v>
+        <v>-5.1974</v>
       </c>
     </row>
     <row r="51">
@@ -6275,10 +6275,10 @@
         <v>0.87</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.457</v>
+        <v>-0.4164</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.882</v>
+        <v>-10.8264</v>
       </c>
     </row>
     <row r="52">
@@ -6315,10 +6315,10 @@
         <v>1.95</v>
       </c>
       <c r="I52" t="n">
-        <v>1.4929</v>
+        <v>1.5114</v>
       </c>
       <c r="J52" t="n">
-        <v>34.3367</v>
+        <v>34.7622</v>
       </c>
     </row>
     <row r="53">
@@ -6355,10 +6355,10 @@
         <v>1.44</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8489</v>
+        <v>0.837</v>
       </c>
       <c r="J53" t="n">
-        <v>19.5247</v>
+        <v>19.251</v>
       </c>
     </row>
     <row r="54">
@@ -6395,10 +6395,10 @@
         <v>1.27</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6112</v>
+        <v>0.606</v>
       </c>
       <c r="J54" t="n">
-        <v>14.0576</v>
+        <v>13.938</v>
       </c>
     </row>
     <row r="55">
@@ -6435,10 +6435,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3847</v>
+        <v>0.3529</v>
       </c>
       <c r="J55" t="n">
-        <v>8.848100000000001</v>
+        <v>8.1167</v>
       </c>
     </row>
     <row r="56">
@@ -6475,10 +6475,10 @@
         <v>1.01</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0005</v>
+        <v>-0.0123</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.0115</v>
+        <v>-0.2829</v>
       </c>
     </row>
     <row r="57">
@@ -6515,10 +6515,10 @@
         <v>0.99</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>0.0138</v>
+        <v>0.2001</v>
       </c>
     </row>
     <row r="58">
@@ -6555,10 +6555,10 @@
         <v>0.99</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0138</v>
+        <v>0.2001</v>
       </c>
     </row>
     <row r="59">
@@ -6595,10 +6595,10 @@
         <v>0.75</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2798</v>
+        <v>-0.2627</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.4354</v>
+        <v>-6.0421</v>
       </c>
     </row>
     <row r="60">
@@ -6635,10 +6635,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3625</v>
+        <v>-0.3483</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.3375</v>
+        <v>-8.010899999999999</v>
       </c>
     </row>
     <row r="61">
@@ -6675,10 +6675,10 @@
         <v>0.54</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4692</v>
+        <v>-0.4645</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.7916</v>
+        <v>-10.6835</v>
       </c>
     </row>
     <row r="62">
@@ -6715,10 +6715,10 @@
         <v>1.66</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1066</v>
+        <v>1.1035</v>
       </c>
       <c r="J62" t="n">
-        <v>19.9188</v>
+        <v>19.863</v>
       </c>
     </row>
     <row r="63">
@@ -6755,10 +6755,10 @@
         <v>1.66</v>
       </c>
       <c r="I63" t="n">
-        <v>1.1066</v>
+        <v>1.1035</v>
       </c>
       <c r="J63" t="n">
-        <v>19.9188</v>
+        <v>19.863</v>
       </c>
     </row>
     <row r="64">
@@ -6795,10 +6795,10 @@
         <v>1.64</v>
       </c>
       <c r="I64" t="n">
-        <v>1.0824</v>
+        <v>1.0788</v>
       </c>
       <c r="J64" t="n">
-        <v>19.4832</v>
+        <v>19.4184</v>
       </c>
     </row>
     <row r="65">
@@ -6835,10 +6835,10 @@
         <v>1.61</v>
       </c>
       <c r="I65" t="n">
-        <v>1.0461</v>
+        <v>1.0419</v>
       </c>
       <c r="J65" t="n">
-        <v>18.8298</v>
+        <v>18.7542</v>
       </c>
     </row>
     <row r="66">
@@ -6875,10 +6875,10 @@
         <v>1.33</v>
       </c>
       <c r="I66" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>12.2022</v>
+        <v>12.1302</v>
       </c>
     </row>
     <row r="67">
@@ -6915,10 +6915,10 @@
         <v>0.95</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0118</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="J67" t="n">
-        <v>0.2124</v>
+        <v>1.1808</v>
       </c>
     </row>
     <row r="68">
@@ -6955,10 +6955,10 @@
         <v>0.67</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3218</v>
+        <v>-0.3121</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.7924</v>
+        <v>-5.6178</v>
       </c>
     </row>
     <row r="69">
@@ -6995,10 +6995,10 @@
         <v>0.47</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4992</v>
+        <v>-0.498</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.9856</v>
+        <v>-8.964</v>
       </c>
     </row>
     <row r="70">
@@ -7035,10 +7035,10 @@
         <v>0.35</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6059</v>
+        <v>-0.6176</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.9062</v>
+        <v>-11.1168</v>
       </c>
     </row>
     <row r="71">
@@ -7075,10 +7075,10 @@
         <v>0.33</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6238</v>
+        <v>-0.6384</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.2284</v>
+        <v>-11.4912</v>
       </c>
     </row>
     <row r="72">
@@ -7115,10 +7115,10 @@
         <v>1.55</v>
       </c>
       <c r="I72" t="n">
-        <v>1.1623</v>
+        <v>1.1758</v>
       </c>
       <c r="J72" t="n">
-        <v>32.5444</v>
+        <v>32.9224</v>
       </c>
     </row>
     <row r="73">
@@ -7155,10 +7155,10 @@
         <v>1.38</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9014</v>
+        <v>0.886</v>
       </c>
       <c r="J73" t="n">
-        <v>25.2392</v>
+        <v>24.808</v>
       </c>
     </row>
     <row r="74">
@@ -7195,10 +7195,10 @@
         <v>1.23</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6041</v>
+        <v>0.5735</v>
       </c>
       <c r="J74" t="n">
-        <v>16.9148</v>
+        <v>16.058</v>
       </c>
     </row>
     <row r="75">
@@ -7235,10 +7235,10 @@
         <v>1.1</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3027</v>
+        <v>0.2708</v>
       </c>
       <c r="J75" t="n">
-        <v>8.4756</v>
+        <v>7.5824</v>
       </c>
     </row>
     <row r="76">
@@ -7275,10 +7275,10 @@
         <v>0.97</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1795</v>
+        <v>-0.1487</v>
       </c>
       <c r="J76" t="n">
-        <v>-5.026</v>
+        <v>-4.1636</v>
       </c>
     </row>
     <row r="77">
@@ -7315,10 +7315,10 @@
         <v>1.19</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4308</v>
+        <v>0.3741</v>
       </c>
       <c r="J77" t="n">
-        <v>12.0624</v>
+        <v>10.4748</v>
       </c>
     </row>
     <row r="78">
@@ -7355,10 +7355,10 @@
         <v>1.1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2639</v>
+        <v>0.2161</v>
       </c>
       <c r="J78" t="n">
-        <v>7.3892</v>
+        <v>6.0508</v>
       </c>
     </row>
     <row r="79">
@@ -7395,10 +7395,10 @@
         <v>0.87</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1752</v>
+        <v>-0.1553</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.9056</v>
+        <v>-4.3484</v>
       </c>
     </row>
     <row r="80">
@@ -7435,10 +7435,10 @@
         <v>0.82</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2272</v>
+        <v>-0.2069</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.3616</v>
+        <v>-5.7932</v>
       </c>
     </row>
     <row r="81">
@@ -7475,10 +7475,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3052</v>
+        <v>-0.2874</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.5456</v>
+        <v>-8.0472</v>
       </c>
     </row>
     <row r="82">
@@ -7515,10 +7515,10 @@
         <v>1.42</v>
       </c>
       <c r="I82" t="n">
-        <v>0.987</v>
+        <v>0.9816</v>
       </c>
       <c r="J82" t="n">
-        <v>27.636</v>
+        <v>27.4848</v>
       </c>
     </row>
     <row r="83">
@@ -7555,10 +7555,10 @@
         <v>1.29</v>
       </c>
       <c r="I83" t="n">
-        <v>0.735</v>
+        <v>0.7063</v>
       </c>
       <c r="J83" t="n">
-        <v>20.58</v>
+        <v>19.7764</v>
       </c>
     </row>
     <row r="84">
@@ -7595,10 +7595,10 @@
         <v>1.12</v>
       </c>
       <c r="I84" t="n">
-        <v>0.363</v>
+        <v>0.3287</v>
       </c>
       <c r="J84" t="n">
-        <v>10.164</v>
+        <v>9.2036</v>
       </c>
     </row>
     <row r="85">
@@ -7635,10 +7635,10 @@
         <v>1.12</v>
       </c>
       <c r="I85" t="n">
-        <v>0.363</v>
+        <v>0.3287</v>
       </c>
       <c r="J85" t="n">
-        <v>10.164</v>
+        <v>9.2036</v>
       </c>
     </row>
     <row r="86">
@@ -7675,10 +7675,10 @@
         <v>0.99</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.0703</v>
       </c>
       <c r="J86" t="n">
-        <v>-2.5564</v>
+        <v>-1.9684</v>
       </c>
     </row>
     <row r="87">
@@ -7715,10 +7715,10 @@
         <v>1.44</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8384</v>
+        <v>0.7947</v>
       </c>
       <c r="J87" t="n">
-        <v>23.4752</v>
+        <v>22.2516</v>
       </c>
     </row>
     <row r="88">
@@ -7755,10 +7755,10 @@
         <v>0.92</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1182</v>
+        <v>-0.1014</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.3096</v>
+        <v>-2.8392</v>
       </c>
     </row>
     <row r="89">
@@ -7795,10 +7795,10 @@
         <v>0.85</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1949</v>
+        <v>-0.1749</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.4572</v>
+        <v>-4.8972</v>
       </c>
     </row>
     <row r="90">
@@ -7835,10 +7835,10 @@
         <v>0.8</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2457</v>
+        <v>-0.2258</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.8796</v>
+        <v>-6.3224</v>
       </c>
     </row>
     <row r="91">
@@ -7875,10 +7875,10 @@
         <v>0.63</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4044</v>
+        <v>-0.3939</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.3232</v>
+        <v>-11.0292</v>
       </c>
     </row>
     <row r="92">
@@ -7915,10 +7915,10 @@
         <v>1.72</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8176</v>
+        <v>0.7463</v>
       </c>
       <c r="J92" t="n">
-        <v>18.8048</v>
+        <v>17.1649</v>
       </c>
     </row>
     <row r="93">
@@ -7955,10 +7955,10 @@
         <v>1.43</v>
       </c>
       <c r="I93" t="n">
-        <v>0.537</v>
+        <v>0.4697</v>
       </c>
       <c r="J93" t="n">
-        <v>12.351</v>
+        <v>10.8031</v>
       </c>
     </row>
     <row r="94">
@@ -7995,10 +7995,10 @@
         <v>1.42</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5269</v>
+        <v>0.4601</v>
       </c>
       <c r="J94" t="n">
-        <v>12.1187</v>
+        <v>10.5823</v>
       </c>
     </row>
     <row r="95">
@@ -8035,10 +8035,10 @@
         <v>1.19</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2768</v>
+        <v>0.2291</v>
       </c>
       <c r="J95" t="n">
-        <v>6.3664</v>
+        <v>5.2693</v>
       </c>
     </row>
     <row r="96">
@@ -8075,10 +8075,10 @@
         <v>0.93</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1374</v>
+        <v>-0.1204</v>
       </c>
       <c r="J96" t="n">
-        <v>-3.1602</v>
+        <v>-2.7692</v>
       </c>
     </row>
     <row r="97">
@@ -8115,10 +8115,10 @@
         <v>1.19</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3817</v>
+        <v>0.3873</v>
       </c>
       <c r="J97" t="n">
-        <v>8.7791</v>
+        <v>8.9079</v>
       </c>
     </row>
     <row r="98">
@@ -8155,10 +8155,10 @@
         <v>0.97</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0352</v>
+        <v>-0.0257</v>
       </c>
       <c r="J98" t="n">
-        <v>-0.8096</v>
+        <v>-0.5911</v>
       </c>
     </row>
     <row r="99">
@@ -8195,10 +8195,10 @@
         <v>0.6</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4168</v>
+        <v>-0.4067</v>
       </c>
       <c r="J99" t="n">
-        <v>-9.586399999999999</v>
+        <v>-9.354100000000001</v>
       </c>
     </row>
     <row r="100">
@@ -8235,10 +8235,10 @@
         <v>0.6</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4168</v>
+        <v>-0.4067</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.586399999999999</v>
+        <v>-9.354100000000001</v>
       </c>
     </row>
     <row r="101">
@@ -8275,10 +8275,10 @@
         <v>0.59</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4257</v>
+        <v>-0.4164</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.7911</v>
+        <v>-9.577199999999999</v>
       </c>
     </row>
     <row r="102">
@@ -8315,10 +8315,10 @@
         <v>1.08</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2277</v>
+        <v>0.1833</v>
       </c>
       <c r="J102" t="n">
-        <v>5.9202</v>
+        <v>4.7658</v>
       </c>
     </row>
     <row r="103">
@@ -8355,10 +8355,10 @@
         <v>0.96</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0678</v>
+        <v>-0.0556</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.7628</v>
+        <v>-1.4456</v>
       </c>
     </row>
     <row r="104">
@@ -8395,10 +8395,10 @@
         <v>0.93</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1064</v>
+        <v>-0.0905</v>
       </c>
       <c r="J104" t="n">
-        <v>-2.7664</v>
+        <v>-2.353</v>
       </c>
     </row>
     <row r="105">
@@ -8435,10 +8435,10 @@
         <v>0.86</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1841</v>
+        <v>-0.1643</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.7866</v>
+        <v>-4.2718</v>
       </c>
     </row>
     <row r="106">
@@ -8475,10 +8475,10 @@
         <v>0.79</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2551</v>
+        <v>-0.2354</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.6326</v>
+        <v>-6.1204</v>
       </c>
     </row>
     <row r="107">
@@ -8515,10 +8515,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>1.2736</v>
+        <v>1.293</v>
       </c>
       <c r="J107" t="n">
-        <v>33.1136</v>
+        <v>33.618</v>
       </c>
     </row>
     <row r="108">
@@ -8555,10 +8555,10 @@
         <v>1.47</v>
       </c>
       <c r="I108" t="n">
-        <v>1.0685</v>
+        <v>1.0766</v>
       </c>
       <c r="J108" t="n">
-        <v>27.781</v>
+        <v>27.9916</v>
       </c>
     </row>
     <row r="109">
@@ -8595,10 +8595,10 @@
         <v>1.16</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4602</v>
+        <v>0.4242</v>
       </c>
       <c r="J109" t="n">
-        <v>11.9652</v>
+        <v>11.0292</v>
       </c>
     </row>
     <row r="110">
@@ -8635,10 +8635,10 @@
         <v>1.03</v>
       </c>
       <c r="I110" t="n">
-        <v>0.109</v>
+        <v>0.0883</v>
       </c>
       <c r="J110" t="n">
-        <v>2.834</v>
+        <v>2.2958</v>
       </c>
     </row>
     <row r="111">
@@ -8675,10 +8675,10 @@
         <v>0.58</v>
       </c>
       <c r="I111" t="n">
-        <v>-1.0859</v>
+        <v>-1.0987</v>
       </c>
       <c r="J111" t="n">
-        <v>-28.2334</v>
+        <v>-28.5662</v>
       </c>
     </row>
     <row r="112">
@@ -8715,10 +8715,10 @@
         <v>1.22</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4814</v>
+        <v>0.4237</v>
       </c>
       <c r="J112" t="n">
-        <v>13.9606</v>
+        <v>12.2873</v>
       </c>
     </row>
     <row r="113">
@@ -8755,10 +8755,10 @@
         <v>1.11</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2827</v>
+        <v>0.2333</v>
       </c>
       <c r="J113" t="n">
-        <v>8.1983</v>
+        <v>6.7657</v>
       </c>
     </row>
     <row r="114">
@@ -8795,10 +8795,10 @@
         <v>0.88</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1648</v>
+        <v>-0.1451</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.7792</v>
+        <v>-4.2079</v>
       </c>
     </row>
     <row r="115">
@@ -8835,10 +8835,10 @@
         <v>0.78</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2672</v>
+        <v>-0.2478</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.7488</v>
+        <v>-7.1862</v>
       </c>
     </row>
     <row r="116">
@@ -8875,10 +8875,10 @@
         <v>0.75</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2961</v>
+        <v>-0.2778</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.5869</v>
+        <v>-8.0562</v>
       </c>
     </row>
     <row r="117">
@@ -8915,10 +8915,10 @@
         <v>1.45</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0419</v>
+        <v>1.046</v>
       </c>
       <c r="J117" t="n">
-        <v>30.2151</v>
+        <v>30.334</v>
       </c>
     </row>
     <row r="118">
@@ -8955,10 +8955,10 @@
         <v>1.26</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6784</v>
+        <v>0.646</v>
       </c>
       <c r="J118" t="n">
-        <v>19.6736</v>
+        <v>18.734</v>
       </c>
     </row>
     <row r="119">
@@ -8995,10 +8995,10 @@
         <v>1.08</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2633</v>
+        <v>0.2313</v>
       </c>
       <c r="J119" t="n">
-        <v>7.6357</v>
+        <v>6.7077</v>
       </c>
     </row>
     <row r="120">
@@ -9035,10 +9035,10 @@
         <v>1.05</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1763</v>
+        <v>0.1495</v>
       </c>
       <c r="J120" t="n">
-        <v>5.1127</v>
+        <v>4.3355</v>
       </c>
     </row>
     <row r="121">
@@ -9075,10 +9075,10 @@
         <v>0.96</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1982</v>
+        <v>-0.1635</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.7478</v>
+        <v>-4.7415</v>
       </c>
     </row>
     <row r="122">
@@ -9115,10 +9115,10 @@
         <v>1.34</v>
       </c>
       <c r="I122" t="n">
-        <v>0.699</v>
+        <v>0.6495</v>
       </c>
       <c r="J122" t="n">
-        <v>19.572</v>
+        <v>18.186</v>
       </c>
     </row>
     <row r="123">
@@ -9155,10 +9155,10 @@
         <v>0.89</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.1497</v>
+        <v>-0.1319</v>
       </c>
       <c r="J123" t="n">
-        <v>-4.1916</v>
+        <v>-3.6932</v>
       </c>
     </row>
     <row r="124">
@@ -9195,10 +9195,10 @@
         <v>0.84</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2019</v>
+        <v>-0.1824</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.6532</v>
+        <v>-5.1072</v>
       </c>
     </row>
     <row r="125">
@@ -9235,10 +9235,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2321</v>
+        <v>-0.2124</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.4988</v>
+        <v>-5.9472</v>
       </c>
     </row>
     <row r="126">
@@ -9275,10 +9275,10 @@
         <v>0.57</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4537</v>
+        <v>-0.4481</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.7036</v>
+        <v>-12.5468</v>
       </c>
     </row>
     <row r="127">
@@ -9315,10 +9315,10 @@
         <v>1.41</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9706</v>
+        <v>0.9624</v>
       </c>
       <c r="J127" t="n">
-        <v>27.1768</v>
+        <v>26.9472</v>
       </c>
     </row>
     <row r="128">
@@ -9355,10 +9355,10 @@
         <v>1.34</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8366</v>
+        <v>0.8142</v>
       </c>
       <c r="J128" t="n">
-        <v>23.4248</v>
+        <v>22.7976</v>
       </c>
     </row>
     <row r="129">
@@ -9395,10 +9395,10 @@
         <v>1.33</v>
       </c>
       <c r="I129" t="n">
-        <v>0.8166</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="J129" t="n">
-        <v>22.8648</v>
+        <v>22.1984</v>
       </c>
     </row>
     <row r="130">
@@ -9435,10 +9435,10 @@
         <v>1.16</v>
       </c>
       <c r="I130" t="n">
-        <v>0.4589</v>
+        <v>0.4234</v>
       </c>
       <c r="J130" t="n">
-        <v>12.8492</v>
+        <v>11.8552</v>
       </c>
     </row>
     <row r="131">
@@ -9475,10 +9475,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8844</v>
+        <v>-0.8722</v>
       </c>
       <c r="J131" t="n">
-        <v>-24.7632</v>
+        <v>-24.4216</v>
       </c>
     </row>
     <row r="132">
@@ -9515,10 +9515,10 @@
         <v>1.24</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5351</v>
+        <v>0.4801</v>
       </c>
       <c r="J132" t="n">
-        <v>12.8424</v>
+        <v>11.5224</v>
       </c>
     </row>
     <row r="133">
@@ -9555,10 +9555,10 @@
         <v>0.97</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0496</v>
+        <v>-0.0399</v>
       </c>
       <c r="J133" t="n">
-        <v>-1.1904</v>
+        <v>-0.9576</v>
       </c>
     </row>
     <row r="134">
@@ -9595,10 +9595,10 @@
         <v>0.88</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1601</v>
+        <v>-0.1419</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.8424</v>
+        <v>-3.4056</v>
       </c>
     </row>
     <row r="135">
@@ -9635,10 +9635,10 @@
         <v>0.84</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2017</v>
+        <v>-0.1823</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.8408</v>
+        <v>-4.3752</v>
       </c>
     </row>
     <row r="136">
@@ -9675,10 +9675,10 @@
         <v>0.51</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-0.5064</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.132</v>
+        <v>-12.1536</v>
       </c>
     </row>
     <row r="137">
@@ -9715,10 +9715,10 @@
         <v>2.2</v>
       </c>
       <c r="I137" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J137" t="n">
-        <v>46.4928</v>
+        <v>47.5632</v>
       </c>
     </row>
     <row r="138">
@@ -9755,10 +9755,10 @@
         <v>1.11</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3244</v>
+        <v>0.2923</v>
       </c>
       <c r="J138" t="n">
-        <v>7.7856</v>
+        <v>7.0152</v>
       </c>
     </row>
     <row r="139">
@@ -9795,10 +9795,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1256</v>
+        <v>0.1019</v>
       </c>
       <c r="J139" t="n">
-        <v>3.0144</v>
+        <v>2.4456</v>
       </c>
     </row>
     <row r="140">
@@ -9835,10 +9835,10 @@
         <v>1.01</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0139</v>
+        <v>0.0037</v>
       </c>
       <c r="J140" t="n">
-        <v>0.3336</v>
+        <v>0.0888</v>
       </c>
     </row>
     <row r="141">
@@ -9875,10 +9875,10 @@
         <v>1</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.0459</v>
+        <v>-0.0409</v>
       </c>
       <c r="J141" t="n">
-        <v>-1.1016</v>
+        <v>-0.9816</v>
       </c>
     </row>
     <row r="142">
@@ -9915,10 +9915,10 @@
         <v>1.4</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9413</v>
+        <v>0.9297</v>
       </c>
       <c r="J142" t="n">
-        <v>24.4738</v>
+        <v>24.1722</v>
       </c>
     </row>
     <row r="143">
@@ -9955,10 +9955,10 @@
         <v>1.33</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8065</v>
+        <v>0.7839</v>
       </c>
       <c r="J143" t="n">
-        <v>20.969</v>
+        <v>20.3814</v>
       </c>
     </row>
     <row r="144">
@@ -9995,10 +9995,10 @@
         <v>1.24</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.5949</v>
       </c>
       <c r="J144" t="n">
-        <v>16.263</v>
+        <v>15.4674</v>
       </c>
     </row>
     <row r="145">
@@ -10035,10 +10035,10 @@
         <v>1.17</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4749</v>
+        <v>0.4418</v>
       </c>
       <c r="J145" t="n">
-        <v>12.3474</v>
+        <v>11.4868</v>
       </c>
     </row>
     <row r="146">
@@ -10075,10 +10075,10 @@
         <v>1.03</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0983</v>
+        <v>0.0779</v>
       </c>
       <c r="J146" t="n">
-        <v>2.5558</v>
+        <v>2.0254</v>
       </c>
     </row>
     <row r="147">
@@ -10115,10 +10115,10 @@
         <v>1.19</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4422</v>
+        <v>0.3864</v>
       </c>
       <c r="J147" t="n">
-        <v>11.4972</v>
+        <v>10.0464</v>
       </c>
     </row>
     <row r="148">
@@ -10155,10 +10155,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.0785</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.4128</v>
+        <v>-2.041</v>
       </c>
     </row>
     <row r="149">
@@ -10195,10 +10195,10 @@
         <v>0.83</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2135</v>
+        <v>-0.1936</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.551</v>
+        <v>-5.0336</v>
       </c>
     </row>
     <row r="150">
@@ -10235,10 +10235,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2336</v>
+        <v>-0.2138</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.0736</v>
+        <v>-5.5588</v>
       </c>
     </row>
     <row r="151">
@@ -10275,10 +10275,10 @@
         <v>0.76</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2824</v>
+        <v>-0.2636</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.3424</v>
+        <v>-6.8536</v>
       </c>
     </row>
     <row r="152">
@@ -10315,10 +10315,10 @@
         <v>1.75</v>
       </c>
       <c r="I152" t="n">
-        <v>1.3832</v>
+        <v>1.4073</v>
       </c>
       <c r="J152" t="n">
-        <v>29.0472</v>
+        <v>29.5533</v>
       </c>
     </row>
     <row r="153">
@@ -10355,10 +10355,10 @@
         <v>1.65</v>
       </c>
       <c r="I153" t="n">
-        <v>1.2593</v>
+        <v>1.278</v>
       </c>
       <c r="J153" t="n">
-        <v>26.4453</v>
+        <v>26.838</v>
       </c>
     </row>
     <row r="154">
@@ -10395,10 +10395,10 @@
         <v>1.45</v>
       </c>
       <c r="I154" t="n">
-        <v>0.9965000000000001</v>
+        <v>1.001</v>
       </c>
       <c r="J154" t="n">
-        <v>20.9265</v>
+        <v>21.021</v>
       </c>
     </row>
     <row r="155">
@@ -10435,10 +10435,10 @@
         <v>1.22</v>
       </c>
       <c r="I155" t="n">
-        <v>0.5567</v>
+        <v>0.5299</v>
       </c>
       <c r="J155" t="n">
-        <v>11.6907</v>
+        <v>11.1279</v>
       </c>
     </row>
     <row r="156">
@@ -10475,10 +10475,10 @@
         <v>1.09</v>
       </c>
       <c r="I156" t="n">
-        <v>0.2469</v>
+        <v>0.2147</v>
       </c>
       <c r="J156" t="n">
-        <v>5.1849</v>
+        <v>4.5087</v>
       </c>
     </row>
     <row r="157">
@@ -10515,10 +10515,10 @@
         <v>0.99</v>
       </c>
       <c r="I157" t="n">
-        <v>0.0083</v>
+        <v>0.017</v>
       </c>
       <c r="J157" t="n">
-        <v>0.1743</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="158">
@@ -10555,10 +10555,10 @@
         <v>0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0301</v>
+        <v>-0.0201</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.6321</v>
+        <v>-0.4221</v>
       </c>
     </row>
     <row r="159">
@@ -10595,10 +10595,10 @@
         <v>0.93</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0728</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.8165</v>
+        <v>-1.5288</v>
       </c>
     </row>
     <row r="160">
@@ -10635,10 +10635,10 @@
         <v>0.48</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.519</v>
+        <v>-0.5203</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.899</v>
+        <v>-10.9263</v>
       </c>
     </row>
     <row r="161">
@@ -10675,10 +10675,10 @@
         <v>0.45</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.4429</v>
+        <v>-11.5479</v>
       </c>
     </row>
     <row r="162">
@@ -10715,10 +10715,10 @@
         <v>1.62</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2627</v>
+        <v>1.2807</v>
       </c>
       <c r="J162" t="n">
-        <v>31.5675</v>
+        <v>32.0175</v>
       </c>
     </row>
     <row r="163">
@@ -10755,10 +10755,10 @@
         <v>1.21</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5653</v>
+        <v>0.5322</v>
       </c>
       <c r="J163" t="n">
-        <v>14.1325</v>
+        <v>13.305</v>
       </c>
     </row>
     <row r="164">
@@ -10795,10 +10795,10 @@
         <v>1.14</v>
       </c>
       <c r="I164" t="n">
-        <v>0.4078</v>
+        <v>0.3739</v>
       </c>
       <c r="J164" t="n">
-        <v>10.195</v>
+        <v>9.3475</v>
       </c>
     </row>
     <row r="165">
@@ -10835,10 +10835,10 @@
         <v>1.06</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1973</v>
+        <v>0.1693</v>
       </c>
       <c r="J165" t="n">
-        <v>4.9325</v>
+        <v>4.2325</v>
       </c>
     </row>
     <row r="166">
@@ -10875,10 +10875,10 @@
         <v>1.04</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1354</v>
+        <v>0.1118</v>
       </c>
       <c r="J166" t="n">
-        <v>3.385</v>
+        <v>2.795</v>
       </c>
     </row>
     <row r="167">
@@ -10915,10 +10915,10 @@
         <v>1.21</v>
       </c>
       <c r="I167" t="n">
-        <v>0.469</v>
+        <v>0.4119</v>
       </c>
       <c r="J167" t="n">
-        <v>11.725</v>
+        <v>10.2975</v>
       </c>
     </row>
     <row r="168">
@@ -10955,10 +10955,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0384</v>
+        <v>-0.03</v>
       </c>
       <c r="J168" t="n">
-        <v>-0.96</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="169">
@@ -10995,10 +10995,10 @@
         <v>0.86</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1848</v>
+        <v>-0.1649</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.62</v>
+        <v>-4.1225</v>
       </c>
     </row>
     <row r="170">
@@ -11035,10 +11035,10 @@
         <v>0.82</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2261</v>
+        <v>-0.2059</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.6525</v>
+        <v>-5.1475</v>
       </c>
     </row>
     <row r="171">
@@ -11075,10 +11075,10 @@
         <v>0.79</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2559</v>
+        <v>-0.2362</v>
       </c>
       <c r="J171" t="n">
-        <v>-6.3975</v>
+        <v>-5.905</v>
       </c>
     </row>
     <row r="172">
@@ -11115,10 +11115,10 @@
         <v>1.28</v>
       </c>
       <c r="I172" t="n">
-        <v>0.7308</v>
+        <v>0.6997</v>
       </c>
       <c r="J172" t="n">
-        <v>21.924</v>
+        <v>20.991</v>
       </c>
     </row>
     <row r="173">
@@ -11155,10 +11155,10 @@
         <v>1.27</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7098</v>
+        <v>0.6775</v>
       </c>
       <c r="J173" t="n">
-        <v>21.294</v>
+        <v>20.325</v>
       </c>
     </row>
     <row r="174">
@@ -11195,10 +11195,10 @@
         <v>1.21</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5802</v>
+        <v>0.5425</v>
       </c>
       <c r="J174" t="n">
-        <v>17.406</v>
+        <v>16.275</v>
       </c>
     </row>
     <row r="175">
@@ -11235,10 +11235,10 @@
         <v>1.05</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1841</v>
+        <v>0.1559</v>
       </c>
       <c r="J175" t="n">
-        <v>5.523</v>
+        <v>4.677</v>
       </c>
     </row>
     <row r="176">
@@ -11275,10 +11275,10 @@
         <v>0.76</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7005</v>
+        <v>-0.6696</v>
       </c>
       <c r="J176" t="n">
-        <v>-21.015</v>
+        <v>-20.088</v>
       </c>
     </row>
     <row r="177">
@@ -11315,10 +11315,10 @@
         <v>1.34</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6513</v>
+        <v>0.5926</v>
       </c>
       <c r="J177" t="n">
-        <v>19.539</v>
+        <v>17.778</v>
       </c>
     </row>
     <row r="178">
@@ -11355,10 +11355,10 @@
         <v>1.22</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4605</v>
+        <v>0.4022</v>
       </c>
       <c r="J178" t="n">
-        <v>13.815</v>
+        <v>12.066</v>
       </c>
     </row>
     <row r="179">
@@ -11395,10 +11395,10 @@
         <v>1.03</v>
       </c>
       <c r="I179" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>2.913</v>
+        <v>2.172</v>
       </c>
     </row>
     <row r="180">
@@ -11435,10 +11435,10 @@
         <v>0.86</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1936</v>
+        <v>-0.1729</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.808</v>
+        <v>-5.187</v>
       </c>
     </row>
     <row r="181">
@@ -11475,10 +11475,10 @@
         <v>0.7</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3503</v>
+        <v>-0.3359</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.509</v>
+        <v>-10.077</v>
       </c>
     </row>
     <row r="182">
@@ -11515,10 +11515,10 @@
         <v>1.52</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1073</v>
+        <v>1.1202</v>
       </c>
       <c r="J182" t="n">
-        <v>23.2533</v>
+        <v>23.5242</v>
       </c>
     </row>
     <row r="183">
@@ -11555,10 +11555,10 @@
         <v>1.43</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9765</v>
+        <v>0.9734</v>
       </c>
       <c r="J183" t="n">
-        <v>20.5065</v>
+        <v>20.4414</v>
       </c>
     </row>
     <row r="184">
@@ -11595,10 +11595,10 @@
         <v>1.27</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6763</v>
+        <v>0.6522</v>
       </c>
       <c r="J184" t="n">
-        <v>14.2023</v>
+        <v>13.6962</v>
       </c>
     </row>
     <row r="185">
@@ -11635,10 +11635,10 @@
         <v>1.23</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5931</v>
+        <v>0.5658</v>
       </c>
       <c r="J185" t="n">
-        <v>12.4551</v>
+        <v>11.8818</v>
       </c>
     </row>
     <row r="186">
@@ -11675,10 +11675,10 @@
         <v>1.2</v>
       </c>
       <c r="I186" t="n">
-        <v>0.5281</v>
+        <v>0.4987</v>
       </c>
       <c r="J186" t="n">
-        <v>11.0901</v>
+        <v>10.4727</v>
       </c>
     </row>
     <row r="187">
@@ -11715,10 +11715,10 @@
         <v>1</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0584</v>
+        <v>0.0543</v>
       </c>
       <c r="J187" t="n">
-        <v>1.2264</v>
+        <v>1.1403</v>
       </c>
     </row>
     <row r="188">
@@ -11755,10 +11755,10 @@
         <v>0.91</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1095</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J188" t="n">
-        <v>-2.2995</v>
+        <v>-1.9887</v>
       </c>
     </row>
     <row r="189">
@@ -11795,10 +11795,10 @@
         <v>0.72</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3041</v>
+        <v>-0.2884</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.3861</v>
+        <v>-6.0564</v>
       </c>
     </row>
     <row r="190">
@@ -11835,10 +11835,10 @@
         <v>0.6</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4123</v>
+        <v>-0.4019</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.658300000000001</v>
+        <v>-8.4399</v>
       </c>
     </row>
     <row r="191">
@@ -11875,10 +11875,10 @@
         <v>0.53</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4741</v>
+        <v>-0.4697</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.956099999999999</v>
+        <v>-9.8637</v>
       </c>
     </row>
     <row r="192">
@@ -11915,10 +11915,10 @@
         <v>1.18</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3164</v>
+        <v>0.3055</v>
       </c>
       <c r="J192" t="n">
-        <v>7.91</v>
+        <v>7.6375</v>
       </c>
     </row>
     <row r="193">
@@ -11955,10 +11955,10 @@
         <v>1.15</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2746</v>
+        <v>0.2608</v>
       </c>
       <c r="J193" t="n">
-        <v>6.865</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="194">
@@ -11995,10 +11995,10 @@
         <v>1.14</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2603</v>
+        <v>0.2456</v>
       </c>
       <c r="J194" t="n">
-        <v>6.5075</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="195">
@@ -12035,10 +12035,10 @@
         <v>0.82</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2306</v>
+        <v>-0.2102</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.765</v>
+        <v>-5.255</v>
       </c>
     </row>
     <row r="196">
@@ -12075,10 +12075,10 @@
         <v>0.61</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4268</v>
+        <v>-0.4191</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.67</v>
+        <v>-10.4775</v>
       </c>
     </row>
     <row r="197">
@@ -12115,10 +12115,10 @@
         <v>1.42</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5587</v>
+        <v>0.4887</v>
       </c>
       <c r="J197" t="n">
-        <v>13.9675</v>
+        <v>12.2175</v>
       </c>
     </row>
     <row r="198">
@@ -12155,10 +12155,10 @@
         <v>1.17</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2703</v>
+        <v>0.2186</v>
       </c>
       <c r="J198" t="n">
-        <v>6.7575</v>
+        <v>5.465</v>
       </c>
     </row>
     <row r="199">
@@ -12195,10 +12195,10 @@
         <v>1.14</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2317</v>
+        <v>0.1847</v>
       </c>
       <c r="J199" t="n">
-        <v>5.7925</v>
+        <v>4.6175</v>
       </c>
     </row>
     <row r="200">
@@ -12235,10 +12235,10 @@
         <v>1.05</v>
       </c>
       <c r="I200" t="n">
-        <v>0.1022</v>
+        <v>0.076</v>
       </c>
       <c r="J200" t="n">
-        <v>2.555</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="201">
@@ -12275,10 +12275,10 @@
         <v>0.72</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3375</v>
+        <v>-0.3229</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.4375</v>
+        <v>-8.0725</v>
       </c>
     </row>
     <row r="202">
@@ -12315,10 +12315,10 @@
         <v>1.37</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9034</v>
+        <v>0.8859</v>
       </c>
       <c r="J202" t="n">
-        <v>25.2952</v>
+        <v>24.8052</v>
       </c>
     </row>
     <row r="203">
@@ -12355,10 +12355,10 @@
         <v>1.29</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7421</v>
+        <v>0.7127</v>
       </c>
       <c r="J203" t="n">
-        <v>20.7788</v>
+        <v>19.9556</v>
       </c>
     </row>
     <row r="204">
@@ -12395,10 +12395,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3923</v>
+        <v>0.356</v>
       </c>
       <c r="J204" t="n">
-        <v>10.9844</v>
+        <v>9.968</v>
       </c>
     </row>
     <row r="205">
@@ -12435,10 +12435,10 @@
         <v>1.04</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1458</v>
+        <v>0.1214</v>
       </c>
       <c r="J205" t="n">
-        <v>4.0824</v>
+        <v>3.3992</v>
       </c>
     </row>
     <row r="206">
@@ -12475,10 +12475,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2595</v>
+        <v>-0.2207</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.266</v>
+        <v>-6.1796</v>
       </c>
     </row>
     <row r="207">
@@ -12515,10 +12515,10 @@
         <v>1.14</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3583</v>
+        <v>0.306</v>
       </c>
       <c r="J207" t="n">
-        <v>10.0324</v>
+        <v>8.568</v>
       </c>
     </row>
     <row r="208">
@@ -12555,10 +12555,10 @@
         <v>1.02</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0945</v>
+        <v>0.0692</v>
       </c>
       <c r="J208" t="n">
-        <v>2.646</v>
+        <v>1.9376</v>
       </c>
     </row>
     <row r="209">
@@ -12595,10 +12595,10 @@
         <v>0.92</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1152</v>
+        <v>-0.0997</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.2256</v>
+        <v>-2.7916</v>
       </c>
     </row>
     <row r="210">
@@ -12635,10 +12635,10 @@
         <v>0.7</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3364</v>
+        <v>-0.3203</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.4192</v>
+        <v>-8.968400000000001</v>
       </c>
     </row>
     <row r="211">
@@ -12675,10 +12675,10 @@
         <v>0.63</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3999</v>
+        <v>-0.3887</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.1972</v>
+        <v>-10.8836</v>
       </c>
     </row>
     <row r="212">
@@ -12715,10 +12715,10 @@
         <v>1.64</v>
       </c>
       <c r="I212" t="n">
-        <v>1.2906</v>
+        <v>1.3103</v>
       </c>
       <c r="J212" t="n">
-        <v>45.171</v>
+        <v>45.8605</v>
       </c>
     </row>
     <row r="213">
@@ -12755,10 +12755,10 @@
         <v>1.41</v>
       </c>
       <c r="I213" t="n">
-        <v>0.965</v>
+        <v>0.9562</v>
       </c>
       <c r="J213" t="n">
-        <v>33.775</v>
+        <v>33.467</v>
       </c>
     </row>
     <row r="214">
@@ -12795,10 +12795,10 @@
         <v>1.11</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3347</v>
+        <v>0.3015</v>
       </c>
       <c r="J214" t="n">
-        <v>11.7145</v>
+        <v>10.5525</v>
       </c>
     </row>
     <row r="215">
@@ -12835,10 +12835,10 @@
         <v>1</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.035</v>
+        <v>-0.0294</v>
       </c>
       <c r="J215" t="n">
-        <v>-1.225</v>
+        <v>-1.029</v>
       </c>
     </row>
     <row r="216">
@@ -12875,10 +12875,10 @@
         <v>0.88</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4337</v>
+        <v>-0.3931</v>
       </c>
       <c r="J216" t="n">
-        <v>-15.1795</v>
+        <v>-13.7585</v>
       </c>
     </row>
     <row r="217">
@@ -12915,10 +12915,10 @@
         <v>1.11</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2996</v>
+        <v>0.2502</v>
       </c>
       <c r="J217" t="n">
-        <v>10.486</v>
+        <v>8.757</v>
       </c>
     </row>
     <row r="218">
@@ -12955,10 +12955,10 @@
         <v>1.01</v>
       </c>
       <c r="I218" t="n">
-        <v>0.063</v>
+        <v>0.0442</v>
       </c>
       <c r="J218" t="n">
-        <v>2.205</v>
+        <v>1.547</v>
       </c>
     </row>
     <row r="219">
@@ -12995,10 +12995,10 @@
         <v>0.85</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1911</v>
+        <v>-0.172</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.6885</v>
+        <v>-6.02</v>
       </c>
     </row>
     <row r="220">
@@ -13035,10 +13035,10 @@
         <v>0.82</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2216</v>
+        <v>-0.202</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.756</v>
+        <v>-7.07</v>
       </c>
     </row>
     <row r="221">
@@ -13075,10 +13075,10 @@
         <v>0.63</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4001</v>
+        <v>-0.3889</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.0035</v>
+        <v>-13.6115</v>
       </c>
     </row>
     <row r="222">
@@ -13115,10 +13115,10 @@
         <v>2.08</v>
       </c>
       <c r="I222" t="n">
-        <v>1.8156</v>
+        <v>1.8824</v>
       </c>
       <c r="J222" t="n">
-        <v>43.5744</v>
+        <v>45.1776</v>
       </c>
     </row>
     <row r="223">
@@ -13155,10 +13155,10 @@
         <v>1.33</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7974</v>
+        <v>0.7771</v>
       </c>
       <c r="J223" t="n">
-        <v>19.1376</v>
+        <v>18.6504</v>
       </c>
     </row>
     <row r="224">
@@ -13195,10 +13195,10 @@
         <v>1.12</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3465</v>
+        <v>0.3143</v>
       </c>
       <c r="J224" t="n">
-        <v>8.316000000000001</v>
+        <v>7.5432</v>
       </c>
     </row>
     <row r="225">
@@ -13235,10 +13235,10 @@
         <v>0.97</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1871</v>
+        <v>-0.1572</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.4904</v>
+        <v>-3.7728</v>
       </c>
     </row>
     <row r="226">
@@ -13275,10 +13275,10 @@
         <v>0.96</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.221</v>
+        <v>-0.1882</v>
       </c>
       <c r="J226" t="n">
-        <v>-5.304</v>
+        <v>-4.5168</v>
       </c>
     </row>
     <row r="227">
@@ -13315,10 +13315,10 @@
         <v>0.98</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.0231</v>
+        <v>-0.0158</v>
       </c>
       <c r="J227" t="n">
-        <v>-0.5544</v>
+        <v>-0.3792</v>
       </c>
     </row>
     <row r="228">
@@ -13355,10 +13355,10 @@
         <v>0.84</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1964</v>
+        <v>-0.1792</v>
       </c>
       <c r="J228" t="n">
-        <v>-4.7136</v>
+        <v>-4.3008</v>
       </c>
     </row>
     <row r="229">
@@ -13395,10 +13395,10 @@
         <v>0.83</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2064</v>
+        <v>-0.189</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.9536</v>
+        <v>-4.536</v>
       </c>
     </row>
     <row r="230">
@@ -13435,10 +13435,10 @@
         <v>0.78</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2542</v>
+        <v>-0.2362</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.1008</v>
+        <v>-5.6688</v>
       </c>
     </row>
     <row r="231">
@@ -13475,10 +13475,10 @@
         <v>0.64</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3837</v>
+        <v>-0.3709</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.2088</v>
+        <v>-8.9016</v>
       </c>
     </row>
     <row r="232">
@@ -13515,10 +13515,10 @@
         <v>1.62</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2832</v>
+        <v>1.3044</v>
       </c>
       <c r="J232" t="n">
-        <v>38.496</v>
+        <v>39.132</v>
       </c>
     </row>
     <row r="233">
@@ -13555,10 +13555,10 @@
         <v>1.29</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7458</v>
+        <v>0.7161</v>
       </c>
       <c r="J233" t="n">
-        <v>22.374</v>
+        <v>21.483</v>
       </c>
     </row>
     <row r="234">
@@ -13595,10 +13595,10 @@
         <v>1.05</v>
       </c>
       <c r="I234" t="n">
-        <v>0.1801</v>
+        <v>0.1527</v>
       </c>
       <c r="J234" t="n">
-        <v>5.403</v>
+        <v>4.581</v>
       </c>
     </row>
     <row r="235">
@@ -13635,10 +13635,10 @@
         <v>0.99</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0823</v>
+        <v>-0.0615</v>
       </c>
       <c r="J235" t="n">
-        <v>-2.469</v>
+        <v>-1.845</v>
       </c>
     </row>
     <row r="236">
@@ -13675,10 +13675,10 @@
         <v>0.74</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.7488</v>
+        <v>-0.7222</v>
       </c>
       <c r="J236" t="n">
-        <v>-22.464</v>
+        <v>-21.666</v>
       </c>
     </row>
     <row r="237">
@@ -13715,10 +13715,10 @@
         <v>1.31</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5928</v>
+        <v>0.533</v>
       </c>
       <c r="J237" t="n">
-        <v>17.784</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="238">
@@ -13755,10 +13755,10 @@
         <v>1.19</v>
       </c>
       <c r="I238" t="n">
-        <v>0.4007</v>
+        <v>0.3452</v>
       </c>
       <c r="J238" t="n">
-        <v>12.021</v>
+        <v>10.356</v>
       </c>
     </row>
     <row r="239">
@@ -13795,10 +13795,10 @@
         <v>1.16</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3495</v>
+        <v>0.297</v>
       </c>
       <c r="J239" t="n">
-        <v>10.485</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="240">
@@ -13835,10 +13835,10 @@
         <v>0.91</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1422</v>
+        <v>-0.1225</v>
       </c>
       <c r="J240" t="n">
-        <v>-4.266</v>
+        <v>-3.675</v>
       </c>
     </row>
     <row r="241">
@@ -13875,10 +13875,10 @@
         <v>0.83</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2292</v>
+        <v>-0.209</v>
       </c>
       <c r="J241" t="n">
-        <v>-6.876</v>
+        <v>-6.27</v>
       </c>
     </row>
     <row r="242">
@@ -13915,10 +13915,10 @@
         <v>0.87</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.1591</v>
+        <v>-0.1434</v>
       </c>
       <c r="J242" t="n">
-        <v>-3.6593</v>
+        <v>-3.2982</v>
       </c>
     </row>
     <row r="243">
@@ -13955,10 +13955,10 @@
         <v>0.82</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.2121</v>
+        <v>-0.1958</v>
       </c>
       <c r="J243" t="n">
-        <v>-4.8783</v>
+        <v>-4.5034</v>
       </c>
     </row>
     <row r="244">
@@ -13995,10 +13995,10 @@
         <v>0.78</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2511</v>
+        <v>-0.2345</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.7753</v>
+        <v>-5.3935</v>
       </c>
     </row>
     <row r="245">
@@ -14035,10 +14035,10 @@
         <v>0.73</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2967</v>
+        <v>-0.2803</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.8241</v>
+        <v>-6.4469</v>
       </c>
     </row>
     <row r="246">
@@ -14075,10 +14075,10 @@
         <v>0.65</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3697</v>
+        <v>-0.3561</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.5031</v>
+        <v>-8.190300000000001</v>
       </c>
     </row>
     <row r="247">
@@ -14115,10 +14115,10 @@
         <v>1.53</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6379</v>
+        <v>0.5669</v>
       </c>
       <c r="J247" t="n">
-        <v>14.6717</v>
+        <v>13.0387</v>
       </c>
     </row>
     <row r="248">
@@ -14155,10 +14155,10 @@
         <v>1.5</v>
       </c>
       <c r="I248" t="n">
-        <v>0.6084000000000001</v>
+        <v>0.538</v>
       </c>
       <c r="J248" t="n">
-        <v>13.9932</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="249">
@@ -14195,10 +14195,10 @@
         <v>1.31</v>
       </c>
       <c r="I249" t="n">
-        <v>0.4149</v>
+        <v>0.3549</v>
       </c>
       <c r="J249" t="n">
-        <v>9.5427</v>
+        <v>8.162699999999999</v>
       </c>
     </row>
     <row r="250">
@@ -14235,10 +14235,10 @@
         <v>1.17</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2531</v>
+        <v>0.2077</v>
       </c>
       <c r="J250" t="n">
-        <v>5.8213</v>
+        <v>4.7771</v>
       </c>
     </row>
     <row r="251">
@@ -14275,10 +14275,10 @@
         <v>1.11</v>
       </c>
       <c r="I251" t="n">
-        <v>0.1734</v>
+        <v>0.1371</v>
       </c>
       <c r="J251" t="n">
-        <v>3.9882</v>
+        <v>3.1533</v>
       </c>
     </row>
     <row r="252">
@@ -14315,10 +14315,10 @@
         <v>1.26</v>
       </c>
       <c r="I252" t="n">
-        <v>0.6946</v>
+        <v>0.661</v>
       </c>
       <c r="J252" t="n">
-        <v>19.4488</v>
+        <v>18.508</v>
       </c>
     </row>
     <row r="253">
@@ -14355,10 +14355,10 @@
         <v>1.15</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4478</v>
+        <v>0.4075</v>
       </c>
       <c r="J253" t="n">
-        <v>12.5384</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="254">
@@ -14395,10 +14395,10 @@
         <v>1.07</v>
       </c>
       <c r="I254" t="n">
-        <v>0.2461</v>
+        <v>0.2125</v>
       </c>
       <c r="J254" t="n">
-        <v>6.8908</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="255">
@@ -14435,10 +14435,10 @@
         <v>1</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0139</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="J255" t="n">
-        <v>-0.3892</v>
+        <v>-0.2688</v>
       </c>
     </row>
     <row r="256">
@@ -14475,10 +14475,10 @@
         <v>0.97</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1515</v>
+        <v>-0.1204</v>
       </c>
       <c r="J256" t="n">
-        <v>-4.242</v>
+        <v>-3.3712</v>
       </c>
     </row>
     <row r="257">
@@ -14515,10 +14515,10 @@
         <v>1.33</v>
       </c>
       <c r="I257" t="n">
-        <v>0.6462</v>
+        <v>0.5884</v>
       </c>
       <c r="J257" t="n">
-        <v>18.0936</v>
+        <v>16.4752</v>
       </c>
     </row>
     <row r="258">
@@ -14555,10 +14555,10 @@
         <v>1.08</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2134</v>
+        <v>0.1708</v>
       </c>
       <c r="J258" t="n">
-        <v>5.9752</v>
+        <v>4.7824</v>
       </c>
     </row>
     <row r="259">
@@ -14595,10 +14595,10 @@
         <v>0.99</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.0249</v>
+        <v>-0.018</v>
       </c>
       <c r="J259" t="n">
-        <v>-0.6972</v>
+        <v>-0.504</v>
       </c>
     </row>
     <row r="260">
@@ -14635,10 +14635,10 @@
         <v>0.97</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.0578</v>
+        <v>-0.0454</v>
       </c>
       <c r="J260" t="n">
-        <v>-1.6184</v>
+        <v>-1.2712</v>
       </c>
     </row>
     <row r="261">
@@ -14675,10 +14675,10 @@
         <v>0.6</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4367</v>
+        <v>-0.4303</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.2276</v>
+        <v>-12.0484</v>
       </c>
     </row>
     <row r="262">
@@ -14715,10 +14715,10 @@
         <v>1.42</v>
       </c>
       <c r="I262" t="n">
-        <v>0.9837</v>
+        <v>0.978</v>
       </c>
       <c r="J262" t="n">
-        <v>24.5925</v>
+        <v>24.45</v>
       </c>
     </row>
     <row r="263">
@@ -14755,10 +14755,10 @@
         <v>1.33</v>
       </c>
       <c r="I263" t="n">
-        <v>0.8127</v>
+        <v>0.7893</v>
       </c>
       <c r="J263" t="n">
-        <v>20.3175</v>
+        <v>19.7325</v>
       </c>
     </row>
     <row r="264">
@@ -14795,10 +14795,10 @@
         <v>1.22</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="J264" t="n">
-        <v>14.68</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="265">
@@ -14835,10 +14835,10 @@
         <v>1.06</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1993</v>
+        <v>0.1712</v>
       </c>
       <c r="J265" t="n">
-        <v>4.9825</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="266">
@@ -14875,10 +14875,10 @@
         <v>0.98</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.1352</v>
+        <v>-0.1081</v>
       </c>
       <c r="J266" t="n">
-        <v>-3.38</v>
+        <v>-2.7025</v>
       </c>
     </row>
     <row r="267">
@@ -14915,10 +14915,10 @@
         <v>1.16</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3944</v>
+        <v>0.3406</v>
       </c>
       <c r="J267" t="n">
-        <v>9.859999999999999</v>
+        <v>8.515000000000001</v>
       </c>
     </row>
     <row r="268">
@@ -14955,10 +14955,10 @@
         <v>0.9</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1386</v>
+        <v>-0.1215</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.465</v>
+        <v>-3.0375</v>
       </c>
     </row>
     <row r="269">
@@ -14995,10 +14995,10 @@
         <v>0.86</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.181</v>
+        <v>-0.162</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.525</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="270">
@@ -15035,10 +15035,10 @@
         <v>0.82</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2217</v>
+        <v>-0.2022</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.5425</v>
+        <v>-5.055</v>
       </c>
     </row>
     <row r="271">
@@ -15075,10 +15075,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.346</v>
+        <v>-0.3305</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.65</v>
+        <v>-8.262499999999999</v>
       </c>
     </row>
     <row r="272">
@@ -15115,10 +15115,10 @@
         <v>1.16</v>
       </c>
       <c r="I272" t="n">
-        <v>0.3645</v>
+        <v>0.3099</v>
       </c>
       <c r="J272" t="n">
-        <v>9.112500000000001</v>
+        <v>7.7475</v>
       </c>
     </row>
     <row r="273">
@@ -15155,10 +15155,10 @@
         <v>1.08</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2127</v>
+        <v>0.1703</v>
       </c>
       <c r="J273" t="n">
-        <v>5.3175</v>
+        <v>4.2575</v>
       </c>
     </row>
     <row r="274">
@@ -15195,10 +15195,10 @@
         <v>1.01</v>
       </c>
       <c r="I274" t="n">
-        <v>0.0435</v>
+        <v>0.0294</v>
       </c>
       <c r="J274" t="n">
-        <v>1.0875</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="275">
@@ -15235,10 +15235,10 @@
         <v>0.91</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1353</v>
+        <v>-0.1161</v>
       </c>
       <c r="J275" t="n">
-        <v>-3.3825</v>
+        <v>-2.9025</v>
       </c>
     </row>
     <row r="276">
@@ -15275,10 +15275,10 @@
         <v>0.83</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.222</v>
+        <v>-0.2015</v>
       </c>
       <c r="J276" t="n">
-        <v>-5.55</v>
+        <v>-5.0375</v>
       </c>
     </row>
     <row r="277">
@@ -15315,10 +15315,10 @@
         <v>1.2</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5613</v>
+        <v>0.5226</v>
       </c>
       <c r="J277" t="n">
-        <v>14.0325</v>
+        <v>13.065</v>
       </c>
     </row>
     <row r="278">
@@ -15355,10 +15355,10 @@
         <v>1.18</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5161</v>
+        <v>0.4765</v>
       </c>
       <c r="J278" t="n">
-        <v>12.9025</v>
+        <v>11.9125</v>
       </c>
     </row>
     <row r="279">
@@ -15395,10 +15395,10 @@
         <v>1.17</v>
       </c>
       <c r="I279" t="n">
-        <v>0.4931</v>
+        <v>0.4533</v>
       </c>
       <c r="J279" t="n">
-        <v>12.3275</v>
+        <v>11.3325</v>
       </c>
     </row>
     <row r="280">
@@ -15435,10 +15435,10 @@
         <v>1.13</v>
       </c>
       <c r="I280" t="n">
-        <v>0.3985</v>
+        <v>0.3592</v>
       </c>
       <c r="J280" t="n">
-        <v>9.9625</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="281">
@@ -15475,10 +15475,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.584</v>
+        <v>-0.5456</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.6</v>
+        <v>-13.64</v>
       </c>
     </row>
     <row r="282">
@@ -15515,10 +15515,10 @@
         <v>1.64</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3107</v>
+        <v>1.3338</v>
       </c>
       <c r="J282" t="n">
-        <v>44.5638</v>
+        <v>45.3492</v>
       </c>
     </row>
     <row r="283">
@@ -15555,10 +15555,10 @@
         <v>1.2</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5538</v>
+        <v>0.5165</v>
       </c>
       <c r="J283" t="n">
-        <v>18.8292</v>
+        <v>17.561</v>
       </c>
     </row>
     <row r="284">
@@ -15595,10 +15595,10 @@
         <v>1.04</v>
       </c>
       <c r="I284" t="n">
-        <v>0.1489</v>
+        <v>0.1241</v>
       </c>
       <c r="J284" t="n">
-        <v>5.0626</v>
+        <v>4.2194</v>
       </c>
     </row>
     <row r="285">
@@ -15635,10 +15635,10 @@
         <v>0.91</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3416</v>
+        <v>-0.2998</v>
       </c>
       <c r="J285" t="n">
-        <v>-11.6144</v>
+        <v>-10.1932</v>
       </c>
     </row>
     <row r="286">
@@ -15675,10 +15675,10 @@
         <v>0.89</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3949</v>
+        <v>-0.3526</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.4266</v>
+        <v>-11.9884</v>
       </c>
     </row>
     <row r="287">
@@ -15715,10 +15715,10 @@
         <v>1.13</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3251</v>
+        <v>0.273</v>
       </c>
       <c r="J287" t="n">
-        <v>11.0534</v>
+        <v>9.282</v>
       </c>
     </row>
     <row r="288">
@@ -15755,10 +15755,10 @@
         <v>1.02</v>
       </c>
       <c r="I288" t="n">
-        <v>0.0838</v>
+        <v>0.0598</v>
       </c>
       <c r="J288" t="n">
-        <v>2.8492</v>
+        <v>2.0332</v>
       </c>
     </row>
     <row r="289">
@@ -15795,10 +15795,10 @@
         <v>1.02</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0838</v>
+        <v>0.0598</v>
       </c>
       <c r="J289" t="n">
-        <v>2.8492</v>
+        <v>2.0332</v>
       </c>
     </row>
     <row r="290">
@@ -15835,10 +15835,10 @@
         <v>0.79</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2559</v>
+        <v>-0.2362</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.7006</v>
+        <v>-8.030799999999999</v>
       </c>
     </row>
     <row r="291">
@@ -15875,10 +15875,10 @@
         <v>0.7</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3414</v>
+        <v>-0.3257</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.6076</v>
+        <v>-11.0738</v>
       </c>
     </row>
     <row r="292">
@@ -15915,10 +15915,10 @@
         <v>0.95</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.0675</v>
+        <v>-0.0556</v>
       </c>
       <c r="J292" t="n">
-        <v>-1.5525</v>
+        <v>-1.2788</v>
       </c>
     </row>
     <row r="293">
@@ -15955,10 +15955,10 @@
         <v>0.88</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.1532</v>
+        <v>-0.1372</v>
       </c>
       <c r="J293" t="n">
-        <v>-3.5236</v>
+        <v>-3.1556</v>
       </c>
     </row>
     <row r="294">
@@ -15995,10 +15995,10 @@
         <v>0.82</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2158</v>
+        <v>-0.1984</v>
       </c>
       <c r="J294" t="n">
-        <v>-4.9634</v>
+        <v>-4.5632</v>
       </c>
     </row>
     <row r="295">
@@ -16035,10 +16035,10 @@
         <v>0.78</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2537</v>
+        <v>-0.2358</v>
       </c>
       <c r="J295" t="n">
-        <v>-5.8351</v>
+        <v>-5.4234</v>
       </c>
     </row>
     <row r="296">
@@ -16075,10 +16075,10 @@
         <v>0.61</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4099</v>
+        <v>-0.3992</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.4277</v>
+        <v>-9.1816</v>
       </c>
     </row>
     <row r="297">
@@ -16115,10 +16115,10 @@
         <v>1.71</v>
       </c>
       <c r="I297" t="n">
-        <v>1.3715</v>
+        <v>1.3956</v>
       </c>
       <c r="J297" t="n">
-        <v>31.5445</v>
+        <v>32.0988</v>
       </c>
     </row>
     <row r="298">
@@ -16155,10 +16155,10 @@
         <v>1.62</v>
       </c>
       <c r="I298" t="n">
-        <v>1.2547</v>
+        <v>1.2719</v>
       </c>
       <c r="J298" t="n">
-        <v>28.8581</v>
+        <v>29.2537</v>
       </c>
     </row>
     <row r="299">
@@ -16195,10 +16195,10 @@
         <v>1.22</v>
       </c>
       <c r="I299" t="n">
-        <v>0.5829</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="J299" t="n">
-        <v>13.4067</v>
+        <v>12.6937</v>
       </c>
     </row>
     <row r="300">
@@ -16235,10 +16235,10 @@
         <v>0.96</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2137</v>
+        <v>-0.18</v>
       </c>
       <c r="J300" t="n">
-        <v>-4.9151</v>
+        <v>-4.14</v>
       </c>
     </row>
     <row r="301">
@@ -16275,10 +16275,10 @@
         <v>0.73</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.7883</v>
+        <v>-0.7683</v>
       </c>
       <c r="J301" t="n">
-        <v>-18.1309</v>
+        <v>-17.6709</v>
       </c>
     </row>
     <row r="302">
@@ -16315,10 +16315,10 @@
         <v>1.34</v>
       </c>
       <c r="I302" t="n">
-        <v>0.6635</v>
+        <v>0.6065</v>
       </c>
       <c r="J302" t="n">
-        <v>18.578</v>
+        <v>16.982</v>
       </c>
     </row>
     <row r="303">
@@ -16355,10 +16355,10 @@
         <v>1.1</v>
       </c>
       <c r="I303" t="n">
-        <v>0.2547</v>
+        <v>0.2078</v>
       </c>
       <c r="J303" t="n">
-        <v>7.1316</v>
+        <v>5.8184</v>
       </c>
     </row>
     <row r="304">
@@ -16395,10 +16395,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.0815</v>
       </c>
       <c r="J304" t="n">
-        <v>-2.7468</v>
+        <v>-2.282</v>
       </c>
     </row>
     <row r="305">
@@ -16435,10 +16435,10 @@
         <v>0.93</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1105</v>
+        <v>-0.093</v>
       </c>
       <c r="J305" t="n">
-        <v>-3.094</v>
+        <v>-2.604</v>
       </c>
     </row>
     <row r="306">
@@ -16475,10 +16475,10 @@
         <v>0.63</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4098</v>
+        <v>-0.4004</v>
       </c>
       <c r="J306" t="n">
-        <v>-11.4744</v>
+        <v>-11.2112</v>
       </c>
     </row>
     <row r="307">
@@ -16515,10 +16515,10 @@
         <v>1.38</v>
       </c>
       <c r="I307" t="n">
-        <v>0.9261</v>
+        <v>0.9109</v>
       </c>
       <c r="J307" t="n">
-        <v>25.9308</v>
+        <v>25.5052</v>
       </c>
     </row>
     <row r="308">
@@ -16555,10 +16555,10 @@
         <v>1.29</v>
       </c>
       <c r="I308" t="n">
-        <v>0.7448</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="J308" t="n">
-        <v>20.8544</v>
+        <v>20.0256</v>
       </c>
     </row>
     <row r="309">
@@ -16595,10 +16595,10 @@
         <v>1.17</v>
       </c>
       <c r="I309" t="n">
-        <v>0.4857</v>
+        <v>0.448</v>
       </c>
       <c r="J309" t="n">
-        <v>13.5996</v>
+        <v>12.544</v>
       </c>
     </row>
     <row r="310">
@@ -16635,10 +16635,10 @@
         <v>1.03</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1143</v>
+        <v>0.0931</v>
       </c>
       <c r="J310" t="n">
-        <v>3.2004</v>
+        <v>2.6068</v>
       </c>
     </row>
     <row r="311">
@@ -16675,10 +16675,10 @@
         <v>0.84</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5212</v>
+        <v>-0.4811</v>
       </c>
       <c r="J311" t="n">
-        <v>-14.5936</v>
+        <v>-13.4708</v>
       </c>
     </row>
     <row r="312">
@@ -16715,10 +16715,10 @@
         <v>1.13</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3246</v>
+        <v>0.2725</v>
       </c>
       <c r="J312" t="n">
-        <v>7.7904</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="313">
@@ -16755,10 +16755,10 @@
         <v>1.03</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1106</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="J313" t="n">
-        <v>2.6544</v>
+        <v>1.9584</v>
       </c>
     </row>
     <row r="314">
@@ -16795,10 +16795,10 @@
         <v>1.01</v>
       </c>
       <c r="I314" t="n">
-        <v>0.0527</v>
+        <v>0.0355</v>
       </c>
       <c r="J314" t="n">
-        <v>1.2648</v>
+        <v>0.852</v>
       </c>
     </row>
     <row r="315">
@@ -16835,10 +16835,10 @@
         <v>0.76</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2852</v>
+        <v>-0.2664</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.8448</v>
+        <v>-6.3936</v>
       </c>
     </row>
     <row r="316">
@@ -16875,10 +16875,10 @@
         <v>0.74</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3042</v>
+        <v>-0.2863</v>
       </c>
       <c r="J316" t="n">
-        <v>-7.3008</v>
+        <v>-6.8712</v>
       </c>
     </row>
     <row r="317">
@@ -16915,10 +16915,10 @@
         <v>1.59</v>
       </c>
       <c r="I317" t="n">
-        <v>1.2109</v>
+        <v>1.2262</v>
       </c>
       <c r="J317" t="n">
-        <v>29.0616</v>
+        <v>29.4288</v>
       </c>
     </row>
     <row r="318">
@@ -16955,10 +16955,10 @@
         <v>1.52</v>
       </c>
       <c r="I318" t="n">
-        <v>1.1178</v>
+        <v>1.1301</v>
       </c>
       <c r="J318" t="n">
-        <v>26.8272</v>
+        <v>27.1224</v>
       </c>
     </row>
     <row r="319">
@@ -16995,10 +16995,10 @@
         <v>1.13</v>
       </c>
       <c r="I319" t="n">
-        <v>0.3751</v>
+        <v>0.3426</v>
       </c>
       <c r="J319" t="n">
-        <v>9.0024</v>
+        <v>8.2224</v>
       </c>
     </row>
     <row r="320">
@@ -17035,10 +17035,10 @@
         <v>1.08</v>
       </c>
       <c r="I320" t="n">
-        <v>0.2454</v>
+        <v>0.2151</v>
       </c>
       <c r="J320" t="n">
-        <v>5.8896</v>
+        <v>5.1624</v>
       </c>
     </row>
     <row r="321">
@@ -17075,10 +17075,10 @@
         <v>1.02</v>
       </c>
       <c r="I321" t="n">
-        <v>0.056</v>
+        <v>0.0396</v>
       </c>
       <c r="J321" t="n">
-        <v>1.344</v>
+        <v>0.9504</v>
       </c>
     </row>
     <row r="322">
@@ -17115,10 +17115,10 @@
         <v>1.54</v>
       </c>
       <c r="I322" t="n">
-        <v>1.137</v>
+        <v>1.1503</v>
       </c>
       <c r="J322" t="n">
-        <v>27.288</v>
+        <v>27.6072</v>
       </c>
     </row>
     <row r="323">
@@ -17155,10 +17155,10 @@
         <v>1.45</v>
       </c>
       <c r="I323" t="n">
-        <v>1.0119</v>
+        <v>1.0134</v>
       </c>
       <c r="J323" t="n">
-        <v>24.2856</v>
+        <v>24.3216</v>
       </c>
     </row>
     <row r="324">
@@ -17195,10 +17195,10 @@
         <v>1.24</v>
       </c>
       <c r="I324" t="n">
-        <v>0.617</v>
+        <v>0.5898</v>
       </c>
       <c r="J324" t="n">
-        <v>14.808</v>
+        <v>14.1552</v>
       </c>
     </row>
     <row r="325">
@@ -17235,10 +17235,10 @@
         <v>1.18</v>
       </c>
       <c r="I325" t="n">
-        <v>0.4863</v>
+        <v>0.4555</v>
       </c>
       <c r="J325" t="n">
-        <v>11.6712</v>
+        <v>10.932</v>
       </c>
     </row>
     <row r="326">
@@ -17275,10 +17275,10 @@
         <v>1.14</v>
       </c>
       <c r="I326" t="n">
-        <v>0.3928</v>
+        <v>0.3608</v>
       </c>
       <c r="J326" t="n">
-        <v>9.427199999999999</v>
+        <v>8.6592</v>
       </c>
     </row>
     <row r="327">
@@ -17315,10 +17315,10 @@
         <v>1.07</v>
       </c>
       <c r="I327" t="n">
-        <v>0.2263</v>
+        <v>0.1841</v>
       </c>
       <c r="J327" t="n">
-        <v>5.4312</v>
+        <v>4.4184</v>
       </c>
     </row>
     <row r="328">
@@ -17355,10 +17355,10 @@
         <v>0.93</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.0856</v>
       </c>
       <c r="J328" t="n">
-        <v>-2.3904</v>
+        <v>-2.0544</v>
       </c>
     </row>
     <row r="329">
@@ -17395,10 +17395,10 @@
         <v>0.77</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.2672</v>
+        <v>-0.2486</v>
       </c>
       <c r="J329" t="n">
-        <v>-6.4128</v>
+        <v>-5.9664</v>
       </c>
     </row>
     <row r="330">
@@ -17435,10 +17435,10 @@
         <v>0.76</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2768</v>
+        <v>-0.2583</v>
       </c>
       <c r="J330" t="n">
-        <v>-6.6432</v>
+        <v>-6.1992</v>
       </c>
     </row>
     <row r="331">
@@ -17475,10 +17475,10 @@
         <v>0.72</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3145</v>
+        <v>-0.2973</v>
       </c>
       <c r="J331" t="n">
-        <v>-7.548</v>
+        <v>-7.1352</v>
       </c>
     </row>
     <row r="332">
@@ -17515,10 +17515,10 @@
         <v>1.55</v>
       </c>
       <c r="I332" t="n">
-        <v>0.9392</v>
+        <v>0.8941</v>
       </c>
       <c r="J332" t="n">
-        <v>38.5072</v>
+        <v>36.6581</v>
       </c>
     </row>
     <row r="333">
@@ -17555,10 +17555,10 @@
         <v>1.15</v>
       </c>
       <c r="I333" t="n">
-        <v>0.3312</v>
+        <v>0.2801</v>
       </c>
       <c r="J333" t="n">
-        <v>13.5792</v>
+        <v>11.4841</v>
       </c>
     </row>
     <row r="334">
@@ -17595,10 +17595,10 @@
         <v>1.06</v>
       </c>
       <c r="I334" t="n">
-        <v>0.1611</v>
+        <v>0.1279</v>
       </c>
       <c r="J334" t="n">
-        <v>6.6051</v>
+        <v>5.2439</v>
       </c>
     </row>
     <row r="335">
@@ -17635,10 +17635,10 @@
         <v>0.88</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.1767</v>
+        <v>-0.1563</v>
       </c>
       <c r="J335" t="n">
-        <v>-7.2447</v>
+        <v>-6.4083</v>
       </c>
     </row>
     <row r="336">
@@ -17675,10 +17675,10 @@
         <v>0.79</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2698</v>
+        <v>-0.251</v>
       </c>
       <c r="J336" t="n">
-        <v>-11.0618</v>
+        <v>-10.291</v>
       </c>
     </row>
     <row r="337">
@@ -17715,10 +17715,10 @@
         <v>1.5</v>
       </c>
       <c r="I337" t="n">
-        <v>1.1178</v>
+        <v>1.1304</v>
       </c>
       <c r="J337" t="n">
-        <v>45.8298</v>
+        <v>46.3464</v>
       </c>
     </row>
     <row r="338">
@@ -17755,10 +17755,10 @@
         <v>1.41</v>
       </c>
       <c r="I338" t="n">
-        <v>0.9813</v>
+        <v>0.9746</v>
       </c>
       <c r="J338" t="n">
-        <v>40.2333</v>
+        <v>39.9586</v>
       </c>
     </row>
     <row r="339">
@@ -17795,10 +17795,10 @@
         <v>1.13</v>
       </c>
       <c r="I339" t="n">
-        <v>0.3937</v>
+        <v>0.3568</v>
       </c>
       <c r="J339" t="n">
-        <v>16.1417</v>
+        <v>14.6288</v>
       </c>
     </row>
     <row r="340">
@@ -17835,10 +17835,10 @@
         <v>0.87</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4473</v>
+        <v>-0.4054</v>
       </c>
       <c r="J340" t="n">
-        <v>-18.3393</v>
+        <v>-16.6214</v>
       </c>
     </row>
     <row r="341">
@@ -17875,10 +17875,10 @@
         <v>0.8</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.6153</v>
+        <v>-0.5794</v>
       </c>
       <c r="J341" t="n">
-        <v>-25.2273</v>
+        <v>-23.7554</v>
       </c>
     </row>
     <row r="342">
@@ -17915,10 +17915,10 @@
         <v>1.01</v>
       </c>
       <c r="I342" t="n">
-        <v>0.0538</v>
+        <v>0.0364</v>
       </c>
       <c r="J342" t="n">
-        <v>1.614</v>
+        <v>1.092</v>
       </c>
     </row>
     <row r="343">
@@ -17955,10 +17955,10 @@
         <v>0.98</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.038</v>
+        <v>-0.0297</v>
       </c>
       <c r="J343" t="n">
-        <v>-1.14</v>
+        <v>-0.891</v>
       </c>
     </row>
     <row r="344">
@@ -17995,10 +17995,10 @@
         <v>0.96</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0558</v>
       </c>
       <c r="J344" t="n">
-        <v>-2.043</v>
+        <v>-1.674</v>
       </c>
     </row>
     <row r="345">
@@ -18035,10 +18035,10 @@
         <v>0.89</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1521</v>
+        <v>-0.1333</v>
       </c>
       <c r="J345" t="n">
-        <v>-4.563</v>
+        <v>-3.999</v>
       </c>
     </row>
     <row r="346">
@@ -18075,10 +18075,10 @@
         <v>0.8</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2457</v>
+        <v>-0.2258</v>
       </c>
       <c r="J346" t="n">
-        <v>-7.371</v>
+        <v>-6.774</v>
       </c>
     </row>
     <row r="347">
@@ -18115,10 +18115,10 @@
         <v>1.33</v>
       </c>
       <c r="I347" t="n">
-        <v>0.8132</v>
+        <v>0.7896</v>
       </c>
       <c r="J347" t="n">
-        <v>24.396</v>
+        <v>23.688</v>
       </c>
     </row>
     <row r="348">
@@ -18155,10 +18155,10 @@
         <v>1.32</v>
       </c>
       <c r="I348" t="n">
-        <v>0.7932</v>
+        <v>0.7684</v>
       </c>
       <c r="J348" t="n">
-        <v>23.796</v>
+        <v>23.052</v>
       </c>
     </row>
     <row r="349">
@@ -18195,10 +18195,10 @@
         <v>1.25</v>
       </c>
       <c r="I349" t="n">
-        <v>0.6504</v>
+        <v>0.6187</v>
       </c>
       <c r="J349" t="n">
-        <v>19.512</v>
+        <v>18.561</v>
       </c>
     </row>
     <row r="350">
@@ -18235,10 +18235,10 @@
         <v>1.13</v>
       </c>
       <c r="I350" t="n">
-        <v>0.3858</v>
+        <v>0.3516</v>
       </c>
       <c r="J350" t="n">
-        <v>11.574</v>
+        <v>10.548</v>
       </c>
     </row>
     <row r="351">
@@ -18275,10 +18275,10 @@
         <v>0.97</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.1715</v>
+        <v>-0.1402</v>
       </c>
       <c r="J351" t="n">
-        <v>-5.145</v>
+        <v>-4.206</v>
       </c>
     </row>
     <row r="352">
@@ -18315,10 +18315,10 @@
         <v>1.77</v>
       </c>
       <c r="I352" t="n">
-        <v>1.4558</v>
+        <v>1.4872</v>
       </c>
       <c r="J352" t="n">
-        <v>34.9392</v>
+        <v>35.6928</v>
       </c>
     </row>
     <row r="353">
@@ -18355,10 +18355,10 @@
         <v>1.52</v>
       </c>
       <c r="I353" t="n">
-        <v>1.1273</v>
+        <v>1.1396</v>
       </c>
       <c r="J353" t="n">
-        <v>27.0552</v>
+        <v>27.3504</v>
       </c>
     </row>
     <row r="354">
@@ -18395,10 +18395,10 @@
         <v>1.18</v>
       </c>
       <c r="I354" t="n">
-        <v>0.4995</v>
+        <v>0.4659</v>
       </c>
       <c r="J354" t="n">
-        <v>11.988</v>
+        <v>11.1816</v>
       </c>
     </row>
     <row r="355">
@@ -18435,10 +18435,10 @@
         <v>1.04</v>
       </c>
       <c r="I355" t="n">
-        <v>0.1344</v>
+        <v>0.1108</v>
       </c>
       <c r="J355" t="n">
-        <v>3.2256</v>
+        <v>2.6592</v>
       </c>
     </row>
     <row r="356">
@@ -18475,10 +18475,10 @@
         <v>0.59</v>
       </c>
       <c r="I356" t="n">
-        <v>-1.0727</v>
+        <v>-1.0851</v>
       </c>
       <c r="J356" t="n">
-        <v>-25.7448</v>
+        <v>-26.0424</v>
       </c>
     </row>
     <row r="357">
@@ -18515,10 +18515,10 @@
         <v>1.63</v>
       </c>
       <c r="I357" t="n">
-        <v>1.0588</v>
+        <v>1.0423</v>
       </c>
       <c r="J357" t="n">
-        <v>25.4112</v>
+        <v>25.0152</v>
       </c>
     </row>
     <row r="358">
@@ -18555,10 +18555,10 @@
         <v>1.26</v>
       </c>
       <c r="I358" t="n">
-        <v>0.5308</v>
+        <v>0.4714</v>
       </c>
       <c r="J358" t="n">
-        <v>12.7392</v>
+        <v>11.3136</v>
       </c>
     </row>
     <row r="359">
@@ -18595,10 +18595,10 @@
         <v>0.82</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.2333</v>
+        <v>-0.2129</v>
       </c>
       <c r="J359" t="n">
-        <v>-5.5992</v>
+        <v>-5.1096</v>
       </c>
     </row>
     <row r="360">
@@ -18635,10 +18635,10 @@
         <v>0.68</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.3668</v>
+        <v>-0.3537</v>
       </c>
       <c r="J360" t="n">
-        <v>-8.8032</v>
+        <v>-8.488799999999999</v>
       </c>
     </row>
     <row r="361">
@@ -18675,10 +18675,10 @@
         <v>0.66</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3849</v>
+        <v>-0.3733</v>
       </c>
       <c r="J361" t="n">
-        <v>-9.2376</v>
+        <v>-8.959199999999999</v>
       </c>
     </row>
     <row r="362">
@@ -18715,10 +18715,10 @@
         <v>0.98</v>
       </c>
       <c r="I362" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0012</v>
       </c>
       <c r="J362" t="n">
-        <v>-0.1512</v>
+        <v>0.0216</v>
       </c>
     </row>
     <row r="363">
@@ -18755,10 +18755,10 @@
         <v>0.78</v>
       </c>
       <c r="I363" t="n">
-        <v>-0.2481</v>
+        <v>-0.2326</v>
       </c>
       <c r="J363" t="n">
-        <v>-4.4658</v>
+        <v>-4.1868</v>
       </c>
     </row>
     <row r="364">
@@ -18795,10 +18795,10 @@
         <v>0.68</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.3391</v>
+        <v>-0.3245</v>
       </c>
       <c r="J364" t="n">
-        <v>-6.1038</v>
+        <v>-5.841</v>
       </c>
     </row>
     <row r="365">
@@ -18835,10 +18835,10 @@
         <v>0.64</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.3751</v>
+        <v>-0.3622</v>
       </c>
       <c r="J365" t="n">
-        <v>-6.7518</v>
+        <v>-6.5196</v>
       </c>
     </row>
     <row r="366">
@@ -18875,10 +18875,10 @@
         <v>0.62</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.393</v>
+        <v>-0.3812</v>
       </c>
       <c r="J366" t="n">
-        <v>-7.074</v>
+        <v>-6.8616</v>
       </c>
     </row>
     <row r="367">
@@ -18915,10 +18915,10 @@
         <v>1.83</v>
       </c>
       <c r="I367" t="n">
-        <v>1.4743</v>
+        <v>1.5041</v>
       </c>
       <c r="J367" t="n">
-        <v>26.5374</v>
+        <v>27.0738</v>
       </c>
     </row>
     <row r="368">
@@ -18955,10 +18955,10 @@
         <v>1.47</v>
       </c>
       <c r="I368" t="n">
-        <v>1.0237</v>
+        <v>1.0334</v>
       </c>
       <c r="J368" t="n">
-        <v>18.4266</v>
+        <v>18.6012</v>
       </c>
     </row>
     <row r="369">
@@ -18995,10 +18995,10 @@
         <v>1.42</v>
       </c>
       <c r="I369" t="n">
-        <v>0.9455</v>
+        <v>0.9449</v>
       </c>
       <c r="J369" t="n">
-        <v>17.019</v>
+        <v>17.0082</v>
       </c>
     </row>
     <row r="370">
@@ -19035,10 +19035,10 @@
         <v>1.31</v>
       </c>
       <c r="I370" t="n">
-        <v>0.7382</v>
+        <v>0.7217</v>
       </c>
       <c r="J370" t="n">
-        <v>13.2876</v>
+        <v>12.9906</v>
       </c>
     </row>
     <row r="371">
@@ -19075,10 +19075,10 @@
         <v>1.3</v>
       </c>
       <c r="I371" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.7005</v>
       </c>
       <c r="J371" t="n">
-        <v>12.9276</v>
+        <v>12.609</v>
       </c>
     </row>
     <row r="372">
@@ -19115,10 +19115,10 @@
         <v>1.62</v>
       </c>
       <c r="I372" t="n">
-        <v>1.2574</v>
+        <v>1.2749</v>
       </c>
       <c r="J372" t="n">
-        <v>31.435</v>
+        <v>31.8725</v>
       </c>
     </row>
     <row r="373">
@@ -19155,10 +19155,10 @@
         <v>1.37</v>
       </c>
       <c r="I373" t="n">
-        <v>0.8842</v>
+        <v>0.867</v>
       </c>
       <c r="J373" t="n">
-        <v>22.105</v>
+        <v>21.675</v>
       </c>
     </row>
     <row r="374">
@@ -19195,10 +19195,10 @@
         <v>1.23</v>
       </c>
       <c r="I374" t="n">
-        <v>0.6051</v>
+        <v>0.574</v>
       </c>
       <c r="J374" t="n">
-        <v>15.1275</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="375">
@@ -19235,10 +19235,10 @@
         <v>1.16</v>
       </c>
       <c r="I375" t="n">
-        <v>0.4517</v>
+        <v>0.4184</v>
       </c>
       <c r="J375" t="n">
-        <v>11.2925</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="376">
@@ -19275,10 +19275,10 @@
         <v>0.8</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.6313</v>
+        <v>-0.5988</v>
       </c>
       <c r="J376" t="n">
-        <v>-15.7825</v>
+        <v>-14.97</v>
       </c>
     </row>
     <row r="377">
@@ -19315,10 +19315,10 @@
         <v>1.01</v>
       </c>
       <c r="I377" t="n">
-        <v>0.0912</v>
+        <v>0.0725</v>
       </c>
       <c r="J377" t="n">
-        <v>2.28</v>
+        <v>1.8125</v>
       </c>
     </row>
     <row r="378">
@@ -19355,10 +19355,10 @@
         <v>0.85</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.183</v>
+        <v>-0.1667</v>
       </c>
       <c r="J378" t="n">
-        <v>-4.575</v>
+        <v>-4.1675</v>
       </c>
     </row>
     <row r="379">
@@ -19395,10 +19395,10 @@
         <v>0.84</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.1935</v>
+        <v>-0.1771</v>
       </c>
       <c r="J379" t="n">
-        <v>-4.8375</v>
+        <v>-4.4275</v>
       </c>
     </row>
     <row r="380">
@@ -19435,10 +19435,10 @@
         <v>0.62</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.3985</v>
+        <v>-0.3868</v>
       </c>
       <c r="J380" t="n">
-        <v>-9.9625</v>
+        <v>-9.67</v>
       </c>
     </row>
     <row r="381">
@@ -19475,10 +19475,10 @@
         <v>0.61</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.4074</v>
+        <v>-0.3965</v>
       </c>
       <c r="J381" t="n">
-        <v>-10.185</v>
+        <v>-9.9125</v>
       </c>
     </row>
     <row r="382">
@@ -19515,10 +19515,10 @@
         <v>0.86</v>
       </c>
       <c r="I382" t="n">
-        <v>-0.1274</v>
+        <v>-0.105</v>
       </c>
       <c r="J382" t="n">
-        <v>-2.2932</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="383">
@@ -19555,10 +19555,10 @@
         <v>0.7</v>
       </c>
       <c r="I383" t="n">
-        <v>-0.3005</v>
+        <v>-0.2893</v>
       </c>
       <c r="J383" t="n">
-        <v>-5.409</v>
+        <v>-5.2074</v>
       </c>
     </row>
     <row r="384">
@@ -19595,10 +19595,10 @@
         <v>0.5</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.4782</v>
+        <v>-0.4747</v>
       </c>
       <c r="J384" t="n">
-        <v>-8.6076</v>
+        <v>-8.544600000000001</v>
       </c>
     </row>
     <row r="385">
@@ -19635,10 +19635,10 @@
         <v>0.46</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.5135</v>
+        <v>-0.5131</v>
       </c>
       <c r="J385" t="n">
-        <v>-9.243</v>
+        <v>-9.235799999999999</v>
       </c>
     </row>
     <row r="386">
@@ -19675,10 +19675,10 @@
         <v>0.42</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.5488</v>
+        <v>-0.5526</v>
       </c>
       <c r="J386" t="n">
-        <v>-9.878399999999999</v>
+        <v>-9.9468</v>
       </c>
     </row>
     <row r="387">
@@ -19715,10 +19715,10 @@
         <v>1.79</v>
       </c>
       <c r="I387" t="n">
-        <v>1.4097</v>
+        <v>1.4375</v>
       </c>
       <c r="J387" t="n">
-        <v>25.3746</v>
+        <v>25.875</v>
       </c>
     </row>
     <row r="388">
@@ -19755,10 +19755,10 @@
         <v>1.74</v>
       </c>
       <c r="I388" t="n">
-        <v>1.3502</v>
+        <v>1.3755</v>
       </c>
       <c r="J388" t="n">
-        <v>24.3036</v>
+        <v>24.759</v>
       </c>
     </row>
     <row r="389">
@@ -19795,10 +19795,10 @@
         <v>1.56</v>
       </c>
       <c r="I389" t="n">
-        <v>1.1331</v>
+        <v>1.1538</v>
       </c>
       <c r="J389" t="n">
-        <v>20.3958</v>
+        <v>20.7684</v>
       </c>
     </row>
     <row r="390">
@@ -19835,10 +19835,10 @@
         <v>1.43</v>
       </c>
       <c r="I390" t="n">
-        <v>0.95</v>
+        <v>0.954</v>
       </c>
       <c r="J390" t="n">
-        <v>17.1</v>
+        <v>17.172</v>
       </c>
     </row>
     <row r="391">
@@ -19875,10 +19875,10 @@
         <v>1.37</v>
       </c>
       <c r="I391" t="n">
-        <v>0.8397</v>
+        <v>0.8329</v>
       </c>
       <c r="J391" t="n">
-        <v>15.1146</v>
+        <v>14.9922</v>
       </c>
     </row>
     <row r="392">
@@ -19915,10 +19915,10 @@
         <v>1.39</v>
       </c>
       <c r="I392" t="n">
-        <v>0.9495</v>
+        <v>0.9376</v>
       </c>
       <c r="J392" t="n">
-        <v>25.6365</v>
+        <v>25.3152</v>
       </c>
     </row>
     <row r="393">
@@ -19955,10 +19955,10 @@
         <v>1.38</v>
       </c>
       <c r="I393" t="n">
-        <v>0.9306</v>
+        <v>0.916</v>
       </c>
       <c r="J393" t="n">
-        <v>25.1262</v>
+        <v>24.732</v>
       </c>
     </row>
     <row r="394">
@@ -19995,10 +19995,10 @@
         <v>1.14</v>
       </c>
       <c r="I394" t="n">
-        <v>0.4186</v>
+        <v>0.3805</v>
       </c>
       <c r="J394" t="n">
-        <v>11.3022</v>
+        <v>10.2735</v>
       </c>
     </row>
     <row r="395">
@@ -20035,10 +20035,10 @@
         <v>0.89</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.3931</v>
+        <v>-0.3506</v>
       </c>
       <c r="J395" t="n">
-        <v>-10.6137</v>
+        <v>-9.466200000000001</v>
       </c>
     </row>
     <row r="396">
@@ -20075,10 +20075,10 @@
         <v>0.83</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.5422</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="J396" t="n">
-        <v>-14.6394</v>
+        <v>-13.5675</v>
       </c>
     </row>
     <row r="397">
@@ -20115,10 +20115,10 @@
         <v>1.08</v>
       </c>
       <c r="I397" t="n">
-        <v>0.2287</v>
+        <v>0.1842</v>
       </c>
       <c r="J397" t="n">
-        <v>6.1749</v>
+        <v>4.9734</v>
       </c>
     </row>
     <row r="398">
@@ -20155,10 +20155,10 @@
         <v>1.05</v>
       </c>
       <c r="I398" t="n">
-        <v>0.1625</v>
+        <v>0.1257</v>
       </c>
       <c r="J398" t="n">
-        <v>4.3875</v>
+        <v>3.3939</v>
       </c>
     </row>
     <row r="399">
@@ -20195,10 +20195,10 @@
         <v>1.03</v>
       </c>
       <c r="I399" t="n">
-        <v>0.1134</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J399" t="n">
-        <v>3.0618</v>
+        <v>2.268</v>
       </c>
     </row>
     <row r="400">
@@ -20235,10 +20235,10 @@
         <v>0.88</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.1624</v>
+        <v>-0.1433</v>
       </c>
       <c r="J400" t="n">
-        <v>-4.3848</v>
+        <v>-3.8691</v>
       </c>
     </row>
     <row r="401">
@@ -20275,10 +20275,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.4652</v>
+        <v>-0.4613</v>
       </c>
       <c r="J401" t="n">
-        <v>-12.5604</v>
+        <v>-12.4551</v>
       </c>
     </row>
     <row r="402">
@@ -20315,10 +20315,10 @@
         <v>1.25</v>
       </c>
       <c r="I402" t="n">
-        <v>0.5181</v>
+        <v>0.4591</v>
       </c>
       <c r="J402" t="n">
-        <v>15.0249</v>
+        <v>13.3139</v>
       </c>
     </row>
     <row r="403">
@@ -20355,10 +20355,10 @@
         <v>1.04</v>
       </c>
       <c r="I403" t="n">
-        <v>0.1251</v>
+        <v>0.0946</v>
       </c>
       <c r="J403" t="n">
-        <v>3.6279</v>
+        <v>2.7434</v>
       </c>
     </row>
     <row r="404">
@@ -20395,10 +20395,10 @@
         <v>1.02</v>
       </c>
       <c r="I404" t="n">
-        <v>0.0738</v>
+        <v>0.0527</v>
       </c>
       <c r="J404" t="n">
-        <v>2.1402</v>
+        <v>1.5283</v>
       </c>
     </row>
     <row r="405">
@@ -20435,10 +20435,10 @@
         <v>0.99</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.025</v>
+        <v>-0.018</v>
       </c>
       <c r="J405" t="n">
-        <v>-0.725</v>
+        <v>-0.522</v>
       </c>
     </row>
     <row r="406">
@@ -20475,10 +20475,10 @@
         <v>0.68</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.3656</v>
+        <v>-0.3522</v>
       </c>
       <c r="J406" t="n">
-        <v>-10.6024</v>
+        <v>-10.2138</v>
       </c>
     </row>
     <row r="407">
@@ -20515,10 +20515,10 @@
         <v>1.26</v>
       </c>
       <c r="I407" t="n">
-        <v>0.6776</v>
+        <v>0.6453</v>
       </c>
       <c r="J407" t="n">
-        <v>19.6504</v>
+        <v>18.7137</v>
       </c>
     </row>
     <row r="408">
@@ -20555,10 +20555,10 @@
         <v>1.26</v>
       </c>
       <c r="I408" t="n">
-        <v>0.6776</v>
+        <v>0.6453</v>
       </c>
       <c r="J408" t="n">
-        <v>19.6504</v>
+        <v>18.7137</v>
       </c>
     </row>
     <row r="409">
@@ -20595,10 +20595,10 @@
         <v>1.24</v>
       </c>
       <c r="I409" t="n">
-        <v>0.6354</v>
+        <v>0.6015</v>
       </c>
       <c r="J409" t="n">
-        <v>18.4266</v>
+        <v>17.4435</v>
       </c>
     </row>
     <row r="410">
@@ -20635,10 +20635,10 @@
         <v>1.15</v>
       </c>
       <c r="I410" t="n">
-        <v>0.4382</v>
+        <v>0.4019</v>
       </c>
       <c r="J410" t="n">
-        <v>12.7078</v>
+        <v>11.6551</v>
       </c>
     </row>
     <row r="411">
@@ -20675,10 +20675,10 @@
         <v>0.91</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.3467</v>
+        <v>-0.3053</v>
       </c>
       <c r="J411" t="n">
-        <v>-10.0543</v>
+        <v>-8.8537</v>
       </c>
     </row>
     <row r="412">
@@ -20715,10 +20715,10 @@
         <v>1.79</v>
       </c>
       <c r="I412" t="n">
-        <v>1.4285</v>
+        <v>1.4554</v>
       </c>
       <c r="J412" t="n">
-        <v>32.8555</v>
+        <v>33.4742</v>
       </c>
     </row>
     <row r="413">
@@ -20755,10 +20755,10 @@
         <v>1.74</v>
       </c>
       <c r="I413" t="n">
-        <v>1.3676</v>
+        <v>1.3912</v>
       </c>
       <c r="J413" t="n">
-        <v>31.4548</v>
+        <v>31.9976</v>
       </c>
     </row>
     <row r="414">
@@ -20795,10 +20795,10 @@
         <v>1.59</v>
       </c>
       <c r="I414" t="n">
-        <v>1.1811</v>
+        <v>1.1982</v>
       </c>
       <c r="J414" t="n">
-        <v>27.1653</v>
+        <v>27.5586</v>
       </c>
     </row>
     <row r="415">
@@ -20835,10 +20835,10 @@
         <v>1.1</v>
       </c>
       <c r="I415" t="n">
-        <v>0.2706</v>
+        <v>0.2377</v>
       </c>
       <c r="J415" t="n">
-        <v>6.2238</v>
+        <v>5.4671</v>
       </c>
     </row>
     <row r="416">
@@ -20875,10 +20875,10 @@
         <v>1.04</v>
       </c>
       <c r="I416" t="n">
-        <v>0.0977</v>
+        <v>0.0711</v>
       </c>
       <c r="J416" t="n">
-        <v>2.2471</v>
+        <v>1.6353</v>
       </c>
     </row>
     <row r="417">
@@ -20915,10 +20915,10 @@
         <v>1.02</v>
       </c>
       <c r="I417" t="n">
-        <v>0.1393</v>
+        <v>0.1167</v>
       </c>
       <c r="J417" t="n">
-        <v>3.2039</v>
+        <v>2.6841</v>
       </c>
     </row>
     <row r="418">
@@ -20955,10 +20955,10 @@
         <v>1.01</v>
       </c>
       <c r="I418" t="n">
-        <v>0.1072</v>
+        <v>0.0905</v>
       </c>
       <c r="J418" t="n">
-        <v>2.4656</v>
+        <v>2.0815</v>
       </c>
     </row>
     <row r="419">
@@ -20995,10 +20995,10 @@
         <v>0.59</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.4202</v>
+        <v>-0.4104</v>
       </c>
       <c r="J419" t="n">
-        <v>-9.6646</v>
+        <v>-9.4392</v>
       </c>
     </row>
     <row r="420">
@@ -21035,10 +21035,10 @@
         <v>0.58</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.4291</v>
+        <v>-0.4201</v>
       </c>
       <c r="J420" t="n">
-        <v>-9.869300000000001</v>
+        <v>-9.6623</v>
       </c>
     </row>
     <row r="421">
@@ -21075,10 +21075,10 @@
         <v>0.52</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.4819</v>
+        <v>-0.4783</v>
       </c>
       <c r="J421" t="n">
-        <v>-11.0837</v>
+        <v>-11.0009</v>
       </c>
     </row>
   </sheetData>
